--- a/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
@@ -6,29 +6,36 @@
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId4"/>
+    <sheet name="填写说明" sheetId="2" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
   <si>
-    <t>集团</t>
+    <t>所属集团</t>
   </si>
   <si>
-    <t>医院</t>
+    <t>所属医院*</t>
   </si>
   <si>
-    <t>院区</t>
+    <t>所属院区</t>
   </si>
   <si>
-    <t>科室</t>
+    <t>科室1</t>
   </si>
   <si>
-    <t>登录用户名</t>
+    <t>科室2</t>
   </si>
   <si>
-    <t>姓名</t>
+    <t>科室3</t>
+  </si>
+  <si>
+    <t>登录用户名*</t>
+  </si>
+  <si>
+    <t>姓名*</t>
   </si>
   <si>
     <t>Email</t>
@@ -37,13 +44,16 @@
     <t>电话</t>
   </si>
   <si>
-    <t>激活?</t>
+    <t>激活?*</t>
   </si>
   <si>
-    <t>锁定?</t>
+    <t>锁定?*</t>
   </si>
   <si>
-    <t>角色</t>
+    <t>角色*</t>
+  </si>
+  <si>
+    <t>可见范围（科室）</t>
   </si>
   <si>
     <t>UUID</t>
@@ -52,13 +62,127 @@
     <t>Digital Healthcare</t>
   </si>
   <si>
-    <t>新增医院</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>新增医院</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>A</t>
+    </r>
   </si>
   <si>
     <t>新增院区1</t>
   </si>
   <si>
-    <t>新增科室1</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>新增层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>科室</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>新增层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>科室</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>新增层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>科室</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
   </si>
   <si>
     <t>tony1</t>
@@ -72,6 +196,69 @@
   <si>
     <t>否</t>
   </si>
+  <si>
+    <t>工程师,设备调剂管理人员</t>
+  </si>
+  <si>
+    <t>内科-门诊-内科1，新增层级3科室4</t>
+  </si>
+  <si>
+    <t>填写说明</t>
+  </si>
+  <si>
+    <t>1.在datalist sheet中带有*标记的列为必填项。</t>
+  </si>
+  <si>
+    <t>2.“科室1”、“科室2”和“科室3”分别表示“科室层级1”、“科室层级2”和“科室层级3”</t>
+  </si>
+  <si>
+    <t>3.角色列需要输入以下角色名称，否则系统找不到相对应的名称，不导入该条数据</t>
+  </si>
+  <si>
+    <t>4.多个角色用逗号分隔(不区分大小写)，多个角色中其中有一条角色名称输入有误，则不导入该条数据</t>
+  </si>
+  <si>
+    <t>5.从系统导出时，会带有UUID列，此列不可更改，系统会根据UUID更新相应字段内容</t>
+  </si>
+  <si>
+    <t>6.可见范围中，输入除本人所在科室以外的其他科室名称，可见多个科室用逗号分隔</t>
+  </si>
+  <si>
+    <t>7.可见范围只支持科室的设定，院区、医院等不支持</t>
+  </si>
+  <si>
+    <t>角色名称</t>
+  </si>
+  <si>
+    <t>临床科室人员</t>
+  </si>
+  <si>
+    <t>医学工程处主任</t>
+  </si>
+  <si>
+    <t>后台运营管理</t>
+  </si>
+  <si>
+    <t>仅报修权限账号</t>
+  </si>
+  <si>
+    <t>工程师</t>
+  </si>
+  <si>
+    <t>护理人员</t>
+  </si>
+  <si>
+    <t>院长</t>
+  </si>
+  <si>
+    <t>临床科室主任</t>
+  </si>
+  <si>
+    <t>维修商医工</t>
+  </si>
+  <si>
+    <t>设备调剂管理人员</t>
+  </si>
 </sst>
 </file>
 
@@ -80,7 +267,7 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -96,8 +283,18 @@
       <color indexed="8"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -106,12 +303,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor indexed="10"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="9"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -121,17 +324,169 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -140,17 +495,80 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -171,6 +589,7 @@
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
       <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ff4d5d2c"/>
       <rgbColor rgb="ffaaaaaa"/>
     </indexedColors>
   </colors>
@@ -309,13 +728,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -405,7 +818,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -414,10 +827,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Cambria"/>
-            <a:ea typeface="Cambria"/>
-            <a:cs typeface="Cambria"/>
-            <a:sym typeface="Cambria"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -672,13 +1085,7 @@
           <a:prstDash val="solid"/>
           <a:round/>
         </a:ln>
-        <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
-            <a:srgbClr val="000000">
-              <a:alpha val="38000"/>
-            </a:srgbClr>
-          </a:outerShdw>
-        </a:effectLst>
+        <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
       <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
@@ -982,7 +1389,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -991,10 +1398,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Cambria"/>
-            <a:ea typeface="Cambria"/>
-            <a:cs typeface="Cambria"/>
-            <a:sym typeface="Cambria"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1245,25 +1652,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:IU10"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="17.3516" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.6719" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85156" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.85156" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85156" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85156" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.85156" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.85156" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85156" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="32.6719" style="1" customWidth="1"/>
-    <col min="13" max="256" width="8.85156" style="1" customWidth="1"/>
+    <col min="3" max="4" width="13.5" style="1" customWidth="1"/>
+    <col min="5" max="6" width="14.3516" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6719" style="1" customWidth="1"/>
+    <col min="8" max="9" width="8.85156" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" customWidth="1"/>
+    <col min="11" max="12" width="8.85156" style="1" customWidth="1"/>
+    <col min="13" max="13" width="24.6719" style="1" customWidth="1"/>
+    <col min="14" max="14" width="30" style="1" customWidth="1"/>
+    <col min="15" max="15" width="32.6719" style="1" customWidth="1"/>
+    <col min="16" max="255" width="8.85156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1">
+    <row r="1" ht="30.75" customHeight="1">
       <c r="A1" t="s" s="2">
         <v>0</v>
       </c>
@@ -1300,38 +1706,2594 @@
       <c r="L1" t="s" s="2">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AJ1" s="4"/>
+      <c r="AK1" s="4"/>
+      <c r="AL1" s="4"/>
+      <c r="AM1" s="4"/>
+      <c r="AN1" s="4"/>
+      <c r="AO1" s="4"/>
+      <c r="AP1" s="4"/>
+      <c r="AQ1" s="4"/>
+      <c r="AR1" s="4"/>
+      <c r="AS1" s="4"/>
+      <c r="AT1" s="4"/>
+      <c r="AU1" s="4"/>
+      <c r="AV1" s="4"/>
+      <c r="AW1" s="4"/>
+      <c r="AX1" s="4"/>
+      <c r="AY1" s="4"/>
+      <c r="AZ1" s="4"/>
+      <c r="BA1" s="4"/>
+      <c r="BB1" s="4"/>
+      <c r="BC1" s="4"/>
+      <c r="BD1" s="4"/>
+      <c r="BE1" s="4"/>
+      <c r="BF1" s="4"/>
+      <c r="BG1" s="4"/>
+      <c r="BH1" s="4"/>
+      <c r="BI1" s="4"/>
+      <c r="BJ1" s="4"/>
+      <c r="BK1" s="4"/>
+      <c r="BL1" s="4"/>
+      <c r="BM1" s="4"/>
+      <c r="BN1" s="4"/>
+      <c r="BO1" s="4"/>
+      <c r="BP1" s="4"/>
+      <c r="BQ1" s="4"/>
+      <c r="BR1" s="4"/>
+      <c r="BS1" s="4"/>
+      <c r="BT1" s="4"/>
+      <c r="BU1" s="4"/>
+      <c r="BV1" s="4"/>
+      <c r="BW1" s="4"/>
+      <c r="BX1" s="4"/>
+      <c r="BY1" s="4"/>
+      <c r="BZ1" s="4"/>
+      <c r="CA1" s="4"/>
+      <c r="CB1" s="4"/>
+      <c r="CC1" s="4"/>
+      <c r="CD1" s="4"/>
+      <c r="CE1" s="4"/>
+      <c r="CF1" s="4"/>
+      <c r="CG1" s="4"/>
+      <c r="CH1" s="4"/>
+      <c r="CI1" s="4"/>
+      <c r="CJ1" s="4"/>
+      <c r="CK1" s="4"/>
+      <c r="CL1" s="4"/>
+      <c r="CM1" s="4"/>
+      <c r="CN1" s="4"/>
+      <c r="CO1" s="4"/>
+      <c r="CP1" s="4"/>
+      <c r="CQ1" s="4"/>
+      <c r="CR1" s="4"/>
+      <c r="CS1" s="4"/>
+      <c r="CT1" s="4"/>
+      <c r="CU1" s="4"/>
+      <c r="CV1" s="4"/>
+      <c r="CW1" s="4"/>
+      <c r="CX1" s="4"/>
+      <c r="CY1" s="4"/>
+      <c r="CZ1" s="4"/>
+      <c r="DA1" s="4"/>
+      <c r="DB1" s="4"/>
+      <c r="DC1" s="4"/>
+      <c r="DD1" s="4"/>
+      <c r="DE1" s="4"/>
+      <c r="DF1" s="4"/>
+      <c r="DG1" s="4"/>
+      <c r="DH1" s="4"/>
+      <c r="DI1" s="4"/>
+      <c r="DJ1" s="4"/>
+      <c r="DK1" s="4"/>
+      <c r="DL1" s="4"/>
+      <c r="DM1" s="4"/>
+      <c r="DN1" s="4"/>
+      <c r="DO1" s="4"/>
+      <c r="DP1" s="4"/>
+      <c r="DQ1" s="4"/>
+      <c r="DR1" s="4"/>
+      <c r="DS1" s="4"/>
+      <c r="DT1" s="4"/>
+      <c r="DU1" s="4"/>
+      <c r="DV1" s="4"/>
+      <c r="DW1" s="4"/>
+      <c r="DX1" s="4"/>
+      <c r="DY1" s="4"/>
+      <c r="DZ1" s="4"/>
+      <c r="EA1" s="4"/>
+      <c r="EB1" s="4"/>
+      <c r="EC1" s="4"/>
+      <c r="ED1" s="4"/>
+      <c r="EE1" s="4"/>
+      <c r="EF1" s="4"/>
+      <c r="EG1" s="4"/>
+      <c r="EH1" s="4"/>
+      <c r="EI1" s="4"/>
+      <c r="EJ1" s="4"/>
+      <c r="EK1" s="4"/>
+      <c r="EL1" s="4"/>
+      <c r="EM1" s="4"/>
+      <c r="EN1" s="4"/>
+      <c r="EO1" s="4"/>
+      <c r="EP1" s="4"/>
+      <c r="EQ1" s="4"/>
+      <c r="ER1" s="4"/>
+      <c r="ES1" s="4"/>
+      <c r="ET1" s="4"/>
+      <c r="EU1" s="4"/>
+      <c r="EV1" s="4"/>
+      <c r="EW1" s="4"/>
+      <c r="EX1" s="4"/>
+      <c r="EY1" s="4"/>
+      <c r="EZ1" s="4"/>
+      <c r="FA1" s="4"/>
+      <c r="FB1" s="4"/>
+      <c r="FC1" s="4"/>
+      <c r="FD1" s="4"/>
+      <c r="FE1" s="4"/>
+      <c r="FF1" s="4"/>
+      <c r="FG1" s="4"/>
+      <c r="FH1" s="4"/>
+      <c r="FI1" s="4"/>
+      <c r="FJ1" s="4"/>
+      <c r="FK1" s="4"/>
+      <c r="FL1" s="4"/>
+      <c r="FM1" s="4"/>
+      <c r="FN1" s="4"/>
+      <c r="FO1" s="4"/>
+      <c r="FP1" s="4"/>
+      <c r="FQ1" s="4"/>
+      <c r="FR1" s="4"/>
+      <c r="FS1" s="4"/>
+      <c r="FT1" s="4"/>
+      <c r="FU1" s="4"/>
+      <c r="FV1" s="4"/>
+      <c r="FW1" s="4"/>
+      <c r="FX1" s="4"/>
+      <c r="FY1" s="4"/>
+      <c r="FZ1" s="4"/>
+      <c r="GA1" s="4"/>
+      <c r="GB1" s="4"/>
+      <c r="GC1" s="4"/>
+      <c r="GD1" s="4"/>
+      <c r="GE1" s="4"/>
+      <c r="GF1" s="4"/>
+      <c r="GG1" s="4"/>
+      <c r="GH1" s="4"/>
+      <c r="GI1" s="4"/>
+      <c r="GJ1" s="4"/>
+      <c r="GK1" s="4"/>
+      <c r="GL1" s="4"/>
+      <c r="GM1" s="4"/>
+      <c r="GN1" s="4"/>
+      <c r="GO1" s="4"/>
+      <c r="GP1" s="4"/>
+      <c r="GQ1" s="4"/>
+      <c r="GR1" s="4"/>
+      <c r="GS1" s="4"/>
+      <c r="GT1" s="4"/>
+      <c r="GU1" s="4"/>
+      <c r="GV1" s="4"/>
+      <c r="GW1" s="4"/>
+      <c r="GX1" s="4"/>
+      <c r="GY1" s="4"/>
+      <c r="GZ1" s="4"/>
+      <c r="HA1" s="4"/>
+      <c r="HB1" s="4"/>
+      <c r="HC1" s="4"/>
+      <c r="HD1" s="4"/>
+      <c r="HE1" s="4"/>
+      <c r="HF1" s="4"/>
+      <c r="HG1" s="4"/>
+      <c r="HH1" s="4"/>
+      <c r="HI1" s="4"/>
+      <c r="HJ1" s="4"/>
+      <c r="HK1" s="4"/>
+      <c r="HL1" s="4"/>
+      <c r="HM1" s="4"/>
+      <c r="HN1" s="4"/>
+      <c r="HO1" s="4"/>
+      <c r="HP1" s="4"/>
+      <c r="HQ1" s="4"/>
+      <c r="HR1" s="4"/>
+      <c r="HS1" s="4"/>
+      <c r="HT1" s="4"/>
+      <c r="HU1" s="4"/>
+      <c r="HV1" s="4"/>
+      <c r="HW1" s="4"/>
+      <c r="HX1" s="4"/>
+      <c r="HY1" s="4"/>
+      <c r="HZ1" s="4"/>
+      <c r="IA1" s="4"/>
+      <c r="IB1" s="4"/>
+      <c r="IC1" s="4"/>
+      <c r="ID1" s="4"/>
+      <c r="IE1" s="4"/>
+      <c r="IF1" s="4"/>
+      <c r="IG1" s="4"/>
+      <c r="IH1" s="4"/>
+      <c r="II1" s="4"/>
+      <c r="IJ1" s="4"/>
+      <c r="IK1" s="4"/>
+      <c r="IL1" s="4"/>
+      <c r="IM1" s="4"/>
+      <c r="IN1" s="4"/>
+      <c r="IO1" s="4"/>
+      <c r="IP1" s="4"/>
+      <c r="IQ1" s="4"/>
+      <c r="IR1" s="4"/>
+      <c r="IS1" s="4"/>
+      <c r="IT1" s="4"/>
+      <c r="IU1" s="5"/>
     </row>
-    <row r="2" ht="13.65" customHeight="1">
-      <c r="A2" t="s" s="2">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s" s="2">
+    <row r="2" ht="34.5" customHeight="1">
+      <c r="A2" t="s" s="6">
         <v>15</v>
       </c>
-      <c r="E2" t="s" s="2">
+      <c r="B2" t="s" s="6">
         <v>16</v>
       </c>
-      <c r="F2" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" t="s" s="2">
+      <c r="C2" t="s" s="6">
         <v>17</v>
       </c>
-      <c r="I2" t="s" s="2">
+      <c r="D2" t="s" s="6">
         <v>18</v>
       </c>
-      <c r="J2" t="s" s="2">
+      <c r="E2" t="s" s="6">
         <v>19</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
+      <c r="F2" t="s" s="6">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s" s="6">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s" s="6">
+        <v>21</v>
+      </c>
+      <c r="I2" s="6"/>
+      <c r="J2" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s" s="6">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s" s="6">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s" s="7">
+        <v>25</v>
+      </c>
+      <c r="N2" t="s" s="7">
+        <v>26</v>
+      </c>
+      <c r="O2" s="6"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
+      <c r="AE2" s="9"/>
+      <c r="AF2" s="9"/>
+      <c r="AG2" s="9"/>
+      <c r="AH2" s="9"/>
+      <c r="AI2" s="9"/>
+      <c r="AJ2" s="9"/>
+      <c r="AK2" s="9"/>
+      <c r="AL2" s="9"/>
+      <c r="AM2" s="9"/>
+      <c r="AN2" s="9"/>
+      <c r="AO2" s="9"/>
+      <c r="AP2" s="9"/>
+      <c r="AQ2" s="9"/>
+      <c r="AR2" s="9"/>
+      <c r="AS2" s="9"/>
+      <c r="AT2" s="9"/>
+      <c r="AU2" s="9"/>
+      <c r="AV2" s="9"/>
+      <c r="AW2" s="9"/>
+      <c r="AX2" s="9"/>
+      <c r="AY2" s="9"/>
+      <c r="AZ2" s="9"/>
+      <c r="BA2" s="9"/>
+      <c r="BB2" s="9"/>
+      <c r="BC2" s="9"/>
+      <c r="BD2" s="9"/>
+      <c r="BE2" s="9"/>
+      <c r="BF2" s="9"/>
+      <c r="BG2" s="9"/>
+      <c r="BH2" s="9"/>
+      <c r="BI2" s="9"/>
+      <c r="BJ2" s="9"/>
+      <c r="BK2" s="9"/>
+      <c r="BL2" s="9"/>
+      <c r="BM2" s="9"/>
+      <c r="BN2" s="9"/>
+      <c r="BO2" s="9"/>
+      <c r="BP2" s="9"/>
+      <c r="BQ2" s="9"/>
+      <c r="BR2" s="9"/>
+      <c r="BS2" s="9"/>
+      <c r="BT2" s="9"/>
+      <c r="BU2" s="9"/>
+      <c r="BV2" s="9"/>
+      <c r="BW2" s="9"/>
+      <c r="BX2" s="9"/>
+      <c r="BY2" s="9"/>
+      <c r="BZ2" s="9"/>
+      <c r="CA2" s="9"/>
+      <c r="CB2" s="9"/>
+      <c r="CC2" s="9"/>
+      <c r="CD2" s="9"/>
+      <c r="CE2" s="9"/>
+      <c r="CF2" s="9"/>
+      <c r="CG2" s="9"/>
+      <c r="CH2" s="9"/>
+      <c r="CI2" s="9"/>
+      <c r="CJ2" s="9"/>
+      <c r="CK2" s="9"/>
+      <c r="CL2" s="9"/>
+      <c r="CM2" s="9"/>
+      <c r="CN2" s="9"/>
+      <c r="CO2" s="9"/>
+      <c r="CP2" s="9"/>
+      <c r="CQ2" s="9"/>
+      <c r="CR2" s="9"/>
+      <c r="CS2" s="9"/>
+      <c r="CT2" s="9"/>
+      <c r="CU2" s="9"/>
+      <c r="CV2" s="9"/>
+      <c r="CW2" s="9"/>
+      <c r="CX2" s="9"/>
+      <c r="CY2" s="9"/>
+      <c r="CZ2" s="9"/>
+      <c r="DA2" s="9"/>
+      <c r="DB2" s="9"/>
+      <c r="DC2" s="9"/>
+      <c r="DD2" s="9"/>
+      <c r="DE2" s="9"/>
+      <c r="DF2" s="9"/>
+      <c r="DG2" s="9"/>
+      <c r="DH2" s="9"/>
+      <c r="DI2" s="9"/>
+      <c r="DJ2" s="9"/>
+      <c r="DK2" s="9"/>
+      <c r="DL2" s="9"/>
+      <c r="DM2" s="9"/>
+      <c r="DN2" s="9"/>
+      <c r="DO2" s="9"/>
+      <c r="DP2" s="9"/>
+      <c r="DQ2" s="9"/>
+      <c r="DR2" s="9"/>
+      <c r="DS2" s="9"/>
+      <c r="DT2" s="9"/>
+      <c r="DU2" s="9"/>
+      <c r="DV2" s="9"/>
+      <c r="DW2" s="9"/>
+      <c r="DX2" s="9"/>
+      <c r="DY2" s="9"/>
+      <c r="DZ2" s="9"/>
+      <c r="EA2" s="9"/>
+      <c r="EB2" s="9"/>
+      <c r="EC2" s="9"/>
+      <c r="ED2" s="9"/>
+      <c r="EE2" s="9"/>
+      <c r="EF2" s="9"/>
+      <c r="EG2" s="9"/>
+      <c r="EH2" s="9"/>
+      <c r="EI2" s="9"/>
+      <c r="EJ2" s="9"/>
+      <c r="EK2" s="9"/>
+      <c r="EL2" s="9"/>
+      <c r="EM2" s="9"/>
+      <c r="EN2" s="9"/>
+      <c r="EO2" s="9"/>
+      <c r="EP2" s="9"/>
+      <c r="EQ2" s="9"/>
+      <c r="ER2" s="9"/>
+      <c r="ES2" s="9"/>
+      <c r="ET2" s="9"/>
+      <c r="EU2" s="9"/>
+      <c r="EV2" s="9"/>
+      <c r="EW2" s="9"/>
+      <c r="EX2" s="9"/>
+      <c r="EY2" s="9"/>
+      <c r="EZ2" s="9"/>
+      <c r="FA2" s="9"/>
+      <c r="FB2" s="9"/>
+      <c r="FC2" s="9"/>
+      <c r="FD2" s="9"/>
+      <c r="FE2" s="9"/>
+      <c r="FF2" s="9"/>
+      <c r="FG2" s="9"/>
+      <c r="FH2" s="9"/>
+      <c r="FI2" s="9"/>
+      <c r="FJ2" s="9"/>
+      <c r="FK2" s="9"/>
+      <c r="FL2" s="9"/>
+      <c r="FM2" s="9"/>
+      <c r="FN2" s="9"/>
+      <c r="FO2" s="9"/>
+      <c r="FP2" s="9"/>
+      <c r="FQ2" s="9"/>
+      <c r="FR2" s="9"/>
+      <c r="FS2" s="9"/>
+      <c r="FT2" s="9"/>
+      <c r="FU2" s="9"/>
+      <c r="FV2" s="9"/>
+      <c r="FW2" s="9"/>
+      <c r="FX2" s="9"/>
+      <c r="FY2" s="9"/>
+      <c r="FZ2" s="9"/>
+      <c r="GA2" s="9"/>
+      <c r="GB2" s="9"/>
+      <c r="GC2" s="9"/>
+      <c r="GD2" s="9"/>
+      <c r="GE2" s="9"/>
+      <c r="GF2" s="9"/>
+      <c r="GG2" s="9"/>
+      <c r="GH2" s="9"/>
+      <c r="GI2" s="9"/>
+      <c r="GJ2" s="9"/>
+      <c r="GK2" s="9"/>
+      <c r="GL2" s="9"/>
+      <c r="GM2" s="9"/>
+      <c r="GN2" s="9"/>
+      <c r="GO2" s="9"/>
+      <c r="GP2" s="9"/>
+      <c r="GQ2" s="9"/>
+      <c r="GR2" s="9"/>
+      <c r="GS2" s="9"/>
+      <c r="GT2" s="9"/>
+      <c r="GU2" s="9"/>
+      <c r="GV2" s="9"/>
+      <c r="GW2" s="9"/>
+      <c r="GX2" s="9"/>
+      <c r="GY2" s="9"/>
+      <c r="GZ2" s="9"/>
+      <c r="HA2" s="9"/>
+      <c r="HB2" s="9"/>
+      <c r="HC2" s="9"/>
+      <c r="HD2" s="9"/>
+      <c r="HE2" s="9"/>
+      <c r="HF2" s="9"/>
+      <c r="HG2" s="9"/>
+      <c r="HH2" s="9"/>
+      <c r="HI2" s="9"/>
+      <c r="HJ2" s="9"/>
+      <c r="HK2" s="9"/>
+      <c r="HL2" s="9"/>
+      <c r="HM2" s="9"/>
+      <c r="HN2" s="9"/>
+      <c r="HO2" s="9"/>
+      <c r="HP2" s="9"/>
+      <c r="HQ2" s="9"/>
+      <c r="HR2" s="9"/>
+      <c r="HS2" s="9"/>
+      <c r="HT2" s="9"/>
+      <c r="HU2" s="9"/>
+      <c r="HV2" s="9"/>
+      <c r="HW2" s="9"/>
+      <c r="HX2" s="9"/>
+      <c r="HY2" s="9"/>
+      <c r="HZ2" s="9"/>
+      <c r="IA2" s="9"/>
+      <c r="IB2" s="9"/>
+      <c r="IC2" s="9"/>
+      <c r="ID2" s="9"/>
+      <c r="IE2" s="9"/>
+      <c r="IF2" s="9"/>
+      <c r="IG2" s="9"/>
+      <c r="IH2" s="9"/>
+      <c r="II2" s="9"/>
+      <c r="IJ2" s="9"/>
+      <c r="IK2" s="9"/>
+      <c r="IL2" s="9"/>
+      <c r="IM2" s="9"/>
+      <c r="IN2" s="9"/>
+      <c r="IO2" s="9"/>
+      <c r="IP2" s="9"/>
+      <c r="IQ2" s="9"/>
+      <c r="IR2" s="9"/>
+      <c r="IS2" s="9"/>
+      <c r="IT2" s="9"/>
+      <c r="IU2" s="10"/>
+    </row>
+    <row r="3" ht="13.65" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
+      <c r="AF3" s="9"/>
+      <c r="AG3" s="9"/>
+      <c r="AH3" s="9"/>
+      <c r="AI3" s="9"/>
+      <c r="AJ3" s="9"/>
+      <c r="AK3" s="9"/>
+      <c r="AL3" s="9"/>
+      <c r="AM3" s="9"/>
+      <c r="AN3" s="9"/>
+      <c r="AO3" s="9"/>
+      <c r="AP3" s="9"/>
+      <c r="AQ3" s="9"/>
+      <c r="AR3" s="9"/>
+      <c r="AS3" s="9"/>
+      <c r="AT3" s="9"/>
+      <c r="AU3" s="9"/>
+      <c r="AV3" s="9"/>
+      <c r="AW3" s="9"/>
+      <c r="AX3" s="9"/>
+      <c r="AY3" s="9"/>
+      <c r="AZ3" s="9"/>
+      <c r="BA3" s="9"/>
+      <c r="BB3" s="9"/>
+      <c r="BC3" s="9"/>
+      <c r="BD3" s="9"/>
+      <c r="BE3" s="9"/>
+      <c r="BF3" s="9"/>
+      <c r="BG3" s="9"/>
+      <c r="BH3" s="9"/>
+      <c r="BI3" s="9"/>
+      <c r="BJ3" s="9"/>
+      <c r="BK3" s="9"/>
+      <c r="BL3" s="9"/>
+      <c r="BM3" s="9"/>
+      <c r="BN3" s="9"/>
+      <c r="BO3" s="9"/>
+      <c r="BP3" s="9"/>
+      <c r="BQ3" s="9"/>
+      <c r="BR3" s="9"/>
+      <c r="BS3" s="9"/>
+      <c r="BT3" s="9"/>
+      <c r="BU3" s="9"/>
+      <c r="BV3" s="9"/>
+      <c r="BW3" s="9"/>
+      <c r="BX3" s="9"/>
+      <c r="BY3" s="9"/>
+      <c r="BZ3" s="9"/>
+      <c r="CA3" s="9"/>
+      <c r="CB3" s="9"/>
+      <c r="CC3" s="9"/>
+      <c r="CD3" s="9"/>
+      <c r="CE3" s="9"/>
+      <c r="CF3" s="9"/>
+      <c r="CG3" s="9"/>
+      <c r="CH3" s="9"/>
+      <c r="CI3" s="9"/>
+      <c r="CJ3" s="9"/>
+      <c r="CK3" s="9"/>
+      <c r="CL3" s="9"/>
+      <c r="CM3" s="9"/>
+      <c r="CN3" s="9"/>
+      <c r="CO3" s="9"/>
+      <c r="CP3" s="9"/>
+      <c r="CQ3" s="9"/>
+      <c r="CR3" s="9"/>
+      <c r="CS3" s="9"/>
+      <c r="CT3" s="9"/>
+      <c r="CU3" s="9"/>
+      <c r="CV3" s="9"/>
+      <c r="CW3" s="9"/>
+      <c r="CX3" s="9"/>
+      <c r="CY3" s="9"/>
+      <c r="CZ3" s="9"/>
+      <c r="DA3" s="9"/>
+      <c r="DB3" s="9"/>
+      <c r="DC3" s="9"/>
+      <c r="DD3" s="9"/>
+      <c r="DE3" s="9"/>
+      <c r="DF3" s="9"/>
+      <c r="DG3" s="9"/>
+      <c r="DH3" s="9"/>
+      <c r="DI3" s="9"/>
+      <c r="DJ3" s="9"/>
+      <c r="DK3" s="9"/>
+      <c r="DL3" s="9"/>
+      <c r="DM3" s="9"/>
+      <c r="DN3" s="9"/>
+      <c r="DO3" s="9"/>
+      <c r="DP3" s="9"/>
+      <c r="DQ3" s="9"/>
+      <c r="DR3" s="9"/>
+      <c r="DS3" s="9"/>
+      <c r="DT3" s="9"/>
+      <c r="DU3" s="9"/>
+      <c r="DV3" s="9"/>
+      <c r="DW3" s="9"/>
+      <c r="DX3" s="9"/>
+      <c r="DY3" s="9"/>
+      <c r="DZ3" s="9"/>
+      <c r="EA3" s="9"/>
+      <c r="EB3" s="9"/>
+      <c r="EC3" s="9"/>
+      <c r="ED3" s="9"/>
+      <c r="EE3" s="9"/>
+      <c r="EF3" s="9"/>
+      <c r="EG3" s="9"/>
+      <c r="EH3" s="9"/>
+      <c r="EI3" s="9"/>
+      <c r="EJ3" s="9"/>
+      <c r="EK3" s="9"/>
+      <c r="EL3" s="9"/>
+      <c r="EM3" s="9"/>
+      <c r="EN3" s="9"/>
+      <c r="EO3" s="9"/>
+      <c r="EP3" s="9"/>
+      <c r="EQ3" s="9"/>
+      <c r="ER3" s="9"/>
+      <c r="ES3" s="9"/>
+      <c r="ET3" s="9"/>
+      <c r="EU3" s="9"/>
+      <c r="EV3" s="9"/>
+      <c r="EW3" s="9"/>
+      <c r="EX3" s="9"/>
+      <c r="EY3" s="9"/>
+      <c r="EZ3" s="9"/>
+      <c r="FA3" s="9"/>
+      <c r="FB3" s="9"/>
+      <c r="FC3" s="9"/>
+      <c r="FD3" s="9"/>
+      <c r="FE3" s="9"/>
+      <c r="FF3" s="9"/>
+      <c r="FG3" s="9"/>
+      <c r="FH3" s="9"/>
+      <c r="FI3" s="9"/>
+      <c r="FJ3" s="9"/>
+      <c r="FK3" s="9"/>
+      <c r="FL3" s="9"/>
+      <c r="FM3" s="9"/>
+      <c r="FN3" s="9"/>
+      <c r="FO3" s="9"/>
+      <c r="FP3" s="9"/>
+      <c r="FQ3" s="9"/>
+      <c r="FR3" s="9"/>
+      <c r="FS3" s="9"/>
+      <c r="FT3" s="9"/>
+      <c r="FU3" s="9"/>
+      <c r="FV3" s="9"/>
+      <c r="FW3" s="9"/>
+      <c r="FX3" s="9"/>
+      <c r="FY3" s="9"/>
+      <c r="FZ3" s="9"/>
+      <c r="GA3" s="9"/>
+      <c r="GB3" s="9"/>
+      <c r="GC3" s="9"/>
+      <c r="GD3" s="9"/>
+      <c r="GE3" s="9"/>
+      <c r="GF3" s="9"/>
+      <c r="GG3" s="9"/>
+      <c r="GH3" s="9"/>
+      <c r="GI3" s="9"/>
+      <c r="GJ3" s="9"/>
+      <c r="GK3" s="9"/>
+      <c r="GL3" s="9"/>
+      <c r="GM3" s="9"/>
+      <c r="GN3" s="9"/>
+      <c r="GO3" s="9"/>
+      <c r="GP3" s="9"/>
+      <c r="GQ3" s="9"/>
+      <c r="GR3" s="9"/>
+      <c r="GS3" s="9"/>
+      <c r="GT3" s="9"/>
+      <c r="GU3" s="9"/>
+      <c r="GV3" s="9"/>
+      <c r="GW3" s="9"/>
+      <c r="GX3" s="9"/>
+      <c r="GY3" s="9"/>
+      <c r="GZ3" s="9"/>
+      <c r="HA3" s="9"/>
+      <c r="HB3" s="9"/>
+      <c r="HC3" s="9"/>
+      <c r="HD3" s="9"/>
+      <c r="HE3" s="9"/>
+      <c r="HF3" s="9"/>
+      <c r="HG3" s="9"/>
+      <c r="HH3" s="9"/>
+      <c r="HI3" s="9"/>
+      <c r="HJ3" s="9"/>
+      <c r="HK3" s="9"/>
+      <c r="HL3" s="9"/>
+      <c r="HM3" s="9"/>
+      <c r="HN3" s="9"/>
+      <c r="HO3" s="9"/>
+      <c r="HP3" s="9"/>
+      <c r="HQ3" s="9"/>
+      <c r="HR3" s="9"/>
+      <c r="HS3" s="9"/>
+      <c r="HT3" s="9"/>
+      <c r="HU3" s="9"/>
+      <c r="HV3" s="9"/>
+      <c r="HW3" s="9"/>
+      <c r="HX3" s="9"/>
+      <c r="HY3" s="9"/>
+      <c r="HZ3" s="9"/>
+      <c r="IA3" s="9"/>
+      <c r="IB3" s="9"/>
+      <c r="IC3" s="9"/>
+      <c r="ID3" s="9"/>
+      <c r="IE3" s="9"/>
+      <c r="IF3" s="9"/>
+      <c r="IG3" s="9"/>
+      <c r="IH3" s="9"/>
+      <c r="II3" s="9"/>
+      <c r="IJ3" s="9"/>
+      <c r="IK3" s="9"/>
+      <c r="IL3" s="9"/>
+      <c r="IM3" s="9"/>
+      <c r="IN3" s="9"/>
+      <c r="IO3" s="9"/>
+      <c r="IP3" s="9"/>
+      <c r="IQ3" s="9"/>
+      <c r="IR3" s="9"/>
+      <c r="IS3" s="9"/>
+      <c r="IT3" s="9"/>
+      <c r="IU3" s="10"/>
+    </row>
+    <row r="4" ht="13.65" customHeight="1">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="9"/>
+      <c r="AE4" s="9"/>
+      <c r="AF4" s="9"/>
+      <c r="AG4" s="9"/>
+      <c r="AH4" s="9"/>
+      <c r="AI4" s="9"/>
+      <c r="AJ4" s="9"/>
+      <c r="AK4" s="9"/>
+      <c r="AL4" s="9"/>
+      <c r="AM4" s="9"/>
+      <c r="AN4" s="9"/>
+      <c r="AO4" s="9"/>
+      <c r="AP4" s="9"/>
+      <c r="AQ4" s="9"/>
+      <c r="AR4" s="9"/>
+      <c r="AS4" s="9"/>
+      <c r="AT4" s="9"/>
+      <c r="AU4" s="9"/>
+      <c r="AV4" s="9"/>
+      <c r="AW4" s="9"/>
+      <c r="AX4" s="9"/>
+      <c r="AY4" s="9"/>
+      <c r="AZ4" s="9"/>
+      <c r="BA4" s="9"/>
+      <c r="BB4" s="9"/>
+      <c r="BC4" s="9"/>
+      <c r="BD4" s="9"/>
+      <c r="BE4" s="9"/>
+      <c r="BF4" s="9"/>
+      <c r="BG4" s="9"/>
+      <c r="BH4" s="9"/>
+      <c r="BI4" s="9"/>
+      <c r="BJ4" s="9"/>
+      <c r="BK4" s="9"/>
+      <c r="BL4" s="9"/>
+      <c r="BM4" s="9"/>
+      <c r="BN4" s="9"/>
+      <c r="BO4" s="9"/>
+      <c r="BP4" s="9"/>
+      <c r="BQ4" s="9"/>
+      <c r="BR4" s="9"/>
+      <c r="BS4" s="9"/>
+      <c r="BT4" s="9"/>
+      <c r="BU4" s="9"/>
+      <c r="BV4" s="9"/>
+      <c r="BW4" s="9"/>
+      <c r="BX4" s="9"/>
+      <c r="BY4" s="9"/>
+      <c r="BZ4" s="9"/>
+      <c r="CA4" s="9"/>
+      <c r="CB4" s="9"/>
+      <c r="CC4" s="9"/>
+      <c r="CD4" s="9"/>
+      <c r="CE4" s="9"/>
+      <c r="CF4" s="9"/>
+      <c r="CG4" s="9"/>
+      <c r="CH4" s="9"/>
+      <c r="CI4" s="9"/>
+      <c r="CJ4" s="9"/>
+      <c r="CK4" s="9"/>
+      <c r="CL4" s="9"/>
+      <c r="CM4" s="9"/>
+      <c r="CN4" s="9"/>
+      <c r="CO4" s="9"/>
+      <c r="CP4" s="9"/>
+      <c r="CQ4" s="9"/>
+      <c r="CR4" s="9"/>
+      <c r="CS4" s="9"/>
+      <c r="CT4" s="9"/>
+      <c r="CU4" s="9"/>
+      <c r="CV4" s="9"/>
+      <c r="CW4" s="9"/>
+      <c r="CX4" s="9"/>
+      <c r="CY4" s="9"/>
+      <c r="CZ4" s="9"/>
+      <c r="DA4" s="9"/>
+      <c r="DB4" s="9"/>
+      <c r="DC4" s="9"/>
+      <c r="DD4" s="9"/>
+      <c r="DE4" s="9"/>
+      <c r="DF4" s="9"/>
+      <c r="DG4" s="9"/>
+      <c r="DH4" s="9"/>
+      <c r="DI4" s="9"/>
+      <c r="DJ4" s="9"/>
+      <c r="DK4" s="9"/>
+      <c r="DL4" s="9"/>
+      <c r="DM4" s="9"/>
+      <c r="DN4" s="9"/>
+      <c r="DO4" s="9"/>
+      <c r="DP4" s="9"/>
+      <c r="DQ4" s="9"/>
+      <c r="DR4" s="9"/>
+      <c r="DS4" s="9"/>
+      <c r="DT4" s="9"/>
+      <c r="DU4" s="9"/>
+      <c r="DV4" s="9"/>
+      <c r="DW4" s="9"/>
+      <c r="DX4" s="9"/>
+      <c r="DY4" s="9"/>
+      <c r="DZ4" s="9"/>
+      <c r="EA4" s="9"/>
+      <c r="EB4" s="9"/>
+      <c r="EC4" s="9"/>
+      <c r="ED4" s="9"/>
+      <c r="EE4" s="9"/>
+      <c r="EF4" s="9"/>
+      <c r="EG4" s="9"/>
+      <c r="EH4" s="9"/>
+      <c r="EI4" s="9"/>
+      <c r="EJ4" s="9"/>
+      <c r="EK4" s="9"/>
+      <c r="EL4" s="9"/>
+      <c r="EM4" s="9"/>
+      <c r="EN4" s="9"/>
+      <c r="EO4" s="9"/>
+      <c r="EP4" s="9"/>
+      <c r="EQ4" s="9"/>
+      <c r="ER4" s="9"/>
+      <c r="ES4" s="9"/>
+      <c r="ET4" s="9"/>
+      <c r="EU4" s="9"/>
+      <c r="EV4" s="9"/>
+      <c r="EW4" s="9"/>
+      <c r="EX4" s="9"/>
+      <c r="EY4" s="9"/>
+      <c r="EZ4" s="9"/>
+      <c r="FA4" s="9"/>
+      <c r="FB4" s="9"/>
+      <c r="FC4" s="9"/>
+      <c r="FD4" s="9"/>
+      <c r="FE4" s="9"/>
+      <c r="FF4" s="9"/>
+      <c r="FG4" s="9"/>
+      <c r="FH4" s="9"/>
+      <c r="FI4" s="9"/>
+      <c r="FJ4" s="9"/>
+      <c r="FK4" s="9"/>
+      <c r="FL4" s="9"/>
+      <c r="FM4" s="9"/>
+      <c r="FN4" s="9"/>
+      <c r="FO4" s="9"/>
+      <c r="FP4" s="9"/>
+      <c r="FQ4" s="9"/>
+      <c r="FR4" s="9"/>
+      <c r="FS4" s="9"/>
+      <c r="FT4" s="9"/>
+      <c r="FU4" s="9"/>
+      <c r="FV4" s="9"/>
+      <c r="FW4" s="9"/>
+      <c r="FX4" s="9"/>
+      <c r="FY4" s="9"/>
+      <c r="FZ4" s="9"/>
+      <c r="GA4" s="9"/>
+      <c r="GB4" s="9"/>
+      <c r="GC4" s="9"/>
+      <c r="GD4" s="9"/>
+      <c r="GE4" s="9"/>
+      <c r="GF4" s="9"/>
+      <c r="GG4" s="9"/>
+      <c r="GH4" s="9"/>
+      <c r="GI4" s="9"/>
+      <c r="GJ4" s="9"/>
+      <c r="GK4" s="9"/>
+      <c r="GL4" s="9"/>
+      <c r="GM4" s="9"/>
+      <c r="GN4" s="9"/>
+      <c r="GO4" s="9"/>
+      <c r="GP4" s="9"/>
+      <c r="GQ4" s="9"/>
+      <c r="GR4" s="9"/>
+      <c r="GS4" s="9"/>
+      <c r="GT4" s="9"/>
+      <c r="GU4" s="9"/>
+      <c r="GV4" s="9"/>
+      <c r="GW4" s="9"/>
+      <c r="GX4" s="9"/>
+      <c r="GY4" s="9"/>
+      <c r="GZ4" s="9"/>
+      <c r="HA4" s="9"/>
+      <c r="HB4" s="9"/>
+      <c r="HC4" s="9"/>
+      <c r="HD4" s="9"/>
+      <c r="HE4" s="9"/>
+      <c r="HF4" s="9"/>
+      <c r="HG4" s="9"/>
+      <c r="HH4" s="9"/>
+      <c r="HI4" s="9"/>
+      <c r="HJ4" s="9"/>
+      <c r="HK4" s="9"/>
+      <c r="HL4" s="9"/>
+      <c r="HM4" s="9"/>
+      <c r="HN4" s="9"/>
+      <c r="HO4" s="9"/>
+      <c r="HP4" s="9"/>
+      <c r="HQ4" s="9"/>
+      <c r="HR4" s="9"/>
+      <c r="HS4" s="9"/>
+      <c r="HT4" s="9"/>
+      <c r="HU4" s="9"/>
+      <c r="HV4" s="9"/>
+      <c r="HW4" s="9"/>
+      <c r="HX4" s="9"/>
+      <c r="HY4" s="9"/>
+      <c r="HZ4" s="9"/>
+      <c r="IA4" s="9"/>
+      <c r="IB4" s="9"/>
+      <c r="IC4" s="9"/>
+      <c r="ID4" s="9"/>
+      <c r="IE4" s="9"/>
+      <c r="IF4" s="9"/>
+      <c r="IG4" s="9"/>
+      <c r="IH4" s="9"/>
+      <c r="II4" s="9"/>
+      <c r="IJ4" s="9"/>
+      <c r="IK4" s="9"/>
+      <c r="IL4" s="9"/>
+      <c r="IM4" s="9"/>
+      <c r="IN4" s="9"/>
+      <c r="IO4" s="9"/>
+      <c r="IP4" s="9"/>
+      <c r="IQ4" s="9"/>
+      <c r="IR4" s="9"/>
+      <c r="IS4" s="9"/>
+      <c r="IT4" s="9"/>
+      <c r="IU4" s="10"/>
+    </row>
+    <row r="5" ht="13.65" customHeight="1">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9"/>
+      <c r="AD5" s="9"/>
+      <c r="AE5" s="9"/>
+      <c r="AF5" s="9"/>
+      <c r="AG5" s="9"/>
+      <c r="AH5" s="9"/>
+      <c r="AI5" s="9"/>
+      <c r="AJ5" s="9"/>
+      <c r="AK5" s="9"/>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+      <c r="BI5" s="9"/>
+      <c r="BJ5" s="9"/>
+      <c r="BK5" s="9"/>
+      <c r="BL5" s="9"/>
+      <c r="BM5" s="9"/>
+      <c r="BN5" s="9"/>
+      <c r="BO5" s="9"/>
+      <c r="BP5" s="9"/>
+      <c r="BQ5" s="9"/>
+      <c r="BR5" s="9"/>
+      <c r="BS5" s="9"/>
+      <c r="BT5" s="9"/>
+      <c r="BU5" s="9"/>
+      <c r="BV5" s="9"/>
+      <c r="BW5" s="9"/>
+      <c r="BX5" s="9"/>
+      <c r="BY5" s="9"/>
+      <c r="BZ5" s="9"/>
+      <c r="CA5" s="9"/>
+      <c r="CB5" s="9"/>
+      <c r="CC5" s="9"/>
+      <c r="CD5" s="9"/>
+      <c r="CE5" s="9"/>
+      <c r="CF5" s="9"/>
+      <c r="CG5" s="9"/>
+      <c r="CH5" s="9"/>
+      <c r="CI5" s="9"/>
+      <c r="CJ5" s="9"/>
+      <c r="CK5" s="9"/>
+      <c r="CL5" s="9"/>
+      <c r="CM5" s="9"/>
+      <c r="CN5" s="9"/>
+      <c r="CO5" s="9"/>
+      <c r="CP5" s="9"/>
+      <c r="CQ5" s="9"/>
+      <c r="CR5" s="9"/>
+      <c r="CS5" s="9"/>
+      <c r="CT5" s="9"/>
+      <c r="CU5" s="9"/>
+      <c r="CV5" s="9"/>
+      <c r="CW5" s="9"/>
+      <c r="CX5" s="9"/>
+      <c r="CY5" s="9"/>
+      <c r="CZ5" s="9"/>
+      <c r="DA5" s="9"/>
+      <c r="DB5" s="9"/>
+      <c r="DC5" s="9"/>
+      <c r="DD5" s="9"/>
+      <c r="DE5" s="9"/>
+      <c r="DF5" s="9"/>
+      <c r="DG5" s="9"/>
+      <c r="DH5" s="9"/>
+      <c r="DI5" s="9"/>
+      <c r="DJ5" s="9"/>
+      <c r="DK5" s="9"/>
+      <c r="DL5" s="9"/>
+      <c r="DM5" s="9"/>
+      <c r="DN5" s="9"/>
+      <c r="DO5" s="9"/>
+      <c r="DP5" s="9"/>
+      <c r="DQ5" s="9"/>
+      <c r="DR5" s="9"/>
+      <c r="DS5" s="9"/>
+      <c r="DT5" s="9"/>
+      <c r="DU5" s="9"/>
+      <c r="DV5" s="9"/>
+      <c r="DW5" s="9"/>
+      <c r="DX5" s="9"/>
+      <c r="DY5" s="9"/>
+      <c r="DZ5" s="9"/>
+      <c r="EA5" s="9"/>
+      <c r="EB5" s="9"/>
+      <c r="EC5" s="9"/>
+      <c r="ED5" s="9"/>
+      <c r="EE5" s="9"/>
+      <c r="EF5" s="9"/>
+      <c r="EG5" s="9"/>
+      <c r="EH5" s="9"/>
+      <c r="EI5" s="9"/>
+      <c r="EJ5" s="9"/>
+      <c r="EK5" s="9"/>
+      <c r="EL5" s="9"/>
+      <c r="EM5" s="9"/>
+      <c r="EN5" s="9"/>
+      <c r="EO5" s="9"/>
+      <c r="EP5" s="9"/>
+      <c r="EQ5" s="9"/>
+      <c r="ER5" s="9"/>
+      <c r="ES5" s="9"/>
+      <c r="ET5" s="9"/>
+      <c r="EU5" s="9"/>
+      <c r="EV5" s="9"/>
+      <c r="EW5" s="9"/>
+      <c r="EX5" s="9"/>
+      <c r="EY5" s="9"/>
+      <c r="EZ5" s="9"/>
+      <c r="FA5" s="9"/>
+      <c r="FB5" s="9"/>
+      <c r="FC5" s="9"/>
+      <c r="FD5" s="9"/>
+      <c r="FE5" s="9"/>
+      <c r="FF5" s="9"/>
+      <c r="FG5" s="9"/>
+      <c r="FH5" s="9"/>
+      <c r="FI5" s="9"/>
+      <c r="FJ5" s="9"/>
+      <c r="FK5" s="9"/>
+      <c r="FL5" s="9"/>
+      <c r="FM5" s="9"/>
+      <c r="FN5" s="9"/>
+      <c r="FO5" s="9"/>
+      <c r="FP5" s="9"/>
+      <c r="FQ5" s="9"/>
+      <c r="FR5" s="9"/>
+      <c r="FS5" s="9"/>
+      <c r="FT5" s="9"/>
+      <c r="FU5" s="9"/>
+      <c r="FV5" s="9"/>
+      <c r="FW5" s="9"/>
+      <c r="FX5" s="9"/>
+      <c r="FY5" s="9"/>
+      <c r="FZ5" s="9"/>
+      <c r="GA5" s="9"/>
+      <c r="GB5" s="9"/>
+      <c r="GC5" s="9"/>
+      <c r="GD5" s="9"/>
+      <c r="GE5" s="9"/>
+      <c r="GF5" s="9"/>
+      <c r="GG5" s="9"/>
+      <c r="GH5" s="9"/>
+      <c r="GI5" s="9"/>
+      <c r="GJ5" s="9"/>
+      <c r="GK5" s="9"/>
+      <c r="GL5" s="9"/>
+      <c r="GM5" s="9"/>
+      <c r="GN5" s="9"/>
+      <c r="GO5" s="9"/>
+      <c r="GP5" s="9"/>
+      <c r="GQ5" s="9"/>
+      <c r="GR5" s="9"/>
+      <c r="GS5" s="9"/>
+      <c r="GT5" s="9"/>
+      <c r="GU5" s="9"/>
+      <c r="GV5" s="9"/>
+      <c r="GW5" s="9"/>
+      <c r="GX5" s="9"/>
+      <c r="GY5" s="9"/>
+      <c r="GZ5" s="9"/>
+      <c r="HA5" s="9"/>
+      <c r="HB5" s="9"/>
+      <c r="HC5" s="9"/>
+      <c r="HD5" s="9"/>
+      <c r="HE5" s="9"/>
+      <c r="HF5" s="9"/>
+      <c r="HG5" s="9"/>
+      <c r="HH5" s="9"/>
+      <c r="HI5" s="9"/>
+      <c r="HJ5" s="9"/>
+      <c r="HK5" s="9"/>
+      <c r="HL5" s="9"/>
+      <c r="HM5" s="9"/>
+      <c r="HN5" s="9"/>
+      <c r="HO5" s="9"/>
+      <c r="HP5" s="9"/>
+      <c r="HQ5" s="9"/>
+      <c r="HR5" s="9"/>
+      <c r="HS5" s="9"/>
+      <c r="HT5" s="9"/>
+      <c r="HU5" s="9"/>
+      <c r="HV5" s="9"/>
+      <c r="HW5" s="9"/>
+      <c r="HX5" s="9"/>
+      <c r="HY5" s="9"/>
+      <c r="HZ5" s="9"/>
+      <c r="IA5" s="9"/>
+      <c r="IB5" s="9"/>
+      <c r="IC5" s="9"/>
+      <c r="ID5" s="9"/>
+      <c r="IE5" s="9"/>
+      <c r="IF5" s="9"/>
+      <c r="IG5" s="9"/>
+      <c r="IH5" s="9"/>
+      <c r="II5" s="9"/>
+      <c r="IJ5" s="9"/>
+      <c r="IK5" s="9"/>
+      <c r="IL5" s="9"/>
+      <c r="IM5" s="9"/>
+      <c r="IN5" s="9"/>
+      <c r="IO5" s="9"/>
+      <c r="IP5" s="9"/>
+      <c r="IQ5" s="9"/>
+      <c r="IR5" s="9"/>
+      <c r="IS5" s="9"/>
+      <c r="IT5" s="9"/>
+      <c r="IU5" s="10"/>
+    </row>
+    <row r="6" ht="13.65" customHeight="1">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9"/>
+      <c r="AD6" s="9"/>
+      <c r="AE6" s="9"/>
+      <c r="AF6" s="9"/>
+      <c r="AG6" s="9"/>
+      <c r="AH6" s="9"/>
+      <c r="AI6" s="9"/>
+      <c r="AJ6" s="9"/>
+      <c r="AK6" s="9"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+      <c r="BI6" s="9"/>
+      <c r="BJ6" s="9"/>
+      <c r="BK6" s="9"/>
+      <c r="BL6" s="9"/>
+      <c r="BM6" s="9"/>
+      <c r="BN6" s="9"/>
+      <c r="BO6" s="9"/>
+      <c r="BP6" s="9"/>
+      <c r="BQ6" s="9"/>
+      <c r="BR6" s="9"/>
+      <c r="BS6" s="9"/>
+      <c r="BT6" s="9"/>
+      <c r="BU6" s="9"/>
+      <c r="BV6" s="9"/>
+      <c r="BW6" s="9"/>
+      <c r="BX6" s="9"/>
+      <c r="BY6" s="9"/>
+      <c r="BZ6" s="9"/>
+      <c r="CA6" s="9"/>
+      <c r="CB6" s="9"/>
+      <c r="CC6" s="9"/>
+      <c r="CD6" s="9"/>
+      <c r="CE6" s="9"/>
+      <c r="CF6" s="9"/>
+      <c r="CG6" s="9"/>
+      <c r="CH6" s="9"/>
+      <c r="CI6" s="9"/>
+      <c r="CJ6" s="9"/>
+      <c r="CK6" s="9"/>
+      <c r="CL6" s="9"/>
+      <c r="CM6" s="9"/>
+      <c r="CN6" s="9"/>
+      <c r="CO6" s="9"/>
+      <c r="CP6" s="9"/>
+      <c r="CQ6" s="9"/>
+      <c r="CR6" s="9"/>
+      <c r="CS6" s="9"/>
+      <c r="CT6" s="9"/>
+      <c r="CU6" s="9"/>
+      <c r="CV6" s="9"/>
+      <c r="CW6" s="9"/>
+      <c r="CX6" s="9"/>
+      <c r="CY6" s="9"/>
+      <c r="CZ6" s="9"/>
+      <c r="DA6" s="9"/>
+      <c r="DB6" s="9"/>
+      <c r="DC6" s="9"/>
+      <c r="DD6" s="9"/>
+      <c r="DE6" s="9"/>
+      <c r="DF6" s="9"/>
+      <c r="DG6" s="9"/>
+      <c r="DH6" s="9"/>
+      <c r="DI6" s="9"/>
+      <c r="DJ6" s="9"/>
+      <c r="DK6" s="9"/>
+      <c r="DL6" s="9"/>
+      <c r="DM6" s="9"/>
+      <c r="DN6" s="9"/>
+      <c r="DO6" s="9"/>
+      <c r="DP6" s="9"/>
+      <c r="DQ6" s="9"/>
+      <c r="DR6" s="9"/>
+      <c r="DS6" s="9"/>
+      <c r="DT6" s="9"/>
+      <c r="DU6" s="9"/>
+      <c r="DV6" s="9"/>
+      <c r="DW6" s="9"/>
+      <c r="DX6" s="9"/>
+      <c r="DY6" s="9"/>
+      <c r="DZ6" s="9"/>
+      <c r="EA6" s="9"/>
+      <c r="EB6" s="9"/>
+      <c r="EC6" s="9"/>
+      <c r="ED6" s="9"/>
+      <c r="EE6" s="9"/>
+      <c r="EF6" s="9"/>
+      <c r="EG6" s="9"/>
+      <c r="EH6" s="9"/>
+      <c r="EI6" s="9"/>
+      <c r="EJ6" s="9"/>
+      <c r="EK6" s="9"/>
+      <c r="EL6" s="9"/>
+      <c r="EM6" s="9"/>
+      <c r="EN6" s="9"/>
+      <c r="EO6" s="9"/>
+      <c r="EP6" s="9"/>
+      <c r="EQ6" s="9"/>
+      <c r="ER6" s="9"/>
+      <c r="ES6" s="9"/>
+      <c r="ET6" s="9"/>
+      <c r="EU6" s="9"/>
+      <c r="EV6" s="9"/>
+      <c r="EW6" s="9"/>
+      <c r="EX6" s="9"/>
+      <c r="EY6" s="9"/>
+      <c r="EZ6" s="9"/>
+      <c r="FA6" s="9"/>
+      <c r="FB6" s="9"/>
+      <c r="FC6" s="9"/>
+      <c r="FD6" s="9"/>
+      <c r="FE6" s="9"/>
+      <c r="FF6" s="9"/>
+      <c r="FG6" s="9"/>
+      <c r="FH6" s="9"/>
+      <c r="FI6" s="9"/>
+      <c r="FJ6" s="9"/>
+      <c r="FK6" s="9"/>
+      <c r="FL6" s="9"/>
+      <c r="FM6" s="9"/>
+      <c r="FN6" s="9"/>
+      <c r="FO6" s="9"/>
+      <c r="FP6" s="9"/>
+      <c r="FQ6" s="9"/>
+      <c r="FR6" s="9"/>
+      <c r="FS6" s="9"/>
+      <c r="FT6" s="9"/>
+      <c r="FU6" s="9"/>
+      <c r="FV6" s="9"/>
+      <c r="FW6" s="9"/>
+      <c r="FX6" s="9"/>
+      <c r="FY6" s="9"/>
+      <c r="FZ6" s="9"/>
+      <c r="GA6" s="9"/>
+      <c r="GB6" s="9"/>
+      <c r="GC6" s="9"/>
+      <c r="GD6" s="9"/>
+      <c r="GE6" s="9"/>
+      <c r="GF6" s="9"/>
+      <c r="GG6" s="9"/>
+      <c r="GH6" s="9"/>
+      <c r="GI6" s="9"/>
+      <c r="GJ6" s="9"/>
+      <c r="GK6" s="9"/>
+      <c r="GL6" s="9"/>
+      <c r="GM6" s="9"/>
+      <c r="GN6" s="9"/>
+      <c r="GO6" s="9"/>
+      <c r="GP6" s="9"/>
+      <c r="GQ6" s="9"/>
+      <c r="GR6" s="9"/>
+      <c r="GS6" s="9"/>
+      <c r="GT6" s="9"/>
+      <c r="GU6" s="9"/>
+      <c r="GV6" s="9"/>
+      <c r="GW6" s="9"/>
+      <c r="GX6" s="9"/>
+      <c r="GY6" s="9"/>
+      <c r="GZ6" s="9"/>
+      <c r="HA6" s="9"/>
+      <c r="HB6" s="9"/>
+      <c r="HC6" s="9"/>
+      <c r="HD6" s="9"/>
+      <c r="HE6" s="9"/>
+      <c r="HF6" s="9"/>
+      <c r="HG6" s="9"/>
+      <c r="HH6" s="9"/>
+      <c r="HI6" s="9"/>
+      <c r="HJ6" s="9"/>
+      <c r="HK6" s="9"/>
+      <c r="HL6" s="9"/>
+      <c r="HM6" s="9"/>
+      <c r="HN6" s="9"/>
+      <c r="HO6" s="9"/>
+      <c r="HP6" s="9"/>
+      <c r="HQ6" s="9"/>
+      <c r="HR6" s="9"/>
+      <c r="HS6" s="9"/>
+      <c r="HT6" s="9"/>
+      <c r="HU6" s="9"/>
+      <c r="HV6" s="9"/>
+      <c r="HW6" s="9"/>
+      <c r="HX6" s="9"/>
+      <c r="HY6" s="9"/>
+      <c r="HZ6" s="9"/>
+      <c r="IA6" s="9"/>
+      <c r="IB6" s="9"/>
+      <c r="IC6" s="9"/>
+      <c r="ID6" s="9"/>
+      <c r="IE6" s="9"/>
+      <c r="IF6" s="9"/>
+      <c r="IG6" s="9"/>
+      <c r="IH6" s="9"/>
+      <c r="II6" s="9"/>
+      <c r="IJ6" s="9"/>
+      <c r="IK6" s="9"/>
+      <c r="IL6" s="9"/>
+      <c r="IM6" s="9"/>
+      <c r="IN6" s="9"/>
+      <c r="IO6" s="9"/>
+      <c r="IP6" s="9"/>
+      <c r="IQ6" s="9"/>
+      <c r="IR6" s="9"/>
+      <c r="IS6" s="9"/>
+      <c r="IT6" s="9"/>
+      <c r="IU6" s="10"/>
+    </row>
+    <row r="7" ht="13.65" customHeight="1">
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="9"/>
+      <c r="AC7" s="9"/>
+      <c r="AD7" s="9"/>
+      <c r="AE7" s="9"/>
+      <c r="AF7" s="9"/>
+      <c r="AG7" s="9"/>
+      <c r="AH7" s="9"/>
+      <c r="AI7" s="9"/>
+      <c r="AJ7" s="9"/>
+      <c r="AK7" s="9"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+      <c r="BI7" s="9"/>
+      <c r="BJ7" s="9"/>
+      <c r="BK7" s="9"/>
+      <c r="BL7" s="9"/>
+      <c r="BM7" s="9"/>
+      <c r="BN7" s="9"/>
+      <c r="BO7" s="9"/>
+      <c r="BP7" s="9"/>
+      <c r="BQ7" s="9"/>
+      <c r="BR7" s="9"/>
+      <c r="BS7" s="9"/>
+      <c r="BT7" s="9"/>
+      <c r="BU7" s="9"/>
+      <c r="BV7" s="9"/>
+      <c r="BW7" s="9"/>
+      <c r="BX7" s="9"/>
+      <c r="BY7" s="9"/>
+      <c r="BZ7" s="9"/>
+      <c r="CA7" s="9"/>
+      <c r="CB7" s="9"/>
+      <c r="CC7" s="9"/>
+      <c r="CD7" s="9"/>
+      <c r="CE7" s="9"/>
+      <c r="CF7" s="9"/>
+      <c r="CG7" s="9"/>
+      <c r="CH7" s="9"/>
+      <c r="CI7" s="9"/>
+      <c r="CJ7" s="9"/>
+      <c r="CK7" s="9"/>
+      <c r="CL7" s="9"/>
+      <c r="CM7" s="9"/>
+      <c r="CN7" s="9"/>
+      <c r="CO7" s="9"/>
+      <c r="CP7" s="9"/>
+      <c r="CQ7" s="9"/>
+      <c r="CR7" s="9"/>
+      <c r="CS7" s="9"/>
+      <c r="CT7" s="9"/>
+      <c r="CU7" s="9"/>
+      <c r="CV7" s="9"/>
+      <c r="CW7" s="9"/>
+      <c r="CX7" s="9"/>
+      <c r="CY7" s="9"/>
+      <c r="CZ7" s="9"/>
+      <c r="DA7" s="9"/>
+      <c r="DB7" s="9"/>
+      <c r="DC7" s="9"/>
+      <c r="DD7" s="9"/>
+      <c r="DE7" s="9"/>
+      <c r="DF7" s="9"/>
+      <c r="DG7" s="9"/>
+      <c r="DH7" s="9"/>
+      <c r="DI7" s="9"/>
+      <c r="DJ7" s="9"/>
+      <c r="DK7" s="9"/>
+      <c r="DL7" s="9"/>
+      <c r="DM7" s="9"/>
+      <c r="DN7" s="9"/>
+      <c r="DO7" s="9"/>
+      <c r="DP7" s="9"/>
+      <c r="DQ7" s="9"/>
+      <c r="DR7" s="9"/>
+      <c r="DS7" s="9"/>
+      <c r="DT7" s="9"/>
+      <c r="DU7" s="9"/>
+      <c r="DV7" s="9"/>
+      <c r="DW7" s="9"/>
+      <c r="DX7" s="9"/>
+      <c r="DY7" s="9"/>
+      <c r="DZ7" s="9"/>
+      <c r="EA7" s="9"/>
+      <c r="EB7" s="9"/>
+      <c r="EC7" s="9"/>
+      <c r="ED7" s="9"/>
+      <c r="EE7" s="9"/>
+      <c r="EF7" s="9"/>
+      <c r="EG7" s="9"/>
+      <c r="EH7" s="9"/>
+      <c r="EI7" s="9"/>
+      <c r="EJ7" s="9"/>
+      <c r="EK7" s="9"/>
+      <c r="EL7" s="9"/>
+      <c r="EM7" s="9"/>
+      <c r="EN7" s="9"/>
+      <c r="EO7" s="9"/>
+      <c r="EP7" s="9"/>
+      <c r="EQ7" s="9"/>
+      <c r="ER7" s="9"/>
+      <c r="ES7" s="9"/>
+      <c r="ET7" s="9"/>
+      <c r="EU7" s="9"/>
+      <c r="EV7" s="9"/>
+      <c r="EW7" s="9"/>
+      <c r="EX7" s="9"/>
+      <c r="EY7" s="9"/>
+      <c r="EZ7" s="9"/>
+      <c r="FA7" s="9"/>
+      <c r="FB7" s="9"/>
+      <c r="FC7" s="9"/>
+      <c r="FD7" s="9"/>
+      <c r="FE7" s="9"/>
+      <c r="FF7" s="9"/>
+      <c r="FG7" s="9"/>
+      <c r="FH7" s="9"/>
+      <c r="FI7" s="9"/>
+      <c r="FJ7" s="9"/>
+      <c r="FK7" s="9"/>
+      <c r="FL7" s="9"/>
+      <c r="FM7" s="9"/>
+      <c r="FN7" s="9"/>
+      <c r="FO7" s="9"/>
+      <c r="FP7" s="9"/>
+      <c r="FQ7" s="9"/>
+      <c r="FR7" s="9"/>
+      <c r="FS7" s="9"/>
+      <c r="FT7" s="9"/>
+      <c r="FU7" s="9"/>
+      <c r="FV7" s="9"/>
+      <c r="FW7" s="9"/>
+      <c r="FX7" s="9"/>
+      <c r="FY7" s="9"/>
+      <c r="FZ7" s="9"/>
+      <c r="GA7" s="9"/>
+      <c r="GB7" s="9"/>
+      <c r="GC7" s="9"/>
+      <c r="GD7" s="9"/>
+      <c r="GE7" s="9"/>
+      <c r="GF7" s="9"/>
+      <c r="GG7" s="9"/>
+      <c r="GH7" s="9"/>
+      <c r="GI7" s="9"/>
+      <c r="GJ7" s="9"/>
+      <c r="GK7" s="9"/>
+      <c r="GL7" s="9"/>
+      <c r="GM7" s="9"/>
+      <c r="GN7" s="9"/>
+      <c r="GO7" s="9"/>
+      <c r="GP7" s="9"/>
+      <c r="GQ7" s="9"/>
+      <c r="GR7" s="9"/>
+      <c r="GS7" s="9"/>
+      <c r="GT7" s="9"/>
+      <c r="GU7" s="9"/>
+      <c r="GV7" s="9"/>
+      <c r="GW7" s="9"/>
+      <c r="GX7" s="9"/>
+      <c r="GY7" s="9"/>
+      <c r="GZ7" s="9"/>
+      <c r="HA7" s="9"/>
+      <c r="HB7" s="9"/>
+      <c r="HC7" s="9"/>
+      <c r="HD7" s="9"/>
+      <c r="HE7" s="9"/>
+      <c r="HF7" s="9"/>
+      <c r="HG7" s="9"/>
+      <c r="HH7" s="9"/>
+      <c r="HI7" s="9"/>
+      <c r="HJ7" s="9"/>
+      <c r="HK7" s="9"/>
+      <c r="HL7" s="9"/>
+      <c r="HM7" s="9"/>
+      <c r="HN7" s="9"/>
+      <c r="HO7" s="9"/>
+      <c r="HP7" s="9"/>
+      <c r="HQ7" s="9"/>
+      <c r="HR7" s="9"/>
+      <c r="HS7" s="9"/>
+      <c r="HT7" s="9"/>
+      <c r="HU7" s="9"/>
+      <c r="HV7" s="9"/>
+      <c r="HW7" s="9"/>
+      <c r="HX7" s="9"/>
+      <c r="HY7" s="9"/>
+      <c r="HZ7" s="9"/>
+      <c r="IA7" s="9"/>
+      <c r="IB7" s="9"/>
+      <c r="IC7" s="9"/>
+      <c r="ID7" s="9"/>
+      <c r="IE7" s="9"/>
+      <c r="IF7" s="9"/>
+      <c r="IG7" s="9"/>
+      <c r="IH7" s="9"/>
+      <c r="II7" s="9"/>
+      <c r="IJ7" s="9"/>
+      <c r="IK7" s="9"/>
+      <c r="IL7" s="9"/>
+      <c r="IM7" s="9"/>
+      <c r="IN7" s="9"/>
+      <c r="IO7" s="9"/>
+      <c r="IP7" s="9"/>
+      <c r="IQ7" s="9"/>
+      <c r="IR7" s="9"/>
+      <c r="IS7" s="9"/>
+      <c r="IT7" s="9"/>
+      <c r="IU7" s="10"/>
+    </row>
+    <row r="8" ht="13.65" customHeight="1">
+      <c r="A8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="9"/>
+      <c r="AF8" s="9"/>
+      <c r="AG8" s="9"/>
+      <c r="AH8" s="9"/>
+      <c r="AI8" s="9"/>
+      <c r="AJ8" s="9"/>
+      <c r="AK8" s="9"/>
+      <c r="AL8" s="9"/>
+      <c r="AM8" s="9"/>
+      <c r="AN8" s="9"/>
+      <c r="AO8" s="9"/>
+      <c r="AP8" s="9"/>
+      <c r="AQ8" s="9"/>
+      <c r="AR8" s="9"/>
+      <c r="AS8" s="9"/>
+      <c r="AT8" s="9"/>
+      <c r="AU8" s="9"/>
+      <c r="AV8" s="9"/>
+      <c r="AW8" s="9"/>
+      <c r="AX8" s="9"/>
+      <c r="AY8" s="9"/>
+      <c r="AZ8" s="9"/>
+      <c r="BA8" s="9"/>
+      <c r="BB8" s="9"/>
+      <c r="BC8" s="9"/>
+      <c r="BD8" s="9"/>
+      <c r="BE8" s="9"/>
+      <c r="BF8" s="9"/>
+      <c r="BG8" s="9"/>
+      <c r="BH8" s="9"/>
+      <c r="BI8" s="9"/>
+      <c r="BJ8" s="9"/>
+      <c r="BK8" s="9"/>
+      <c r="BL8" s="9"/>
+      <c r="BM8" s="9"/>
+      <c r="BN8" s="9"/>
+      <c r="BO8" s="9"/>
+      <c r="BP8" s="9"/>
+      <c r="BQ8" s="9"/>
+      <c r="BR8" s="9"/>
+      <c r="BS8" s="9"/>
+      <c r="BT8" s="9"/>
+      <c r="BU8" s="9"/>
+      <c r="BV8" s="9"/>
+      <c r="BW8" s="9"/>
+      <c r="BX8" s="9"/>
+      <c r="BY8" s="9"/>
+      <c r="BZ8" s="9"/>
+      <c r="CA8" s="9"/>
+      <c r="CB8" s="9"/>
+      <c r="CC8" s="9"/>
+      <c r="CD8" s="9"/>
+      <c r="CE8" s="9"/>
+      <c r="CF8" s="9"/>
+      <c r="CG8" s="9"/>
+      <c r="CH8" s="9"/>
+      <c r="CI8" s="9"/>
+      <c r="CJ8" s="9"/>
+      <c r="CK8" s="9"/>
+      <c r="CL8" s="9"/>
+      <c r="CM8" s="9"/>
+      <c r="CN8" s="9"/>
+      <c r="CO8" s="9"/>
+      <c r="CP8" s="9"/>
+      <c r="CQ8" s="9"/>
+      <c r="CR8" s="9"/>
+      <c r="CS8" s="9"/>
+      <c r="CT8" s="9"/>
+      <c r="CU8" s="9"/>
+      <c r="CV8" s="9"/>
+      <c r="CW8" s="9"/>
+      <c r="CX8" s="9"/>
+      <c r="CY8" s="9"/>
+      <c r="CZ8" s="9"/>
+      <c r="DA8" s="9"/>
+      <c r="DB8" s="9"/>
+      <c r="DC8" s="9"/>
+      <c r="DD8" s="9"/>
+      <c r="DE8" s="9"/>
+      <c r="DF8" s="9"/>
+      <c r="DG8" s="9"/>
+      <c r="DH8" s="9"/>
+      <c r="DI8" s="9"/>
+      <c r="DJ8" s="9"/>
+      <c r="DK8" s="9"/>
+      <c r="DL8" s="9"/>
+      <c r="DM8" s="9"/>
+      <c r="DN8" s="9"/>
+      <c r="DO8" s="9"/>
+      <c r="DP8" s="9"/>
+      <c r="DQ8" s="9"/>
+      <c r="DR8" s="9"/>
+      <c r="DS8" s="9"/>
+      <c r="DT8" s="9"/>
+      <c r="DU8" s="9"/>
+      <c r="DV8" s="9"/>
+      <c r="DW8" s="9"/>
+      <c r="DX8" s="9"/>
+      <c r="DY8" s="9"/>
+      <c r="DZ8" s="9"/>
+      <c r="EA8" s="9"/>
+      <c r="EB8" s="9"/>
+      <c r="EC8" s="9"/>
+      <c r="ED8" s="9"/>
+      <c r="EE8" s="9"/>
+      <c r="EF8" s="9"/>
+      <c r="EG8" s="9"/>
+      <c r="EH8" s="9"/>
+      <c r="EI8" s="9"/>
+      <c r="EJ8" s="9"/>
+      <c r="EK8" s="9"/>
+      <c r="EL8" s="9"/>
+      <c r="EM8" s="9"/>
+      <c r="EN8" s="9"/>
+      <c r="EO8" s="9"/>
+      <c r="EP8" s="9"/>
+      <c r="EQ8" s="9"/>
+      <c r="ER8" s="9"/>
+      <c r="ES8" s="9"/>
+      <c r="ET8" s="9"/>
+      <c r="EU8" s="9"/>
+      <c r="EV8" s="9"/>
+      <c r="EW8" s="9"/>
+      <c r="EX8" s="9"/>
+      <c r="EY8" s="9"/>
+      <c r="EZ8" s="9"/>
+      <c r="FA8" s="9"/>
+      <c r="FB8" s="9"/>
+      <c r="FC8" s="9"/>
+      <c r="FD8" s="9"/>
+      <c r="FE8" s="9"/>
+      <c r="FF8" s="9"/>
+      <c r="FG8" s="9"/>
+      <c r="FH8" s="9"/>
+      <c r="FI8" s="9"/>
+      <c r="FJ8" s="9"/>
+      <c r="FK8" s="9"/>
+      <c r="FL8" s="9"/>
+      <c r="FM8" s="9"/>
+      <c r="FN8" s="9"/>
+      <c r="FO8" s="9"/>
+      <c r="FP8" s="9"/>
+      <c r="FQ8" s="9"/>
+      <c r="FR8" s="9"/>
+      <c r="FS8" s="9"/>
+      <c r="FT8" s="9"/>
+      <c r="FU8" s="9"/>
+      <c r="FV8" s="9"/>
+      <c r="FW8" s="9"/>
+      <c r="FX8" s="9"/>
+      <c r="FY8" s="9"/>
+      <c r="FZ8" s="9"/>
+      <c r="GA8" s="9"/>
+      <c r="GB8" s="9"/>
+      <c r="GC8" s="9"/>
+      <c r="GD8" s="9"/>
+      <c r="GE8" s="9"/>
+      <c r="GF8" s="9"/>
+      <c r="GG8" s="9"/>
+      <c r="GH8" s="9"/>
+      <c r="GI8" s="9"/>
+      <c r="GJ8" s="9"/>
+      <c r="GK8" s="9"/>
+      <c r="GL8" s="9"/>
+      <c r="GM8" s="9"/>
+      <c r="GN8" s="9"/>
+      <c r="GO8" s="9"/>
+      <c r="GP8" s="9"/>
+      <c r="GQ8" s="9"/>
+      <c r="GR8" s="9"/>
+      <c r="GS8" s="9"/>
+      <c r="GT8" s="9"/>
+      <c r="GU8" s="9"/>
+      <c r="GV8" s="9"/>
+      <c r="GW8" s="9"/>
+      <c r="GX8" s="9"/>
+      <c r="GY8" s="9"/>
+      <c r="GZ8" s="9"/>
+      <c r="HA8" s="9"/>
+      <c r="HB8" s="9"/>
+      <c r="HC8" s="9"/>
+      <c r="HD8" s="9"/>
+      <c r="HE8" s="9"/>
+      <c r="HF8" s="9"/>
+      <c r="HG8" s="9"/>
+      <c r="HH8" s="9"/>
+      <c r="HI8" s="9"/>
+      <c r="HJ8" s="9"/>
+      <c r="HK8" s="9"/>
+      <c r="HL8" s="9"/>
+      <c r="HM8" s="9"/>
+      <c r="HN8" s="9"/>
+      <c r="HO8" s="9"/>
+      <c r="HP8" s="9"/>
+      <c r="HQ8" s="9"/>
+      <c r="HR8" s="9"/>
+      <c r="HS8" s="9"/>
+      <c r="HT8" s="9"/>
+      <c r="HU8" s="9"/>
+      <c r="HV8" s="9"/>
+      <c r="HW8" s="9"/>
+      <c r="HX8" s="9"/>
+      <c r="HY8" s="9"/>
+      <c r="HZ8" s="9"/>
+      <c r="IA8" s="9"/>
+      <c r="IB8" s="9"/>
+      <c r="IC8" s="9"/>
+      <c r="ID8" s="9"/>
+      <c r="IE8" s="9"/>
+      <c r="IF8" s="9"/>
+      <c r="IG8" s="9"/>
+      <c r="IH8" s="9"/>
+      <c r="II8" s="9"/>
+      <c r="IJ8" s="9"/>
+      <c r="IK8" s="9"/>
+      <c r="IL8" s="9"/>
+      <c r="IM8" s="9"/>
+      <c r="IN8" s="9"/>
+      <c r="IO8" s="9"/>
+      <c r="IP8" s="9"/>
+      <c r="IQ8" s="9"/>
+      <c r="IR8" s="9"/>
+      <c r="IS8" s="9"/>
+      <c r="IT8" s="9"/>
+      <c r="IU8" s="10"/>
+    </row>
+    <row r="9" ht="13.65" customHeight="1">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="9"/>
+      <c r="AB9" s="9"/>
+      <c r="AC9" s="9"/>
+      <c r="AD9" s="9"/>
+      <c r="AE9" s="9"/>
+      <c r="AF9" s="9"/>
+      <c r="AG9" s="9"/>
+      <c r="AH9" s="9"/>
+      <c r="AI9" s="9"/>
+      <c r="AJ9" s="9"/>
+      <c r="AK9" s="9"/>
+      <c r="AL9" s="9"/>
+      <c r="AM9" s="9"/>
+      <c r="AN9" s="9"/>
+      <c r="AO9" s="9"/>
+      <c r="AP9" s="9"/>
+      <c r="AQ9" s="9"/>
+      <c r="AR9" s="9"/>
+      <c r="AS9" s="9"/>
+      <c r="AT9" s="9"/>
+      <c r="AU9" s="9"/>
+      <c r="AV9" s="9"/>
+      <c r="AW9" s="9"/>
+      <c r="AX9" s="9"/>
+      <c r="AY9" s="9"/>
+      <c r="AZ9" s="9"/>
+      <c r="BA9" s="9"/>
+      <c r="BB9" s="9"/>
+      <c r="BC9" s="9"/>
+      <c r="BD9" s="9"/>
+      <c r="BE9" s="9"/>
+      <c r="BF9" s="9"/>
+      <c r="BG9" s="9"/>
+      <c r="BH9" s="9"/>
+      <c r="BI9" s="9"/>
+      <c r="BJ9" s="9"/>
+      <c r="BK9" s="9"/>
+      <c r="BL9" s="9"/>
+      <c r="BM9" s="9"/>
+      <c r="BN9" s="9"/>
+      <c r="BO9" s="9"/>
+      <c r="BP9" s="9"/>
+      <c r="BQ9" s="9"/>
+      <c r="BR9" s="9"/>
+      <c r="BS9" s="9"/>
+      <c r="BT9" s="9"/>
+      <c r="BU9" s="9"/>
+      <c r="BV9" s="9"/>
+      <c r="BW9" s="9"/>
+      <c r="BX9" s="9"/>
+      <c r="BY9" s="9"/>
+      <c r="BZ9" s="9"/>
+      <c r="CA9" s="9"/>
+      <c r="CB9" s="9"/>
+      <c r="CC9" s="9"/>
+      <c r="CD9" s="9"/>
+      <c r="CE9" s="9"/>
+      <c r="CF9" s="9"/>
+      <c r="CG9" s="9"/>
+      <c r="CH9" s="9"/>
+      <c r="CI9" s="9"/>
+      <c r="CJ9" s="9"/>
+      <c r="CK9" s="9"/>
+      <c r="CL9" s="9"/>
+      <c r="CM9" s="9"/>
+      <c r="CN9" s="9"/>
+      <c r="CO9" s="9"/>
+      <c r="CP9" s="9"/>
+      <c r="CQ9" s="9"/>
+      <c r="CR9" s="9"/>
+      <c r="CS9" s="9"/>
+      <c r="CT9" s="9"/>
+      <c r="CU9" s="9"/>
+      <c r="CV9" s="9"/>
+      <c r="CW9" s="9"/>
+      <c r="CX9" s="9"/>
+      <c r="CY9" s="9"/>
+      <c r="CZ9" s="9"/>
+      <c r="DA9" s="9"/>
+      <c r="DB9" s="9"/>
+      <c r="DC9" s="9"/>
+      <c r="DD9" s="9"/>
+      <c r="DE9" s="9"/>
+      <c r="DF9" s="9"/>
+      <c r="DG9" s="9"/>
+      <c r="DH9" s="9"/>
+      <c r="DI9" s="9"/>
+      <c r="DJ9" s="9"/>
+      <c r="DK9" s="9"/>
+      <c r="DL9" s="9"/>
+      <c r="DM9" s="9"/>
+      <c r="DN9" s="9"/>
+      <c r="DO9" s="9"/>
+      <c r="DP9" s="9"/>
+      <c r="DQ9" s="9"/>
+      <c r="DR9" s="9"/>
+      <c r="DS9" s="9"/>
+      <c r="DT9" s="9"/>
+      <c r="DU9" s="9"/>
+      <c r="DV9" s="9"/>
+      <c r="DW9" s="9"/>
+      <c r="DX9" s="9"/>
+      <c r="DY9" s="9"/>
+      <c r="DZ9" s="9"/>
+      <c r="EA9" s="9"/>
+      <c r="EB9" s="9"/>
+      <c r="EC9" s="9"/>
+      <c r="ED9" s="9"/>
+      <c r="EE9" s="9"/>
+      <c r="EF9" s="9"/>
+      <c r="EG9" s="9"/>
+      <c r="EH9" s="9"/>
+      <c r="EI9" s="9"/>
+      <c r="EJ9" s="9"/>
+      <c r="EK9" s="9"/>
+      <c r="EL9" s="9"/>
+      <c r="EM9" s="9"/>
+      <c r="EN9" s="9"/>
+      <c r="EO9" s="9"/>
+      <c r="EP9" s="9"/>
+      <c r="EQ9" s="9"/>
+      <c r="ER9" s="9"/>
+      <c r="ES9" s="9"/>
+      <c r="ET9" s="9"/>
+      <c r="EU9" s="9"/>
+      <c r="EV9" s="9"/>
+      <c r="EW9" s="9"/>
+      <c r="EX9" s="9"/>
+      <c r="EY9" s="9"/>
+      <c r="EZ9" s="9"/>
+      <c r="FA9" s="9"/>
+      <c r="FB9" s="9"/>
+      <c r="FC9" s="9"/>
+      <c r="FD9" s="9"/>
+      <c r="FE9" s="9"/>
+      <c r="FF9" s="9"/>
+      <c r="FG9" s="9"/>
+      <c r="FH9" s="9"/>
+      <c r="FI9" s="9"/>
+      <c r="FJ9" s="9"/>
+      <c r="FK9" s="9"/>
+      <c r="FL9" s="9"/>
+      <c r="FM9" s="9"/>
+      <c r="FN9" s="9"/>
+      <c r="FO9" s="9"/>
+      <c r="FP9" s="9"/>
+      <c r="FQ9" s="9"/>
+      <c r="FR9" s="9"/>
+      <c r="FS9" s="9"/>
+      <c r="FT9" s="9"/>
+      <c r="FU9" s="9"/>
+      <c r="FV9" s="9"/>
+      <c r="FW9" s="9"/>
+      <c r="FX9" s="9"/>
+      <c r="FY9" s="9"/>
+      <c r="FZ9" s="9"/>
+      <c r="GA9" s="9"/>
+      <c r="GB9" s="9"/>
+      <c r="GC9" s="9"/>
+      <c r="GD9" s="9"/>
+      <c r="GE9" s="9"/>
+      <c r="GF9" s="9"/>
+      <c r="GG9" s="9"/>
+      <c r="GH9" s="9"/>
+      <c r="GI9" s="9"/>
+      <c r="GJ9" s="9"/>
+      <c r="GK9" s="9"/>
+      <c r="GL9" s="9"/>
+      <c r="GM9" s="9"/>
+      <c r="GN9" s="9"/>
+      <c r="GO9" s="9"/>
+      <c r="GP9" s="9"/>
+      <c r="GQ9" s="9"/>
+      <c r="GR9" s="9"/>
+      <c r="GS9" s="9"/>
+      <c r="GT9" s="9"/>
+      <c r="GU9" s="9"/>
+      <c r="GV9" s="9"/>
+      <c r="GW9" s="9"/>
+      <c r="GX9" s="9"/>
+      <c r="GY9" s="9"/>
+      <c r="GZ9" s="9"/>
+      <c r="HA9" s="9"/>
+      <c r="HB9" s="9"/>
+      <c r="HC9" s="9"/>
+      <c r="HD9" s="9"/>
+      <c r="HE9" s="9"/>
+      <c r="HF9" s="9"/>
+      <c r="HG9" s="9"/>
+      <c r="HH9" s="9"/>
+      <c r="HI9" s="9"/>
+      <c r="HJ9" s="9"/>
+      <c r="HK9" s="9"/>
+      <c r="HL9" s="9"/>
+      <c r="HM9" s="9"/>
+      <c r="HN9" s="9"/>
+      <c r="HO9" s="9"/>
+      <c r="HP9" s="9"/>
+      <c r="HQ9" s="9"/>
+      <c r="HR9" s="9"/>
+      <c r="HS9" s="9"/>
+      <c r="HT9" s="9"/>
+      <c r="HU9" s="9"/>
+      <c r="HV9" s="9"/>
+      <c r="HW9" s="9"/>
+      <c r="HX9" s="9"/>
+      <c r="HY9" s="9"/>
+      <c r="HZ9" s="9"/>
+      <c r="IA9" s="9"/>
+      <c r="IB9" s="9"/>
+      <c r="IC9" s="9"/>
+      <c r="ID9" s="9"/>
+      <c r="IE9" s="9"/>
+      <c r="IF9" s="9"/>
+      <c r="IG9" s="9"/>
+      <c r="IH9" s="9"/>
+      <c r="II9" s="9"/>
+      <c r="IJ9" s="9"/>
+      <c r="IK9" s="9"/>
+      <c r="IL9" s="9"/>
+      <c r="IM9" s="9"/>
+      <c r="IN9" s="9"/>
+      <c r="IO9" s="9"/>
+      <c r="IP9" s="9"/>
+      <c r="IQ9" s="9"/>
+      <c r="IR9" s="9"/>
+      <c r="IS9" s="9"/>
+      <c r="IT9" s="9"/>
+      <c r="IU9" s="10"/>
+    </row>
+    <row r="10" ht="13.65" customHeight="1">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="12"/>
+      <c r="V10" s="12"/>
+      <c r="W10" s="12"/>
+      <c r="X10" s="12"/>
+      <c r="Y10" s="12"/>
+      <c r="Z10" s="12"/>
+      <c r="AA10" s="12"/>
+      <c r="AB10" s="12"/>
+      <c r="AC10" s="12"/>
+      <c r="AD10" s="12"/>
+      <c r="AE10" s="12"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+      <c r="BI10" s="12"/>
+      <c r="BJ10" s="12"/>
+      <c r="BK10" s="12"/>
+      <c r="BL10" s="12"/>
+      <c r="BM10" s="12"/>
+      <c r="BN10" s="12"/>
+      <c r="BO10" s="12"/>
+      <c r="BP10" s="12"/>
+      <c r="BQ10" s="12"/>
+      <c r="BR10" s="12"/>
+      <c r="BS10" s="12"/>
+      <c r="BT10" s="12"/>
+      <c r="BU10" s="12"/>
+      <c r="BV10" s="12"/>
+      <c r="BW10" s="12"/>
+      <c r="BX10" s="12"/>
+      <c r="BY10" s="12"/>
+      <c r="BZ10" s="12"/>
+      <c r="CA10" s="12"/>
+      <c r="CB10" s="12"/>
+      <c r="CC10" s="12"/>
+      <c r="CD10" s="12"/>
+      <c r="CE10" s="12"/>
+      <c r="CF10" s="12"/>
+      <c r="CG10" s="12"/>
+      <c r="CH10" s="12"/>
+      <c r="CI10" s="12"/>
+      <c r="CJ10" s="12"/>
+      <c r="CK10" s="12"/>
+      <c r="CL10" s="12"/>
+      <c r="CM10" s="12"/>
+      <c r="CN10" s="12"/>
+      <c r="CO10" s="12"/>
+      <c r="CP10" s="12"/>
+      <c r="CQ10" s="12"/>
+      <c r="CR10" s="12"/>
+      <c r="CS10" s="12"/>
+      <c r="CT10" s="12"/>
+      <c r="CU10" s="12"/>
+      <c r="CV10" s="12"/>
+      <c r="CW10" s="12"/>
+      <c r="CX10" s="12"/>
+      <c r="CY10" s="12"/>
+      <c r="CZ10" s="12"/>
+      <c r="DA10" s="12"/>
+      <c r="DB10" s="12"/>
+      <c r="DC10" s="12"/>
+      <c r="DD10" s="12"/>
+      <c r="DE10" s="12"/>
+      <c r="DF10" s="12"/>
+      <c r="DG10" s="12"/>
+      <c r="DH10" s="12"/>
+      <c r="DI10" s="12"/>
+      <c r="DJ10" s="12"/>
+      <c r="DK10" s="12"/>
+      <c r="DL10" s="12"/>
+      <c r="DM10" s="12"/>
+      <c r="DN10" s="12"/>
+      <c r="DO10" s="12"/>
+      <c r="DP10" s="12"/>
+      <c r="DQ10" s="12"/>
+      <c r="DR10" s="12"/>
+      <c r="DS10" s="12"/>
+      <c r="DT10" s="12"/>
+      <c r="DU10" s="12"/>
+      <c r="DV10" s="12"/>
+      <c r="DW10" s="12"/>
+      <c r="DX10" s="12"/>
+      <c r="DY10" s="12"/>
+      <c r="DZ10" s="12"/>
+      <c r="EA10" s="12"/>
+      <c r="EB10" s="12"/>
+      <c r="EC10" s="12"/>
+      <c r="ED10" s="12"/>
+      <c r="EE10" s="12"/>
+      <c r="EF10" s="12"/>
+      <c r="EG10" s="12"/>
+      <c r="EH10" s="12"/>
+      <c r="EI10" s="12"/>
+      <c r="EJ10" s="12"/>
+      <c r="EK10" s="12"/>
+      <c r="EL10" s="12"/>
+      <c r="EM10" s="12"/>
+      <c r="EN10" s="12"/>
+      <c r="EO10" s="12"/>
+      <c r="EP10" s="12"/>
+      <c r="EQ10" s="12"/>
+      <c r="ER10" s="12"/>
+      <c r="ES10" s="12"/>
+      <c r="ET10" s="12"/>
+      <c r="EU10" s="12"/>
+      <c r="EV10" s="12"/>
+      <c r="EW10" s="12"/>
+      <c r="EX10" s="12"/>
+      <c r="EY10" s="12"/>
+      <c r="EZ10" s="12"/>
+      <c r="FA10" s="12"/>
+      <c r="FB10" s="12"/>
+      <c r="FC10" s="12"/>
+      <c r="FD10" s="12"/>
+      <c r="FE10" s="12"/>
+      <c r="FF10" s="12"/>
+      <c r="FG10" s="12"/>
+      <c r="FH10" s="12"/>
+      <c r="FI10" s="12"/>
+      <c r="FJ10" s="12"/>
+      <c r="FK10" s="12"/>
+      <c r="FL10" s="12"/>
+      <c r="FM10" s="12"/>
+      <c r="FN10" s="12"/>
+      <c r="FO10" s="12"/>
+      <c r="FP10" s="12"/>
+      <c r="FQ10" s="12"/>
+      <c r="FR10" s="12"/>
+      <c r="FS10" s="12"/>
+      <c r="FT10" s="12"/>
+      <c r="FU10" s="12"/>
+      <c r="FV10" s="12"/>
+      <c r="FW10" s="12"/>
+      <c r="FX10" s="12"/>
+      <c r="FY10" s="12"/>
+      <c r="FZ10" s="12"/>
+      <c r="GA10" s="12"/>
+      <c r="GB10" s="12"/>
+      <c r="GC10" s="12"/>
+      <c r="GD10" s="12"/>
+      <c r="GE10" s="12"/>
+      <c r="GF10" s="12"/>
+      <c r="GG10" s="12"/>
+      <c r="GH10" s="12"/>
+      <c r="GI10" s="12"/>
+      <c r="GJ10" s="12"/>
+      <c r="GK10" s="12"/>
+      <c r="GL10" s="12"/>
+      <c r="GM10" s="12"/>
+      <c r="GN10" s="12"/>
+      <c r="GO10" s="12"/>
+      <c r="GP10" s="12"/>
+      <c r="GQ10" s="12"/>
+      <c r="GR10" s="12"/>
+      <c r="GS10" s="12"/>
+      <c r="GT10" s="12"/>
+      <c r="GU10" s="12"/>
+      <c r="GV10" s="12"/>
+      <c r="GW10" s="12"/>
+      <c r="GX10" s="12"/>
+      <c r="GY10" s="12"/>
+      <c r="GZ10" s="12"/>
+      <c r="HA10" s="12"/>
+      <c r="HB10" s="12"/>
+      <c r="HC10" s="12"/>
+      <c r="HD10" s="12"/>
+      <c r="HE10" s="12"/>
+      <c r="HF10" s="12"/>
+      <c r="HG10" s="12"/>
+      <c r="HH10" s="12"/>
+      <c r="HI10" s="12"/>
+      <c r="HJ10" s="12"/>
+      <c r="HK10" s="12"/>
+      <c r="HL10" s="12"/>
+      <c r="HM10" s="12"/>
+      <c r="HN10" s="12"/>
+      <c r="HO10" s="12"/>
+      <c r="HP10" s="12"/>
+      <c r="HQ10" s="12"/>
+      <c r="HR10" s="12"/>
+      <c r="HS10" s="12"/>
+      <c r="HT10" s="12"/>
+      <c r="HU10" s="12"/>
+      <c r="HV10" s="12"/>
+      <c r="HW10" s="12"/>
+      <c r="HX10" s="12"/>
+      <c r="HY10" s="12"/>
+      <c r="HZ10" s="12"/>
+      <c r="IA10" s="12"/>
+      <c r="IB10" s="12"/>
+      <c r="IC10" s="12"/>
+      <c r="ID10" s="12"/>
+      <c r="IE10" s="12"/>
+      <c r="IF10" s="12"/>
+      <c r="IG10" s="12"/>
+      <c r="IH10" s="12"/>
+      <c r="II10" s="12"/>
+      <c r="IJ10" s="12"/>
+      <c r="IK10" s="12"/>
+      <c r="IL10" s="12"/>
+      <c r="IM10" s="12"/>
+      <c r="IN10" s="12"/>
+      <c r="IO10" s="12"/>
+      <c r="IP10" s="12"/>
+      <c r="IQ10" s="12"/>
+      <c r="IR10" s="12"/>
+      <c r="IS10" s="12"/>
+      <c r="IT10" s="12"/>
+      <c r="IU10" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1340,4 +4302,219 @@
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="108.672" style="14" customWidth="1"/>
+    <col min="2" max="5" width="8.85156" style="14" customWidth="1"/>
+    <col min="6" max="256" width="8.85156" style="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="13.65" customHeight="1">
+      <c r="A1" t="s" s="15">
+        <v>27</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+    </row>
+    <row r="2" ht="13.65" customHeight="1">
+      <c r="A2" s="18"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" t="s" s="19">
+        <v>28</v>
+      </c>
+      <c r="B3" s="20"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" t="s" s="19">
+        <v>29</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" t="s" s="19">
+        <v>30</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" t="s" s="19">
+        <v>31</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" t="s" s="19">
+        <v>32</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" t="s" s="19">
+        <v>33</v>
+      </c>
+      <c r="B8" s="20"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" t="s" s="19">
+        <v>34</v>
+      </c>
+      <c r="B9" s="20"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="21"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+    </row>
+    <row r="11" ht="13.65" customHeight="1">
+      <c r="A11" t="s" s="22">
+        <v>35</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+    </row>
+    <row r="12" ht="12" customHeight="1">
+      <c r="A12" s="18"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" t="s" s="19">
+        <v>36</v>
+      </c>
+      <c r="B13" s="24"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" t="s" s="19">
+        <v>37</v>
+      </c>
+      <c r="B14" s="24"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" t="s" s="19">
+        <v>38</v>
+      </c>
+      <c r="B15" s="24"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" t="s" s="19">
+        <v>39</v>
+      </c>
+      <c r="B16" s="24"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" t="s" s="19">
+        <v>40</v>
+      </c>
+      <c r="B17" s="24"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" t="s" s="19">
+        <v>41</v>
+      </c>
+      <c r="B18" s="24"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" t="s" s="19">
+        <v>42</v>
+      </c>
+      <c r="B19" s="24"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" t="s" s="19">
+        <v>43</v>
+      </c>
+      <c r="B20" s="24"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" t="s" s="19">
+        <v>44</v>
+      </c>
+      <c r="B21" s="24"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+    </row>
+    <row r="22" ht="13.5" customHeight="1">
+      <c r="A22" t="s" s="19">
+        <v>45</v>
+      </c>
+      <c r="B22" s="20"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A11:A12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
@@ -1,27 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="19126"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212706711\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{7CB5382B-A6B2-4318-9A63-89F662AD6F7D}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
   </bookViews>
   <sheets>
-    <sheet name="datalist" sheetId="1" r:id="rId1"/>
-    <sheet name="填写说明" sheetId="2" r:id="rId2"/>
+    <sheet name="datalist" sheetId="1" r:id="rId4"/>
+    <sheet name="填写说明" sheetId="2" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
   <si>
     <t>所属集团</t>
   </si>
@@ -76,7 +67,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>新增医院</t>
     </r>
@@ -98,7 +88,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>新增层级</t>
     </r>
@@ -115,7 +104,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>科室</t>
     </r>
@@ -134,7 +122,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>新增层级</t>
     </r>
@@ -151,7 +138,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>科室</t>
     </r>
@@ -170,7 +156,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>新增层级</t>
     </r>
@@ -187,7 +172,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>科室</t>
     </r>
@@ -279,10 +263,23 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="0" formatCode="General"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <color indexed="8"/>
       <name val="Arial"/>
     </font>
@@ -290,19 +287,11 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -325,7 +314,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -402,6 +391,37 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -471,130 +491,113 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="25">
+    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FF4D5D2C"/>
-      <rgbColor rgb="FFAAAAAA"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ffff0000"/>
+      <rgbColor rgb="ff00ff00"/>
+      <rgbColor rgb="ff0000ff"/>
+      <rgbColor rgb="ffffff00"/>
+      <rgbColor rgb="ffff00ff"/>
+      <rgbColor rgb="ff00ffff"/>
+      <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ff4d5d2c"/>
+      <rgbColor rgb="ffaaaaaa"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -796,7 +799,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -815,7 +818,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -845,7 +848,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -871,7 +874,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -897,7 +900,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -923,7 +926,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -949,7 +952,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -975,7 +978,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1001,7 +1004,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1027,7 +1030,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1053,7 +1056,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1066,15 +1069,9 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -1091,7 +1088,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1110,7 +1107,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1136,7 +1133,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1162,7 +1159,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1188,7 +1185,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1214,7 +1211,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1240,7 +1237,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1266,7 +1263,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1292,7 +1289,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1318,7 +1315,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1344,7 +1341,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1357,15 +1354,9 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1379,7 +1370,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1398,7 +1389,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1428,7 +1419,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1454,7 +1445,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1480,7 +1471,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1506,7 +1497,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1532,7 +1523,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1558,7 +1549,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1584,7 +1575,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1610,7 +1601,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1636,7 +1627,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1649,616 +1640,264 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IU2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:O10"/>
+  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="13.42578125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="14.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="9" width="8.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.3516" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6719" style="1" customWidth="1"/>
+    <col min="3" max="4" width="13.5" style="1" customWidth="1"/>
+    <col min="5" max="6" width="14.3516" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6719" style="1" customWidth="1"/>
+    <col min="8" max="9" width="8.85156" style="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
-    <col min="11" max="12" width="8.85546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="24.7109375" style="1" customWidth="1"/>
+    <col min="11" max="12" width="8.85156" style="1" customWidth="1"/>
+    <col min="13" max="13" width="24.6719" style="1" customWidth="1"/>
     <col min="14" max="14" width="30" style="1" customWidth="1"/>
-    <col min="15" max="15" width="32.7109375" style="1" customWidth="1"/>
-    <col min="16" max="255" width="8.85546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="32.6719" style="1" customWidth="1"/>
+    <col min="16" max="256" width="8.85156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:255" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="30.75" customHeight="1">
+      <c r="A1" t="s" s="2">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s" s="2">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s" s="2">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s" s="2">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s" s="2">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s" s="2">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s" s="2">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s" s="2">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s" s="2">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" t="s" s="2">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" t="s" s="2">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" t="s" s="2">
         <v>14</v>
       </c>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4"/>
-      <c r="AD1" s="4"/>
-      <c r="AE1" s="4"/>
-      <c r="AF1" s="4"/>
-      <c r="AG1" s="4"/>
-      <c r="AH1" s="4"/>
-      <c r="AI1" s="4"/>
-      <c r="AJ1" s="4"/>
-      <c r="AK1" s="4"/>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
-      <c r="AP1" s="4"/>
-      <c r="AQ1" s="4"/>
-      <c r="AR1" s="4"/>
-      <c r="AS1" s="4"/>
-      <c r="AT1" s="4"/>
-      <c r="AU1" s="4"/>
-      <c r="AV1" s="4"/>
-      <c r="AW1" s="4"/>
-      <c r="AX1" s="4"/>
-      <c r="AY1" s="4"/>
-      <c r="AZ1" s="4"/>
-      <c r="BA1" s="4"/>
-      <c r="BB1" s="4"/>
-      <c r="BC1" s="4"/>
-      <c r="BD1" s="4"/>
-      <c r="BE1" s="4"/>
-      <c r="BF1" s="4"/>
-      <c r="BG1" s="4"/>
-      <c r="BH1" s="4"/>
-      <c r="BI1" s="4"/>
-      <c r="BJ1" s="4"/>
-      <c r="BK1" s="4"/>
-      <c r="BL1" s="4"/>
-      <c r="BM1" s="4"/>
-      <c r="BN1" s="4"/>
-      <c r="BO1" s="4"/>
-      <c r="BP1" s="4"/>
-      <c r="BQ1" s="4"/>
-      <c r="BR1" s="4"/>
-      <c r="BS1" s="4"/>
-      <c r="BT1" s="4"/>
-      <c r="BU1" s="4"/>
-      <c r="BV1" s="4"/>
-      <c r="BW1" s="4"/>
-      <c r="BX1" s="4"/>
-      <c r="BY1" s="4"/>
-      <c r="BZ1" s="4"/>
-      <c r="CA1" s="4"/>
-      <c r="CB1" s="4"/>
-      <c r="CC1" s="4"/>
-      <c r="CD1" s="4"/>
-      <c r="CE1" s="4"/>
-      <c r="CF1" s="4"/>
-      <c r="CG1" s="4"/>
-      <c r="CH1" s="4"/>
-      <c r="CI1" s="4"/>
-      <c r="CJ1" s="4"/>
-      <c r="CK1" s="4"/>
-      <c r="CL1" s="4"/>
-      <c r="CM1" s="4"/>
-      <c r="CN1" s="4"/>
-      <c r="CO1" s="4"/>
-      <c r="CP1" s="4"/>
-      <c r="CQ1" s="4"/>
-      <c r="CR1" s="4"/>
-      <c r="CS1" s="4"/>
-      <c r="CT1" s="4"/>
-      <c r="CU1" s="4"/>
-      <c r="CV1" s="4"/>
-      <c r="CW1" s="4"/>
-      <c r="CX1" s="4"/>
-      <c r="CY1" s="4"/>
-      <c r="CZ1" s="4"/>
-      <c r="DA1" s="4"/>
-      <c r="DB1" s="4"/>
-      <c r="DC1" s="4"/>
-      <c r="DD1" s="4"/>
-      <c r="DE1" s="4"/>
-      <c r="DF1" s="4"/>
-      <c r="DG1" s="4"/>
-      <c r="DH1" s="4"/>
-      <c r="DI1" s="4"/>
-      <c r="DJ1" s="4"/>
-      <c r="DK1" s="4"/>
-      <c r="DL1" s="4"/>
-      <c r="DM1" s="4"/>
-      <c r="DN1" s="4"/>
-      <c r="DO1" s="4"/>
-      <c r="DP1" s="4"/>
-      <c r="DQ1" s="4"/>
-      <c r="DR1" s="4"/>
-      <c r="DS1" s="4"/>
-      <c r="DT1" s="4"/>
-      <c r="DU1" s="4"/>
-      <c r="DV1" s="4"/>
-      <c r="DW1" s="4"/>
-      <c r="DX1" s="4"/>
-      <c r="DY1" s="4"/>
-      <c r="DZ1" s="4"/>
-      <c r="EA1" s="4"/>
-      <c r="EB1" s="4"/>
-      <c r="EC1" s="4"/>
-      <c r="ED1" s="4"/>
-      <c r="EE1" s="4"/>
-      <c r="EF1" s="4"/>
-      <c r="EG1" s="4"/>
-      <c r="EH1" s="4"/>
-      <c r="EI1" s="4"/>
-      <c r="EJ1" s="4"/>
-      <c r="EK1" s="4"/>
-      <c r="EL1" s="4"/>
-      <c r="EM1" s="4"/>
-      <c r="EN1" s="4"/>
-      <c r="EO1" s="4"/>
-      <c r="EP1" s="4"/>
-      <c r="EQ1" s="4"/>
-      <c r="ER1" s="4"/>
-      <c r="ES1" s="4"/>
-      <c r="ET1" s="4"/>
-      <c r="EU1" s="4"/>
-      <c r="EV1" s="4"/>
-      <c r="EW1" s="4"/>
-      <c r="EX1" s="4"/>
-      <c r="EY1" s="4"/>
-      <c r="EZ1" s="4"/>
-      <c r="FA1" s="4"/>
-      <c r="FB1" s="4"/>
-      <c r="FC1" s="4"/>
-      <c r="FD1" s="4"/>
-      <c r="FE1" s="4"/>
-      <c r="FF1" s="4"/>
-      <c r="FG1" s="4"/>
-      <c r="FH1" s="4"/>
-      <c r="FI1" s="4"/>
-      <c r="FJ1" s="4"/>
-      <c r="FK1" s="4"/>
-      <c r="FL1" s="4"/>
-      <c r="FM1" s="4"/>
-      <c r="FN1" s="4"/>
-      <c r="FO1" s="4"/>
-      <c r="FP1" s="4"/>
-      <c r="FQ1" s="4"/>
-      <c r="FR1" s="4"/>
-      <c r="FS1" s="4"/>
-      <c r="FT1" s="4"/>
-      <c r="FU1" s="4"/>
-      <c r="FV1" s="4"/>
-      <c r="FW1" s="4"/>
-      <c r="FX1" s="4"/>
-      <c r="FY1" s="4"/>
-      <c r="FZ1" s="4"/>
-      <c r="GA1" s="4"/>
-      <c r="GB1" s="4"/>
-      <c r="GC1" s="4"/>
-      <c r="GD1" s="4"/>
-      <c r="GE1" s="4"/>
-      <c r="GF1" s="4"/>
-      <c r="GG1" s="4"/>
-      <c r="GH1" s="4"/>
-      <c r="GI1" s="4"/>
-      <c r="GJ1" s="4"/>
-      <c r="GK1" s="4"/>
-      <c r="GL1" s="4"/>
-      <c r="GM1" s="4"/>
-      <c r="GN1" s="4"/>
-      <c r="GO1" s="4"/>
-      <c r="GP1" s="4"/>
-      <c r="GQ1" s="4"/>
-      <c r="GR1" s="4"/>
-      <c r="GS1" s="4"/>
-      <c r="GT1" s="4"/>
-      <c r="GU1" s="4"/>
-      <c r="GV1" s="4"/>
-      <c r="GW1" s="4"/>
-      <c r="GX1" s="4"/>
-      <c r="GY1" s="4"/>
-      <c r="GZ1" s="4"/>
-      <c r="HA1" s="4"/>
-      <c r="HB1" s="4"/>
-      <c r="HC1" s="4"/>
-      <c r="HD1" s="4"/>
-      <c r="HE1" s="4"/>
-      <c r="HF1" s="4"/>
-      <c r="HG1" s="4"/>
-      <c r="HH1" s="4"/>
-      <c r="HI1" s="4"/>
-      <c r="HJ1" s="4"/>
-      <c r="HK1" s="4"/>
-      <c r="HL1" s="4"/>
-      <c r="HM1" s="4"/>
-      <c r="HN1" s="4"/>
-      <c r="HO1" s="4"/>
-      <c r="HP1" s="4"/>
-      <c r="HQ1" s="4"/>
-      <c r="HR1" s="4"/>
-      <c r="HS1" s="4"/>
-      <c r="HT1" s="4"/>
-      <c r="HU1" s="4"/>
-      <c r="HV1" s="4"/>
-      <c r="HW1" s="4"/>
-      <c r="HX1" s="4"/>
-      <c r="HY1" s="4"/>
-      <c r="HZ1" s="4"/>
-      <c r="IA1" s="4"/>
-      <c r="IB1" s="4"/>
-      <c r="IC1" s="4"/>
-      <c r="ID1" s="4"/>
-      <c r="IE1" s="4"/>
-      <c r="IF1" s="4"/>
-      <c r="IG1" s="4"/>
-      <c r="IH1" s="4"/>
-      <c r="II1" s="4"/>
-      <c r="IJ1" s="4"/>
-      <c r="IK1" s="4"/>
-      <c r="IL1" s="4"/>
-      <c r="IM1" s="4"/>
-      <c r="IN1" s="4"/>
-      <c r="IO1" s="4"/>
-      <c r="IP1" s="4"/>
-      <c r="IQ1" s="4"/>
-      <c r="IR1" s="4"/>
-      <c r="IS1" s="4"/>
-      <c r="IT1" s="4"/>
-      <c r="IU1" s="5"/>
-    </row>
-    <row r="2" spans="1:255" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+    </row>
+    <row r="2" ht="34.5" customHeight="1">
+      <c r="A2" t="s" s="3">
         <v>15</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" t="s" s="3">
         <v>16</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" t="s" s="3">
         <v>17</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" t="s" s="3">
         <v>18</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" t="s" s="3">
         <v>19</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" t="s" s="3">
         <v>20</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" t="s" s="3">
         <v>21</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" t="s" s="3">
         <v>21</v>
       </c>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6" t="s">
+      <c r="I2" s="3"/>
+      <c r="J2" t="s" s="3">
         <v>22</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" t="s" s="3">
         <v>23</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" t="s" s="3">
         <v>24</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" t="s" s="4">
         <v>26</v>
       </c>
-      <c r="O2" s="6"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
-      <c r="AE2" s="9"/>
-      <c r="AF2" s="9"/>
-      <c r="AG2" s="9"/>
-      <c r="AH2" s="9"/>
-      <c r="AI2" s="9"/>
-      <c r="AJ2" s="9"/>
-      <c r="AK2" s="9"/>
-      <c r="AL2" s="9"/>
-      <c r="AM2" s="9"/>
-      <c r="AN2" s="9"/>
-      <c r="AO2" s="9"/>
-      <c r="AP2" s="9"/>
-      <c r="AQ2" s="9"/>
-      <c r="AR2" s="9"/>
-      <c r="AS2" s="9"/>
-      <c r="AT2" s="9"/>
-      <c r="AU2" s="9"/>
-      <c r="AV2" s="9"/>
-      <c r="AW2" s="9"/>
-      <c r="AX2" s="9"/>
-      <c r="AY2" s="9"/>
-      <c r="AZ2" s="9"/>
-      <c r="BA2" s="9"/>
-      <c r="BB2" s="9"/>
-      <c r="BC2" s="9"/>
-      <c r="BD2" s="9"/>
-      <c r="BE2" s="9"/>
-      <c r="BF2" s="9"/>
-      <c r="BG2" s="9"/>
-      <c r="BH2" s="9"/>
-      <c r="BI2" s="9"/>
-      <c r="BJ2" s="9"/>
-      <c r="BK2" s="9"/>
-      <c r="BL2" s="9"/>
-      <c r="BM2" s="9"/>
-      <c r="BN2" s="9"/>
-      <c r="BO2" s="9"/>
-      <c r="BP2" s="9"/>
-      <c r="BQ2" s="9"/>
-      <c r="BR2" s="9"/>
-      <c r="BS2" s="9"/>
-      <c r="BT2" s="9"/>
-      <c r="BU2" s="9"/>
-      <c r="BV2" s="9"/>
-      <c r="BW2" s="9"/>
-      <c r="BX2" s="9"/>
-      <c r="BY2" s="9"/>
-      <c r="BZ2" s="9"/>
-      <c r="CA2" s="9"/>
-      <c r="CB2" s="9"/>
-      <c r="CC2" s="9"/>
-      <c r="CD2" s="9"/>
-      <c r="CE2" s="9"/>
-      <c r="CF2" s="9"/>
-      <c r="CG2" s="9"/>
-      <c r="CH2" s="9"/>
-      <c r="CI2" s="9"/>
-      <c r="CJ2" s="9"/>
-      <c r="CK2" s="9"/>
-      <c r="CL2" s="9"/>
-      <c r="CM2" s="9"/>
-      <c r="CN2" s="9"/>
-      <c r="CO2" s="9"/>
-      <c r="CP2" s="9"/>
-      <c r="CQ2" s="9"/>
-      <c r="CR2" s="9"/>
-      <c r="CS2" s="9"/>
-      <c r="CT2" s="9"/>
-      <c r="CU2" s="9"/>
-      <c r="CV2" s="9"/>
-      <c r="CW2" s="9"/>
-      <c r="CX2" s="9"/>
-      <c r="CY2" s="9"/>
-      <c r="CZ2" s="9"/>
-      <c r="DA2" s="9"/>
-      <c r="DB2" s="9"/>
-      <c r="DC2" s="9"/>
-      <c r="DD2" s="9"/>
-      <c r="DE2" s="9"/>
-      <c r="DF2" s="9"/>
-      <c r="DG2" s="9"/>
-      <c r="DH2" s="9"/>
-      <c r="DI2" s="9"/>
-      <c r="DJ2" s="9"/>
-      <c r="DK2" s="9"/>
-      <c r="DL2" s="9"/>
-      <c r="DM2" s="9"/>
-      <c r="DN2" s="9"/>
-      <c r="DO2" s="9"/>
-      <c r="DP2" s="9"/>
-      <c r="DQ2" s="9"/>
-      <c r="DR2" s="9"/>
-      <c r="DS2" s="9"/>
-      <c r="DT2" s="9"/>
-      <c r="DU2" s="9"/>
-      <c r="DV2" s="9"/>
-      <c r="DW2" s="9"/>
-      <c r="DX2" s="9"/>
-      <c r="DY2" s="9"/>
-      <c r="DZ2" s="9"/>
-      <c r="EA2" s="9"/>
-      <c r="EB2" s="9"/>
-      <c r="EC2" s="9"/>
-      <c r="ED2" s="9"/>
-      <c r="EE2" s="9"/>
-      <c r="EF2" s="9"/>
-      <c r="EG2" s="9"/>
-      <c r="EH2" s="9"/>
-      <c r="EI2" s="9"/>
-      <c r="EJ2" s="9"/>
-      <c r="EK2" s="9"/>
-      <c r="EL2" s="9"/>
-      <c r="EM2" s="9"/>
-      <c r="EN2" s="9"/>
-      <c r="EO2" s="9"/>
-      <c r="EP2" s="9"/>
-      <c r="EQ2" s="9"/>
-      <c r="ER2" s="9"/>
-      <c r="ES2" s="9"/>
-      <c r="ET2" s="9"/>
-      <c r="EU2" s="9"/>
-      <c r="EV2" s="9"/>
-      <c r="EW2" s="9"/>
-      <c r="EX2" s="9"/>
-      <c r="EY2" s="9"/>
-      <c r="EZ2" s="9"/>
-      <c r="FA2" s="9"/>
-      <c r="FB2" s="9"/>
-      <c r="FC2" s="9"/>
-      <c r="FD2" s="9"/>
-      <c r="FE2" s="9"/>
-      <c r="FF2" s="9"/>
-      <c r="FG2" s="9"/>
-      <c r="FH2" s="9"/>
-      <c r="FI2" s="9"/>
-      <c r="FJ2" s="9"/>
-      <c r="FK2" s="9"/>
-      <c r="FL2" s="9"/>
-      <c r="FM2" s="9"/>
-      <c r="FN2" s="9"/>
-      <c r="FO2" s="9"/>
-      <c r="FP2" s="9"/>
-      <c r="FQ2" s="9"/>
-      <c r="FR2" s="9"/>
-      <c r="FS2" s="9"/>
-      <c r="FT2" s="9"/>
-      <c r="FU2" s="9"/>
-      <c r="FV2" s="9"/>
-      <c r="FW2" s="9"/>
-      <c r="FX2" s="9"/>
-      <c r="FY2" s="9"/>
-      <c r="FZ2" s="9"/>
-      <c r="GA2" s="9"/>
-      <c r="GB2" s="9"/>
-      <c r="GC2" s="9"/>
-      <c r="GD2" s="9"/>
-      <c r="GE2" s="9"/>
-      <c r="GF2" s="9"/>
-      <c r="GG2" s="9"/>
-      <c r="GH2" s="9"/>
-      <c r="GI2" s="9"/>
-      <c r="GJ2" s="9"/>
-      <c r="GK2" s="9"/>
-      <c r="GL2" s="9"/>
-      <c r="GM2" s="9"/>
-      <c r="GN2" s="9"/>
-      <c r="GO2" s="9"/>
-      <c r="GP2" s="9"/>
-      <c r="GQ2" s="9"/>
-      <c r="GR2" s="9"/>
-      <c r="GS2" s="9"/>
-      <c r="GT2" s="9"/>
-      <c r="GU2" s="9"/>
-      <c r="GV2" s="9"/>
-      <c r="GW2" s="9"/>
-      <c r="GX2" s="9"/>
-      <c r="GY2" s="9"/>
-      <c r="GZ2" s="9"/>
-      <c r="HA2" s="9"/>
-      <c r="HB2" s="9"/>
-      <c r="HC2" s="9"/>
-      <c r="HD2" s="9"/>
-      <c r="HE2" s="9"/>
-      <c r="HF2" s="9"/>
-      <c r="HG2" s="9"/>
-      <c r="HH2" s="9"/>
-      <c r="HI2" s="9"/>
-      <c r="HJ2" s="9"/>
-      <c r="HK2" s="9"/>
-      <c r="HL2" s="9"/>
-      <c r="HM2" s="9"/>
-      <c r="HN2" s="9"/>
-      <c r="HO2" s="9"/>
-      <c r="HP2" s="9"/>
-      <c r="HQ2" s="9"/>
-      <c r="HR2" s="9"/>
-      <c r="HS2" s="9"/>
-      <c r="HT2" s="9"/>
-      <c r="HU2" s="9"/>
-      <c r="HV2" s="9"/>
-      <c r="HW2" s="9"/>
-      <c r="HX2" s="9"/>
-      <c r="HY2" s="9"/>
-      <c r="HZ2" s="9"/>
-      <c r="IA2" s="9"/>
-      <c r="IB2" s="9"/>
-      <c r="IC2" s="9"/>
-      <c r="ID2" s="9"/>
-      <c r="IE2" s="9"/>
-      <c r="IF2" s="9"/>
-      <c r="IG2" s="9"/>
-      <c r="IH2" s="9"/>
-      <c r="II2" s="9"/>
-      <c r="IJ2" s="9"/>
-      <c r="IK2" s="9"/>
-      <c r="IL2" s="9"/>
-      <c r="IM2" s="9"/>
-      <c r="IN2" s="9"/>
-      <c r="IO2" s="9"/>
-      <c r="IP2" s="9"/>
-      <c r="IQ2" s="9"/>
-      <c r="IR2" s="9"/>
-      <c r="IS2" s="9"/>
-      <c r="IT2" s="9"/>
-      <c r="IU2" s="10"/>
+      <c r="O2" s="3"/>
+    </row>
+    <row r="3" ht="13.65" customHeight="1">
+      <c r="A3" s="5"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="7"/>
+    </row>
+    <row r="4" ht="13.65" customHeight="1">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="10"/>
+    </row>
+    <row r="5" ht="13.65" customHeight="1">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="10"/>
+    </row>
+    <row r="6" ht="13.65" customHeight="1">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="10"/>
+    </row>
+    <row r="7" ht="13.65" customHeight="1">
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="10"/>
+    </row>
+    <row r="8" ht="13.65" customHeight="1">
+      <c r="A8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="10"/>
+    </row>
+    <row r="9" ht="13.65" customHeight="1">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="10"/>
+    </row>
+    <row r="10" ht="13.65" customHeight="1">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="13"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -2266,214 +1905,214 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:IV22"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="108.7109375" style="11" customWidth="1"/>
-    <col min="2" max="256" width="8.85546875" style="11" customWidth="1"/>
+    <col min="1" max="1" width="108.672" style="14" customWidth="1"/>
+    <col min="2" max="5" width="8.85156" style="14" customWidth="1"/>
+    <col min="6" max="256" width="8.85156" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+    <row r="1" ht="13.7" customHeight="1">
+      <c r="A1" t="s" s="15">
         <v>27</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-    </row>
-    <row r="2" spans="1:5" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-    </row>
-    <row r="3" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+    </row>
+    <row r="2" ht="13.7" customHeight="1">
+      <c r="A2" s="18"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+    </row>
+    <row r="3" ht="15.95" customHeight="1">
+      <c r="A3" t="s" s="19">
         <v>28</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
+      <c r="B3" s="20"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+    </row>
+    <row r="4" ht="15.95" customHeight="1">
+      <c r="A4" t="s" s="19">
         <v>29</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-    </row>
-    <row r="5" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+    </row>
+    <row r="5" ht="15.95" customHeight="1">
+      <c r="A5" t="s" s="19">
         <v>30</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
+      <c r="B5" s="20"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" ht="15.95" customHeight="1">
+      <c r="A6" t="s" s="19">
         <v>31</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-    </row>
-    <row r="7" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
+      <c r="B6" s="20"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" ht="15.95" customHeight="1">
+      <c r="A7" t="s" s="19">
         <v>32</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-    </row>
-    <row r="8" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
+      <c r="B7" s="20"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+    </row>
+    <row r="8" ht="15.95" customHeight="1">
+      <c r="A8" t="s" s="19">
         <v>33</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-    </row>
-    <row r="9" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="14" t="s">
+      <c r="B8" s="20"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+    </row>
+    <row r="9" ht="15.95" customHeight="1">
+      <c r="A9" t="s" s="19">
         <v>34</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-    </row>
-    <row r="10" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="16"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-    </row>
-    <row r="11" spans="1:5" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="21" t="s">
+      <c r="B9" s="20"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+    </row>
+    <row r="10" ht="15.95" customHeight="1">
+      <c r="A10" s="21"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+    </row>
+    <row r="11" ht="13.7" customHeight="1">
+      <c r="A11" t="s" s="22">
         <v>35</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-    </row>
-    <row r="12" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-    </row>
-    <row r="13" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="14" t="s">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+    </row>
+    <row r="12" ht="12" customHeight="1">
+      <c r="A12" s="18"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+    </row>
+    <row r="13" ht="15.95" customHeight="1">
+      <c r="A13" t="s" s="19">
         <v>36</v>
       </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-    </row>
-    <row r="14" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="14" t="s">
+      <c r="B13" s="24"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+    </row>
+    <row r="14" ht="15.95" customHeight="1">
+      <c r="A14" t="s" s="19">
         <v>37</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-    </row>
-    <row r="15" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="14" t="s">
+      <c r="B14" s="24"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+    </row>
+    <row r="15" ht="15.95" customHeight="1">
+      <c r="A15" t="s" s="19">
         <v>38</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-    </row>
-    <row r="16" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="14" t="s">
+      <c r="B15" s="24"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+    </row>
+    <row r="16" ht="15.95" customHeight="1">
+      <c r="A16" t="s" s="19">
         <v>39</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="14" t="s">
+      <c r="B16" s="24"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+    </row>
+    <row r="17" ht="15.95" customHeight="1">
+      <c r="A17" t="s" s="19">
         <v>40</v>
       </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-    </row>
-    <row r="18" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="14" t="s">
+      <c r="B17" s="24"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+    </row>
+    <row r="18" ht="15.95" customHeight="1">
+      <c r="A18" t="s" s="19">
         <v>41</v>
       </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="14" t="s">
+      <c r="B18" s="24"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+    </row>
+    <row r="19" ht="15.95" customHeight="1">
+      <c r="A19" t="s" s="19">
         <v>42</v>
       </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="14" t="s">
+      <c r="B19" s="24"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+    </row>
+    <row r="20" ht="15.95" customHeight="1">
+      <c r="A20" t="s" s="19">
         <v>43</v>
       </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="14" t="s">
+      <c r="B20" s="24"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+    </row>
+    <row r="21" ht="15.95" customHeight="1">
+      <c r="A21" t="s" s="19">
         <v>44</v>
       </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-    </row>
-    <row r="22" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="14" t="s">
+      <c r="B21" s="24"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+    </row>
+    <row r="22" ht="13.5" customHeight="1">
+      <c r="A22" t="s" s="19">
         <v>45</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A11:A12"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A11:A12"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
@@ -14,10 +14,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
   <si>
-    <t>所属集团</t>
+    <t>所属集团*</t>
   </si>
   <si>
-    <t>所属医院*</t>
+    <t>所属医院</t>
   </si>
   <si>
     <t>所属院区</t>
@@ -505,37 +505,37 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
@@ -1652,7 +1652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:IU10"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="17.3516" style="1" customWidth="1"/>
@@ -1666,7 +1666,7 @@
     <col min="13" max="13" width="24.6719" style="1" customWidth="1"/>
     <col min="14" max="14" width="30" style="1" customWidth="1"/>
     <col min="15" max="15" width="32.6719" style="1" customWidth="1"/>
-    <col min="16" max="256" width="8.85156" style="1" customWidth="1"/>
+    <col min="16" max="255" width="8.85156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1">
@@ -1715,66 +1715,786 @@
       <c r="O1" t="s" s="2">
         <v>14</v>
       </c>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AJ1" s="4"/>
+      <c r="AK1" s="4"/>
+      <c r="AL1" s="4"/>
+      <c r="AM1" s="4"/>
+      <c r="AN1" s="4"/>
+      <c r="AO1" s="4"/>
+      <c r="AP1" s="4"/>
+      <c r="AQ1" s="4"/>
+      <c r="AR1" s="4"/>
+      <c r="AS1" s="4"/>
+      <c r="AT1" s="4"/>
+      <c r="AU1" s="4"/>
+      <c r="AV1" s="4"/>
+      <c r="AW1" s="4"/>
+      <c r="AX1" s="4"/>
+      <c r="AY1" s="4"/>
+      <c r="AZ1" s="4"/>
+      <c r="BA1" s="4"/>
+      <c r="BB1" s="4"/>
+      <c r="BC1" s="4"/>
+      <c r="BD1" s="4"/>
+      <c r="BE1" s="4"/>
+      <c r="BF1" s="4"/>
+      <c r="BG1" s="4"/>
+      <c r="BH1" s="4"/>
+      <c r="BI1" s="4"/>
+      <c r="BJ1" s="4"/>
+      <c r="BK1" s="4"/>
+      <c r="BL1" s="4"/>
+      <c r="BM1" s="4"/>
+      <c r="BN1" s="4"/>
+      <c r="BO1" s="4"/>
+      <c r="BP1" s="4"/>
+      <c r="BQ1" s="4"/>
+      <c r="BR1" s="4"/>
+      <c r="BS1" s="4"/>
+      <c r="BT1" s="4"/>
+      <c r="BU1" s="4"/>
+      <c r="BV1" s="4"/>
+      <c r="BW1" s="4"/>
+      <c r="BX1" s="4"/>
+      <c r="BY1" s="4"/>
+      <c r="BZ1" s="4"/>
+      <c r="CA1" s="4"/>
+      <c r="CB1" s="4"/>
+      <c r="CC1" s="4"/>
+      <c r="CD1" s="4"/>
+      <c r="CE1" s="4"/>
+      <c r="CF1" s="4"/>
+      <c r="CG1" s="4"/>
+      <c r="CH1" s="4"/>
+      <c r="CI1" s="4"/>
+      <c r="CJ1" s="4"/>
+      <c r="CK1" s="4"/>
+      <c r="CL1" s="4"/>
+      <c r="CM1" s="4"/>
+      <c r="CN1" s="4"/>
+      <c r="CO1" s="4"/>
+      <c r="CP1" s="4"/>
+      <c r="CQ1" s="4"/>
+      <c r="CR1" s="4"/>
+      <c r="CS1" s="4"/>
+      <c r="CT1" s="4"/>
+      <c r="CU1" s="4"/>
+      <c r="CV1" s="4"/>
+      <c r="CW1" s="4"/>
+      <c r="CX1" s="4"/>
+      <c r="CY1" s="4"/>
+      <c r="CZ1" s="4"/>
+      <c r="DA1" s="4"/>
+      <c r="DB1" s="4"/>
+      <c r="DC1" s="4"/>
+      <c r="DD1" s="4"/>
+      <c r="DE1" s="4"/>
+      <c r="DF1" s="4"/>
+      <c r="DG1" s="4"/>
+      <c r="DH1" s="4"/>
+      <c r="DI1" s="4"/>
+      <c r="DJ1" s="4"/>
+      <c r="DK1" s="4"/>
+      <c r="DL1" s="4"/>
+      <c r="DM1" s="4"/>
+      <c r="DN1" s="4"/>
+      <c r="DO1" s="4"/>
+      <c r="DP1" s="4"/>
+      <c r="DQ1" s="4"/>
+      <c r="DR1" s="4"/>
+      <c r="DS1" s="4"/>
+      <c r="DT1" s="4"/>
+      <c r="DU1" s="4"/>
+      <c r="DV1" s="4"/>
+      <c r="DW1" s="4"/>
+      <c r="DX1" s="4"/>
+      <c r="DY1" s="4"/>
+      <c r="DZ1" s="4"/>
+      <c r="EA1" s="4"/>
+      <c r="EB1" s="4"/>
+      <c r="EC1" s="4"/>
+      <c r="ED1" s="4"/>
+      <c r="EE1" s="4"/>
+      <c r="EF1" s="4"/>
+      <c r="EG1" s="4"/>
+      <c r="EH1" s="4"/>
+      <c r="EI1" s="4"/>
+      <c r="EJ1" s="4"/>
+      <c r="EK1" s="4"/>
+      <c r="EL1" s="4"/>
+      <c r="EM1" s="4"/>
+      <c r="EN1" s="4"/>
+      <c r="EO1" s="4"/>
+      <c r="EP1" s="4"/>
+      <c r="EQ1" s="4"/>
+      <c r="ER1" s="4"/>
+      <c r="ES1" s="4"/>
+      <c r="ET1" s="4"/>
+      <c r="EU1" s="4"/>
+      <c r="EV1" s="4"/>
+      <c r="EW1" s="4"/>
+      <c r="EX1" s="4"/>
+      <c r="EY1" s="4"/>
+      <c r="EZ1" s="4"/>
+      <c r="FA1" s="4"/>
+      <c r="FB1" s="4"/>
+      <c r="FC1" s="4"/>
+      <c r="FD1" s="4"/>
+      <c r="FE1" s="4"/>
+      <c r="FF1" s="4"/>
+      <c r="FG1" s="4"/>
+      <c r="FH1" s="4"/>
+      <c r="FI1" s="4"/>
+      <c r="FJ1" s="4"/>
+      <c r="FK1" s="4"/>
+      <c r="FL1" s="4"/>
+      <c r="FM1" s="4"/>
+      <c r="FN1" s="4"/>
+      <c r="FO1" s="4"/>
+      <c r="FP1" s="4"/>
+      <c r="FQ1" s="4"/>
+      <c r="FR1" s="4"/>
+      <c r="FS1" s="4"/>
+      <c r="FT1" s="4"/>
+      <c r="FU1" s="4"/>
+      <c r="FV1" s="4"/>
+      <c r="FW1" s="4"/>
+      <c r="FX1" s="4"/>
+      <c r="FY1" s="4"/>
+      <c r="FZ1" s="4"/>
+      <c r="GA1" s="4"/>
+      <c r="GB1" s="4"/>
+      <c r="GC1" s="4"/>
+      <c r="GD1" s="4"/>
+      <c r="GE1" s="4"/>
+      <c r="GF1" s="4"/>
+      <c r="GG1" s="4"/>
+      <c r="GH1" s="4"/>
+      <c r="GI1" s="4"/>
+      <c r="GJ1" s="4"/>
+      <c r="GK1" s="4"/>
+      <c r="GL1" s="4"/>
+      <c r="GM1" s="4"/>
+      <c r="GN1" s="4"/>
+      <c r="GO1" s="4"/>
+      <c r="GP1" s="4"/>
+      <c r="GQ1" s="4"/>
+      <c r="GR1" s="4"/>
+      <c r="GS1" s="4"/>
+      <c r="GT1" s="4"/>
+      <c r="GU1" s="4"/>
+      <c r="GV1" s="4"/>
+      <c r="GW1" s="4"/>
+      <c r="GX1" s="4"/>
+      <c r="GY1" s="4"/>
+      <c r="GZ1" s="4"/>
+      <c r="HA1" s="4"/>
+      <c r="HB1" s="4"/>
+      <c r="HC1" s="4"/>
+      <c r="HD1" s="4"/>
+      <c r="HE1" s="4"/>
+      <c r="HF1" s="4"/>
+      <c r="HG1" s="4"/>
+      <c r="HH1" s="4"/>
+      <c r="HI1" s="4"/>
+      <c r="HJ1" s="4"/>
+      <c r="HK1" s="4"/>
+      <c r="HL1" s="4"/>
+      <c r="HM1" s="4"/>
+      <c r="HN1" s="4"/>
+      <c r="HO1" s="4"/>
+      <c r="HP1" s="4"/>
+      <c r="HQ1" s="4"/>
+      <c r="HR1" s="4"/>
+      <c r="HS1" s="4"/>
+      <c r="HT1" s="4"/>
+      <c r="HU1" s="4"/>
+      <c r="HV1" s="4"/>
+      <c r="HW1" s="4"/>
+      <c r="HX1" s="4"/>
+      <c r="HY1" s="4"/>
+      <c r="HZ1" s="4"/>
+      <c r="IA1" s="4"/>
+      <c r="IB1" s="4"/>
+      <c r="IC1" s="4"/>
+      <c r="ID1" s="4"/>
+      <c r="IE1" s="4"/>
+      <c r="IF1" s="4"/>
+      <c r="IG1" s="4"/>
+      <c r="IH1" s="4"/>
+      <c r="II1" s="4"/>
+      <c r="IJ1" s="4"/>
+      <c r="IK1" s="4"/>
+      <c r="IL1" s="4"/>
+      <c r="IM1" s="4"/>
+      <c r="IN1" s="4"/>
+      <c r="IO1" s="4"/>
+      <c r="IP1" s="4"/>
+      <c r="IQ1" s="4"/>
+      <c r="IR1" s="4"/>
+      <c r="IS1" s="4"/>
+      <c r="IT1" s="4"/>
+      <c r="IU1" s="5"/>
     </row>
     <row r="2" ht="34.5" customHeight="1">
-      <c r="A2" t="s" s="3">
+      <c r="A2" t="s" s="6">
         <v>15</v>
       </c>
-      <c r="B2" t="s" s="3">
+      <c r="B2" t="s" s="6">
         <v>16</v>
       </c>
-      <c r="C2" t="s" s="3">
+      <c r="C2" t="s" s="6">
         <v>17</v>
       </c>
-      <c r="D2" t="s" s="3">
+      <c r="D2" t="s" s="6">
         <v>18</v>
       </c>
-      <c r="E2" t="s" s="3">
+      <c r="E2" t="s" s="6">
         <v>19</v>
       </c>
-      <c r="F2" t="s" s="3">
+      <c r="F2" t="s" s="6">
         <v>20</v>
       </c>
-      <c r="G2" t="s" s="3">
+      <c r="G2" t="s" s="6">
         <v>21</v>
       </c>
-      <c r="H2" t="s" s="3">
+      <c r="H2" t="s" s="6">
         <v>21</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" t="s" s="3">
+      <c r="I2" s="6"/>
+      <c r="J2" t="s" s="6">
         <v>22</v>
       </c>
-      <c r="K2" t="s" s="3">
+      <c r="K2" t="s" s="6">
         <v>23</v>
       </c>
-      <c r="L2" t="s" s="3">
+      <c r="L2" t="s" s="6">
         <v>24</v>
       </c>
-      <c r="M2" t="s" s="4">
+      <c r="M2" t="s" s="7">
         <v>25</v>
       </c>
-      <c r="N2" t="s" s="4">
+      <c r="N2" t="s" s="7">
         <v>26</v>
       </c>
-      <c r="O2" s="3"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
+      <c r="AE2" s="9"/>
+      <c r="AF2" s="9"/>
+      <c r="AG2" s="9"/>
+      <c r="AH2" s="9"/>
+      <c r="AI2" s="9"/>
+      <c r="AJ2" s="9"/>
+      <c r="AK2" s="9"/>
+      <c r="AL2" s="9"/>
+      <c r="AM2" s="9"/>
+      <c r="AN2" s="9"/>
+      <c r="AO2" s="9"/>
+      <c r="AP2" s="9"/>
+      <c r="AQ2" s="9"/>
+      <c r="AR2" s="9"/>
+      <c r="AS2" s="9"/>
+      <c r="AT2" s="9"/>
+      <c r="AU2" s="9"/>
+      <c r="AV2" s="9"/>
+      <c r="AW2" s="9"/>
+      <c r="AX2" s="9"/>
+      <c r="AY2" s="9"/>
+      <c r="AZ2" s="9"/>
+      <c r="BA2" s="9"/>
+      <c r="BB2" s="9"/>
+      <c r="BC2" s="9"/>
+      <c r="BD2" s="9"/>
+      <c r="BE2" s="9"/>
+      <c r="BF2" s="9"/>
+      <c r="BG2" s="9"/>
+      <c r="BH2" s="9"/>
+      <c r="BI2" s="9"/>
+      <c r="BJ2" s="9"/>
+      <c r="BK2" s="9"/>
+      <c r="BL2" s="9"/>
+      <c r="BM2" s="9"/>
+      <c r="BN2" s="9"/>
+      <c r="BO2" s="9"/>
+      <c r="BP2" s="9"/>
+      <c r="BQ2" s="9"/>
+      <c r="BR2" s="9"/>
+      <c r="BS2" s="9"/>
+      <c r="BT2" s="9"/>
+      <c r="BU2" s="9"/>
+      <c r="BV2" s="9"/>
+      <c r="BW2" s="9"/>
+      <c r="BX2" s="9"/>
+      <c r="BY2" s="9"/>
+      <c r="BZ2" s="9"/>
+      <c r="CA2" s="9"/>
+      <c r="CB2" s="9"/>
+      <c r="CC2" s="9"/>
+      <c r="CD2" s="9"/>
+      <c r="CE2" s="9"/>
+      <c r="CF2" s="9"/>
+      <c r="CG2" s="9"/>
+      <c r="CH2" s="9"/>
+      <c r="CI2" s="9"/>
+      <c r="CJ2" s="9"/>
+      <c r="CK2" s="9"/>
+      <c r="CL2" s="9"/>
+      <c r="CM2" s="9"/>
+      <c r="CN2" s="9"/>
+      <c r="CO2" s="9"/>
+      <c r="CP2" s="9"/>
+      <c r="CQ2" s="9"/>
+      <c r="CR2" s="9"/>
+      <c r="CS2" s="9"/>
+      <c r="CT2" s="9"/>
+      <c r="CU2" s="9"/>
+      <c r="CV2" s="9"/>
+      <c r="CW2" s="9"/>
+      <c r="CX2" s="9"/>
+      <c r="CY2" s="9"/>
+      <c r="CZ2" s="9"/>
+      <c r="DA2" s="9"/>
+      <c r="DB2" s="9"/>
+      <c r="DC2" s="9"/>
+      <c r="DD2" s="9"/>
+      <c r="DE2" s="9"/>
+      <c r="DF2" s="9"/>
+      <c r="DG2" s="9"/>
+      <c r="DH2" s="9"/>
+      <c r="DI2" s="9"/>
+      <c r="DJ2" s="9"/>
+      <c r="DK2" s="9"/>
+      <c r="DL2" s="9"/>
+      <c r="DM2" s="9"/>
+      <c r="DN2" s="9"/>
+      <c r="DO2" s="9"/>
+      <c r="DP2" s="9"/>
+      <c r="DQ2" s="9"/>
+      <c r="DR2" s="9"/>
+      <c r="DS2" s="9"/>
+      <c r="DT2" s="9"/>
+      <c r="DU2" s="9"/>
+      <c r="DV2" s="9"/>
+      <c r="DW2" s="9"/>
+      <c r="DX2" s="9"/>
+      <c r="DY2" s="9"/>
+      <c r="DZ2" s="9"/>
+      <c r="EA2" s="9"/>
+      <c r="EB2" s="9"/>
+      <c r="EC2" s="9"/>
+      <c r="ED2" s="9"/>
+      <c r="EE2" s="9"/>
+      <c r="EF2" s="9"/>
+      <c r="EG2" s="9"/>
+      <c r="EH2" s="9"/>
+      <c r="EI2" s="9"/>
+      <c r="EJ2" s="9"/>
+      <c r="EK2" s="9"/>
+      <c r="EL2" s="9"/>
+      <c r="EM2" s="9"/>
+      <c r="EN2" s="9"/>
+      <c r="EO2" s="9"/>
+      <c r="EP2" s="9"/>
+      <c r="EQ2" s="9"/>
+      <c r="ER2" s="9"/>
+      <c r="ES2" s="9"/>
+      <c r="ET2" s="9"/>
+      <c r="EU2" s="9"/>
+      <c r="EV2" s="9"/>
+      <c r="EW2" s="9"/>
+      <c r="EX2" s="9"/>
+      <c r="EY2" s="9"/>
+      <c r="EZ2" s="9"/>
+      <c r="FA2" s="9"/>
+      <c r="FB2" s="9"/>
+      <c r="FC2" s="9"/>
+      <c r="FD2" s="9"/>
+      <c r="FE2" s="9"/>
+      <c r="FF2" s="9"/>
+      <c r="FG2" s="9"/>
+      <c r="FH2" s="9"/>
+      <c r="FI2" s="9"/>
+      <c r="FJ2" s="9"/>
+      <c r="FK2" s="9"/>
+      <c r="FL2" s="9"/>
+      <c r="FM2" s="9"/>
+      <c r="FN2" s="9"/>
+      <c r="FO2" s="9"/>
+      <c r="FP2" s="9"/>
+      <c r="FQ2" s="9"/>
+      <c r="FR2" s="9"/>
+      <c r="FS2" s="9"/>
+      <c r="FT2" s="9"/>
+      <c r="FU2" s="9"/>
+      <c r="FV2" s="9"/>
+      <c r="FW2" s="9"/>
+      <c r="FX2" s="9"/>
+      <c r="FY2" s="9"/>
+      <c r="FZ2" s="9"/>
+      <c r="GA2" s="9"/>
+      <c r="GB2" s="9"/>
+      <c r="GC2" s="9"/>
+      <c r="GD2" s="9"/>
+      <c r="GE2" s="9"/>
+      <c r="GF2" s="9"/>
+      <c r="GG2" s="9"/>
+      <c r="GH2" s="9"/>
+      <c r="GI2" s="9"/>
+      <c r="GJ2" s="9"/>
+      <c r="GK2" s="9"/>
+      <c r="GL2" s="9"/>
+      <c r="GM2" s="9"/>
+      <c r="GN2" s="9"/>
+      <c r="GO2" s="9"/>
+      <c r="GP2" s="9"/>
+      <c r="GQ2" s="9"/>
+      <c r="GR2" s="9"/>
+      <c r="GS2" s="9"/>
+      <c r="GT2" s="9"/>
+      <c r="GU2" s="9"/>
+      <c r="GV2" s="9"/>
+      <c r="GW2" s="9"/>
+      <c r="GX2" s="9"/>
+      <c r="GY2" s="9"/>
+      <c r="GZ2" s="9"/>
+      <c r="HA2" s="9"/>
+      <c r="HB2" s="9"/>
+      <c r="HC2" s="9"/>
+      <c r="HD2" s="9"/>
+      <c r="HE2" s="9"/>
+      <c r="HF2" s="9"/>
+      <c r="HG2" s="9"/>
+      <c r="HH2" s="9"/>
+      <c r="HI2" s="9"/>
+      <c r="HJ2" s="9"/>
+      <c r="HK2" s="9"/>
+      <c r="HL2" s="9"/>
+      <c r="HM2" s="9"/>
+      <c r="HN2" s="9"/>
+      <c r="HO2" s="9"/>
+      <c r="HP2" s="9"/>
+      <c r="HQ2" s="9"/>
+      <c r="HR2" s="9"/>
+      <c r="HS2" s="9"/>
+      <c r="HT2" s="9"/>
+      <c r="HU2" s="9"/>
+      <c r="HV2" s="9"/>
+      <c r="HW2" s="9"/>
+      <c r="HX2" s="9"/>
+      <c r="HY2" s="9"/>
+      <c r="HZ2" s="9"/>
+      <c r="IA2" s="9"/>
+      <c r="IB2" s="9"/>
+      <c r="IC2" s="9"/>
+      <c r="ID2" s="9"/>
+      <c r="IE2" s="9"/>
+      <c r="IF2" s="9"/>
+      <c r="IG2" s="9"/>
+      <c r="IH2" s="9"/>
+      <c r="II2" s="9"/>
+      <c r="IJ2" s="9"/>
+      <c r="IK2" s="9"/>
+      <c r="IL2" s="9"/>
+      <c r="IM2" s="9"/>
+      <c r="IN2" s="9"/>
+      <c r="IO2" s="9"/>
+      <c r="IP2" s="9"/>
+      <c r="IQ2" s="9"/>
+      <c r="IR2" s="9"/>
+      <c r="IS2" s="9"/>
+      <c r="IT2" s="9"/>
+      <c r="IU2" s="10"/>
     </row>
     <row r="3" ht="13.65" customHeight="1">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="7"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
+      <c r="AF3" s="9"/>
+      <c r="AG3" s="9"/>
+      <c r="AH3" s="9"/>
+      <c r="AI3" s="9"/>
+      <c r="AJ3" s="9"/>
+      <c r="AK3" s="9"/>
+      <c r="AL3" s="9"/>
+      <c r="AM3" s="9"/>
+      <c r="AN3" s="9"/>
+      <c r="AO3" s="9"/>
+      <c r="AP3" s="9"/>
+      <c r="AQ3" s="9"/>
+      <c r="AR3" s="9"/>
+      <c r="AS3" s="9"/>
+      <c r="AT3" s="9"/>
+      <c r="AU3" s="9"/>
+      <c r="AV3" s="9"/>
+      <c r="AW3" s="9"/>
+      <c r="AX3" s="9"/>
+      <c r="AY3" s="9"/>
+      <c r="AZ3" s="9"/>
+      <c r="BA3" s="9"/>
+      <c r="BB3" s="9"/>
+      <c r="BC3" s="9"/>
+      <c r="BD3" s="9"/>
+      <c r="BE3" s="9"/>
+      <c r="BF3" s="9"/>
+      <c r="BG3" s="9"/>
+      <c r="BH3" s="9"/>
+      <c r="BI3" s="9"/>
+      <c r="BJ3" s="9"/>
+      <c r="BK3" s="9"/>
+      <c r="BL3" s="9"/>
+      <c r="BM3" s="9"/>
+      <c r="BN3" s="9"/>
+      <c r="BO3" s="9"/>
+      <c r="BP3" s="9"/>
+      <c r="BQ3" s="9"/>
+      <c r="BR3" s="9"/>
+      <c r="BS3" s="9"/>
+      <c r="BT3" s="9"/>
+      <c r="BU3" s="9"/>
+      <c r="BV3" s="9"/>
+      <c r="BW3" s="9"/>
+      <c r="BX3" s="9"/>
+      <c r="BY3" s="9"/>
+      <c r="BZ3" s="9"/>
+      <c r="CA3" s="9"/>
+      <c r="CB3" s="9"/>
+      <c r="CC3" s="9"/>
+      <c r="CD3" s="9"/>
+      <c r="CE3" s="9"/>
+      <c r="CF3" s="9"/>
+      <c r="CG3" s="9"/>
+      <c r="CH3" s="9"/>
+      <c r="CI3" s="9"/>
+      <c r="CJ3" s="9"/>
+      <c r="CK3" s="9"/>
+      <c r="CL3" s="9"/>
+      <c r="CM3" s="9"/>
+      <c r="CN3" s="9"/>
+      <c r="CO3" s="9"/>
+      <c r="CP3" s="9"/>
+      <c r="CQ3" s="9"/>
+      <c r="CR3" s="9"/>
+      <c r="CS3" s="9"/>
+      <c r="CT3" s="9"/>
+      <c r="CU3" s="9"/>
+      <c r="CV3" s="9"/>
+      <c r="CW3" s="9"/>
+      <c r="CX3" s="9"/>
+      <c r="CY3" s="9"/>
+      <c r="CZ3" s="9"/>
+      <c r="DA3" s="9"/>
+      <c r="DB3" s="9"/>
+      <c r="DC3" s="9"/>
+      <c r="DD3" s="9"/>
+      <c r="DE3" s="9"/>
+      <c r="DF3" s="9"/>
+      <c r="DG3" s="9"/>
+      <c r="DH3" s="9"/>
+      <c r="DI3" s="9"/>
+      <c r="DJ3" s="9"/>
+      <c r="DK3" s="9"/>
+      <c r="DL3" s="9"/>
+      <c r="DM3" s="9"/>
+      <c r="DN3" s="9"/>
+      <c r="DO3" s="9"/>
+      <c r="DP3" s="9"/>
+      <c r="DQ3" s="9"/>
+      <c r="DR3" s="9"/>
+      <c r="DS3" s="9"/>
+      <c r="DT3" s="9"/>
+      <c r="DU3" s="9"/>
+      <c r="DV3" s="9"/>
+      <c r="DW3" s="9"/>
+      <c r="DX3" s="9"/>
+      <c r="DY3" s="9"/>
+      <c r="DZ3" s="9"/>
+      <c r="EA3" s="9"/>
+      <c r="EB3" s="9"/>
+      <c r="EC3" s="9"/>
+      <c r="ED3" s="9"/>
+      <c r="EE3" s="9"/>
+      <c r="EF3" s="9"/>
+      <c r="EG3" s="9"/>
+      <c r="EH3" s="9"/>
+      <c r="EI3" s="9"/>
+      <c r="EJ3" s="9"/>
+      <c r="EK3" s="9"/>
+      <c r="EL3" s="9"/>
+      <c r="EM3" s="9"/>
+      <c r="EN3" s="9"/>
+      <c r="EO3" s="9"/>
+      <c r="EP3" s="9"/>
+      <c r="EQ3" s="9"/>
+      <c r="ER3" s="9"/>
+      <c r="ES3" s="9"/>
+      <c r="ET3" s="9"/>
+      <c r="EU3" s="9"/>
+      <c r="EV3" s="9"/>
+      <c r="EW3" s="9"/>
+      <c r="EX3" s="9"/>
+      <c r="EY3" s="9"/>
+      <c r="EZ3" s="9"/>
+      <c r="FA3" s="9"/>
+      <c r="FB3" s="9"/>
+      <c r="FC3" s="9"/>
+      <c r="FD3" s="9"/>
+      <c r="FE3" s="9"/>
+      <c r="FF3" s="9"/>
+      <c r="FG3" s="9"/>
+      <c r="FH3" s="9"/>
+      <c r="FI3" s="9"/>
+      <c r="FJ3" s="9"/>
+      <c r="FK3" s="9"/>
+      <c r="FL3" s="9"/>
+      <c r="FM3" s="9"/>
+      <c r="FN3" s="9"/>
+      <c r="FO3" s="9"/>
+      <c r="FP3" s="9"/>
+      <c r="FQ3" s="9"/>
+      <c r="FR3" s="9"/>
+      <c r="FS3" s="9"/>
+      <c r="FT3" s="9"/>
+      <c r="FU3" s="9"/>
+      <c r="FV3" s="9"/>
+      <c r="FW3" s="9"/>
+      <c r="FX3" s="9"/>
+      <c r="FY3" s="9"/>
+      <c r="FZ3" s="9"/>
+      <c r="GA3" s="9"/>
+      <c r="GB3" s="9"/>
+      <c r="GC3" s="9"/>
+      <c r="GD3" s="9"/>
+      <c r="GE3" s="9"/>
+      <c r="GF3" s="9"/>
+      <c r="GG3" s="9"/>
+      <c r="GH3" s="9"/>
+      <c r="GI3" s="9"/>
+      <c r="GJ3" s="9"/>
+      <c r="GK3" s="9"/>
+      <c r="GL3" s="9"/>
+      <c r="GM3" s="9"/>
+      <c r="GN3" s="9"/>
+      <c r="GO3" s="9"/>
+      <c r="GP3" s="9"/>
+      <c r="GQ3" s="9"/>
+      <c r="GR3" s="9"/>
+      <c r="GS3" s="9"/>
+      <c r="GT3" s="9"/>
+      <c r="GU3" s="9"/>
+      <c r="GV3" s="9"/>
+      <c r="GW3" s="9"/>
+      <c r="GX3" s="9"/>
+      <c r="GY3" s="9"/>
+      <c r="GZ3" s="9"/>
+      <c r="HA3" s="9"/>
+      <c r="HB3" s="9"/>
+      <c r="HC3" s="9"/>
+      <c r="HD3" s="9"/>
+      <c r="HE3" s="9"/>
+      <c r="HF3" s="9"/>
+      <c r="HG3" s="9"/>
+      <c r="HH3" s="9"/>
+      <c r="HI3" s="9"/>
+      <c r="HJ3" s="9"/>
+      <c r="HK3" s="9"/>
+      <c r="HL3" s="9"/>
+      <c r="HM3" s="9"/>
+      <c r="HN3" s="9"/>
+      <c r="HO3" s="9"/>
+      <c r="HP3" s="9"/>
+      <c r="HQ3" s="9"/>
+      <c r="HR3" s="9"/>
+      <c r="HS3" s="9"/>
+      <c r="HT3" s="9"/>
+      <c r="HU3" s="9"/>
+      <c r="HV3" s="9"/>
+      <c r="HW3" s="9"/>
+      <c r="HX3" s="9"/>
+      <c r="HY3" s="9"/>
+      <c r="HZ3" s="9"/>
+      <c r="IA3" s="9"/>
+      <c r="IB3" s="9"/>
+      <c r="IC3" s="9"/>
+      <c r="ID3" s="9"/>
+      <c r="IE3" s="9"/>
+      <c r="IF3" s="9"/>
+      <c r="IG3" s="9"/>
+      <c r="IH3" s="9"/>
+      <c r="II3" s="9"/>
+      <c r="IJ3" s="9"/>
+      <c r="IK3" s="9"/>
+      <c r="IL3" s="9"/>
+      <c r="IM3" s="9"/>
+      <c r="IN3" s="9"/>
+      <c r="IO3" s="9"/>
+      <c r="IP3" s="9"/>
+      <c r="IQ3" s="9"/>
+      <c r="IR3" s="9"/>
+      <c r="IS3" s="9"/>
+      <c r="IT3" s="9"/>
+      <c r="IU3" s="10"/>
     </row>
     <row r="4" ht="13.65" customHeight="1">
       <c r="A4" s="8"/>
@@ -1791,7 +2511,247 @@
       <c r="L4" s="9"/>
       <c r="M4" s="9"/>
       <c r="N4" s="9"/>
-      <c r="O4" s="10"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="9"/>
+      <c r="AE4" s="9"/>
+      <c r="AF4" s="9"/>
+      <c r="AG4" s="9"/>
+      <c r="AH4" s="9"/>
+      <c r="AI4" s="9"/>
+      <c r="AJ4" s="9"/>
+      <c r="AK4" s="9"/>
+      <c r="AL4" s="9"/>
+      <c r="AM4" s="9"/>
+      <c r="AN4" s="9"/>
+      <c r="AO4" s="9"/>
+      <c r="AP4" s="9"/>
+      <c r="AQ4" s="9"/>
+      <c r="AR4" s="9"/>
+      <c r="AS4" s="9"/>
+      <c r="AT4" s="9"/>
+      <c r="AU4" s="9"/>
+      <c r="AV4" s="9"/>
+      <c r="AW4" s="9"/>
+      <c r="AX4" s="9"/>
+      <c r="AY4" s="9"/>
+      <c r="AZ4" s="9"/>
+      <c r="BA4" s="9"/>
+      <c r="BB4" s="9"/>
+      <c r="BC4" s="9"/>
+      <c r="BD4" s="9"/>
+      <c r="BE4" s="9"/>
+      <c r="BF4" s="9"/>
+      <c r="BG4" s="9"/>
+      <c r="BH4" s="9"/>
+      <c r="BI4" s="9"/>
+      <c r="BJ4" s="9"/>
+      <c r="BK4" s="9"/>
+      <c r="BL4" s="9"/>
+      <c r="BM4" s="9"/>
+      <c r="BN4" s="9"/>
+      <c r="BO4" s="9"/>
+      <c r="BP4" s="9"/>
+      <c r="BQ4" s="9"/>
+      <c r="BR4" s="9"/>
+      <c r="BS4" s="9"/>
+      <c r="BT4" s="9"/>
+      <c r="BU4" s="9"/>
+      <c r="BV4" s="9"/>
+      <c r="BW4" s="9"/>
+      <c r="BX4" s="9"/>
+      <c r="BY4" s="9"/>
+      <c r="BZ4" s="9"/>
+      <c r="CA4" s="9"/>
+      <c r="CB4" s="9"/>
+      <c r="CC4" s="9"/>
+      <c r="CD4" s="9"/>
+      <c r="CE4" s="9"/>
+      <c r="CF4" s="9"/>
+      <c r="CG4" s="9"/>
+      <c r="CH4" s="9"/>
+      <c r="CI4" s="9"/>
+      <c r="CJ4" s="9"/>
+      <c r="CK4" s="9"/>
+      <c r="CL4" s="9"/>
+      <c r="CM4" s="9"/>
+      <c r="CN4" s="9"/>
+      <c r="CO4" s="9"/>
+      <c r="CP4" s="9"/>
+      <c r="CQ4" s="9"/>
+      <c r="CR4" s="9"/>
+      <c r="CS4" s="9"/>
+      <c r="CT4" s="9"/>
+      <c r="CU4" s="9"/>
+      <c r="CV4" s="9"/>
+      <c r="CW4" s="9"/>
+      <c r="CX4" s="9"/>
+      <c r="CY4" s="9"/>
+      <c r="CZ4" s="9"/>
+      <c r="DA4" s="9"/>
+      <c r="DB4" s="9"/>
+      <c r="DC4" s="9"/>
+      <c r="DD4" s="9"/>
+      <c r="DE4" s="9"/>
+      <c r="DF4" s="9"/>
+      <c r="DG4" s="9"/>
+      <c r="DH4" s="9"/>
+      <c r="DI4" s="9"/>
+      <c r="DJ4" s="9"/>
+      <c r="DK4" s="9"/>
+      <c r="DL4" s="9"/>
+      <c r="DM4" s="9"/>
+      <c r="DN4" s="9"/>
+      <c r="DO4" s="9"/>
+      <c r="DP4" s="9"/>
+      <c r="DQ4" s="9"/>
+      <c r="DR4" s="9"/>
+      <c r="DS4" s="9"/>
+      <c r="DT4" s="9"/>
+      <c r="DU4" s="9"/>
+      <c r="DV4" s="9"/>
+      <c r="DW4" s="9"/>
+      <c r="DX4" s="9"/>
+      <c r="DY4" s="9"/>
+      <c r="DZ4" s="9"/>
+      <c r="EA4" s="9"/>
+      <c r="EB4" s="9"/>
+      <c r="EC4" s="9"/>
+      <c r="ED4" s="9"/>
+      <c r="EE4" s="9"/>
+      <c r="EF4" s="9"/>
+      <c r="EG4" s="9"/>
+      <c r="EH4" s="9"/>
+      <c r="EI4" s="9"/>
+      <c r="EJ4" s="9"/>
+      <c r="EK4" s="9"/>
+      <c r="EL4" s="9"/>
+      <c r="EM4" s="9"/>
+      <c r="EN4" s="9"/>
+      <c r="EO4" s="9"/>
+      <c r="EP4" s="9"/>
+      <c r="EQ4" s="9"/>
+      <c r="ER4" s="9"/>
+      <c r="ES4" s="9"/>
+      <c r="ET4" s="9"/>
+      <c r="EU4" s="9"/>
+      <c r="EV4" s="9"/>
+      <c r="EW4" s="9"/>
+      <c r="EX4" s="9"/>
+      <c r="EY4" s="9"/>
+      <c r="EZ4" s="9"/>
+      <c r="FA4" s="9"/>
+      <c r="FB4" s="9"/>
+      <c r="FC4" s="9"/>
+      <c r="FD4" s="9"/>
+      <c r="FE4" s="9"/>
+      <c r="FF4" s="9"/>
+      <c r="FG4" s="9"/>
+      <c r="FH4" s="9"/>
+      <c r="FI4" s="9"/>
+      <c r="FJ4" s="9"/>
+      <c r="FK4" s="9"/>
+      <c r="FL4" s="9"/>
+      <c r="FM4" s="9"/>
+      <c r="FN4" s="9"/>
+      <c r="FO4" s="9"/>
+      <c r="FP4" s="9"/>
+      <c r="FQ4" s="9"/>
+      <c r="FR4" s="9"/>
+      <c r="FS4" s="9"/>
+      <c r="FT4" s="9"/>
+      <c r="FU4" s="9"/>
+      <c r="FV4" s="9"/>
+      <c r="FW4" s="9"/>
+      <c r="FX4" s="9"/>
+      <c r="FY4" s="9"/>
+      <c r="FZ4" s="9"/>
+      <c r="GA4" s="9"/>
+      <c r="GB4" s="9"/>
+      <c r="GC4" s="9"/>
+      <c r="GD4" s="9"/>
+      <c r="GE4" s="9"/>
+      <c r="GF4" s="9"/>
+      <c r="GG4" s="9"/>
+      <c r="GH4" s="9"/>
+      <c r="GI4" s="9"/>
+      <c r="GJ4" s="9"/>
+      <c r="GK4" s="9"/>
+      <c r="GL4" s="9"/>
+      <c r="GM4" s="9"/>
+      <c r="GN4" s="9"/>
+      <c r="GO4" s="9"/>
+      <c r="GP4" s="9"/>
+      <c r="GQ4" s="9"/>
+      <c r="GR4" s="9"/>
+      <c r="GS4" s="9"/>
+      <c r="GT4" s="9"/>
+      <c r="GU4" s="9"/>
+      <c r="GV4" s="9"/>
+      <c r="GW4" s="9"/>
+      <c r="GX4" s="9"/>
+      <c r="GY4" s="9"/>
+      <c r="GZ4" s="9"/>
+      <c r="HA4" s="9"/>
+      <c r="HB4" s="9"/>
+      <c r="HC4" s="9"/>
+      <c r="HD4" s="9"/>
+      <c r="HE4" s="9"/>
+      <c r="HF4" s="9"/>
+      <c r="HG4" s="9"/>
+      <c r="HH4" s="9"/>
+      <c r="HI4" s="9"/>
+      <c r="HJ4" s="9"/>
+      <c r="HK4" s="9"/>
+      <c r="HL4" s="9"/>
+      <c r="HM4" s="9"/>
+      <c r="HN4" s="9"/>
+      <c r="HO4" s="9"/>
+      <c r="HP4" s="9"/>
+      <c r="HQ4" s="9"/>
+      <c r="HR4" s="9"/>
+      <c r="HS4" s="9"/>
+      <c r="HT4" s="9"/>
+      <c r="HU4" s="9"/>
+      <c r="HV4" s="9"/>
+      <c r="HW4" s="9"/>
+      <c r="HX4" s="9"/>
+      <c r="HY4" s="9"/>
+      <c r="HZ4" s="9"/>
+      <c r="IA4" s="9"/>
+      <c r="IB4" s="9"/>
+      <c r="IC4" s="9"/>
+      <c r="ID4" s="9"/>
+      <c r="IE4" s="9"/>
+      <c r="IF4" s="9"/>
+      <c r="IG4" s="9"/>
+      <c r="IH4" s="9"/>
+      <c r="II4" s="9"/>
+      <c r="IJ4" s="9"/>
+      <c r="IK4" s="9"/>
+      <c r="IL4" s="9"/>
+      <c r="IM4" s="9"/>
+      <c r="IN4" s="9"/>
+      <c r="IO4" s="9"/>
+      <c r="IP4" s="9"/>
+      <c r="IQ4" s="9"/>
+      <c r="IR4" s="9"/>
+      <c r="IS4" s="9"/>
+      <c r="IT4" s="9"/>
+      <c r="IU4" s="10"/>
     </row>
     <row r="5" ht="13.65" customHeight="1">
       <c r="A5" s="8"/>
@@ -1808,7 +2768,247 @@
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
-      <c r="O5" s="10"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9"/>
+      <c r="AD5" s="9"/>
+      <c r="AE5" s="9"/>
+      <c r="AF5" s="9"/>
+      <c r="AG5" s="9"/>
+      <c r="AH5" s="9"/>
+      <c r="AI5" s="9"/>
+      <c r="AJ5" s="9"/>
+      <c r="AK5" s="9"/>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+      <c r="BI5" s="9"/>
+      <c r="BJ5" s="9"/>
+      <c r="BK5" s="9"/>
+      <c r="BL5" s="9"/>
+      <c r="BM5" s="9"/>
+      <c r="BN5" s="9"/>
+      <c r="BO5" s="9"/>
+      <c r="BP5" s="9"/>
+      <c r="BQ5" s="9"/>
+      <c r="BR5" s="9"/>
+      <c r="BS5" s="9"/>
+      <c r="BT5" s="9"/>
+      <c r="BU5" s="9"/>
+      <c r="BV5" s="9"/>
+      <c r="BW5" s="9"/>
+      <c r="BX5" s="9"/>
+      <c r="BY5" s="9"/>
+      <c r="BZ5" s="9"/>
+      <c r="CA5" s="9"/>
+      <c r="CB5" s="9"/>
+      <c r="CC5" s="9"/>
+      <c r="CD5" s="9"/>
+      <c r="CE5" s="9"/>
+      <c r="CF5" s="9"/>
+      <c r="CG5" s="9"/>
+      <c r="CH5" s="9"/>
+      <c r="CI5" s="9"/>
+      <c r="CJ5" s="9"/>
+      <c r="CK5" s="9"/>
+      <c r="CL5" s="9"/>
+      <c r="CM5" s="9"/>
+      <c r="CN5" s="9"/>
+      <c r="CO5" s="9"/>
+      <c r="CP5" s="9"/>
+      <c r="CQ5" s="9"/>
+      <c r="CR5" s="9"/>
+      <c r="CS5" s="9"/>
+      <c r="CT5" s="9"/>
+      <c r="CU5" s="9"/>
+      <c r="CV5" s="9"/>
+      <c r="CW5" s="9"/>
+      <c r="CX5" s="9"/>
+      <c r="CY5" s="9"/>
+      <c r="CZ5" s="9"/>
+      <c r="DA5" s="9"/>
+      <c r="DB5" s="9"/>
+      <c r="DC5" s="9"/>
+      <c r="DD5" s="9"/>
+      <c r="DE5" s="9"/>
+      <c r="DF5" s="9"/>
+      <c r="DG5" s="9"/>
+      <c r="DH5" s="9"/>
+      <c r="DI5" s="9"/>
+      <c r="DJ5" s="9"/>
+      <c r="DK5" s="9"/>
+      <c r="DL5" s="9"/>
+      <c r="DM5" s="9"/>
+      <c r="DN5" s="9"/>
+      <c r="DO5" s="9"/>
+      <c r="DP5" s="9"/>
+      <c r="DQ5" s="9"/>
+      <c r="DR5" s="9"/>
+      <c r="DS5" s="9"/>
+      <c r="DT5" s="9"/>
+      <c r="DU5" s="9"/>
+      <c r="DV5" s="9"/>
+      <c r="DW5" s="9"/>
+      <c r="DX5" s="9"/>
+      <c r="DY5" s="9"/>
+      <c r="DZ5" s="9"/>
+      <c r="EA5" s="9"/>
+      <c r="EB5" s="9"/>
+      <c r="EC5" s="9"/>
+      <c r="ED5" s="9"/>
+      <c r="EE5" s="9"/>
+      <c r="EF5" s="9"/>
+      <c r="EG5" s="9"/>
+      <c r="EH5" s="9"/>
+      <c r="EI5" s="9"/>
+      <c r="EJ5" s="9"/>
+      <c r="EK5" s="9"/>
+      <c r="EL5" s="9"/>
+      <c r="EM5" s="9"/>
+      <c r="EN5" s="9"/>
+      <c r="EO5" s="9"/>
+      <c r="EP5" s="9"/>
+      <c r="EQ5" s="9"/>
+      <c r="ER5" s="9"/>
+      <c r="ES5" s="9"/>
+      <c r="ET5" s="9"/>
+      <c r="EU5" s="9"/>
+      <c r="EV5" s="9"/>
+      <c r="EW5" s="9"/>
+      <c r="EX5" s="9"/>
+      <c r="EY5" s="9"/>
+      <c r="EZ5" s="9"/>
+      <c r="FA5" s="9"/>
+      <c r="FB5" s="9"/>
+      <c r="FC5" s="9"/>
+      <c r="FD5" s="9"/>
+      <c r="FE5" s="9"/>
+      <c r="FF5" s="9"/>
+      <c r="FG5" s="9"/>
+      <c r="FH5" s="9"/>
+      <c r="FI5" s="9"/>
+      <c r="FJ5" s="9"/>
+      <c r="FK5" s="9"/>
+      <c r="FL5" s="9"/>
+      <c r="FM5" s="9"/>
+      <c r="FN5" s="9"/>
+      <c r="FO5" s="9"/>
+      <c r="FP5" s="9"/>
+      <c r="FQ5" s="9"/>
+      <c r="FR5" s="9"/>
+      <c r="FS5" s="9"/>
+      <c r="FT5" s="9"/>
+      <c r="FU5" s="9"/>
+      <c r="FV5" s="9"/>
+      <c r="FW5" s="9"/>
+      <c r="FX5" s="9"/>
+      <c r="FY5" s="9"/>
+      <c r="FZ5" s="9"/>
+      <c r="GA5" s="9"/>
+      <c r="GB5" s="9"/>
+      <c r="GC5" s="9"/>
+      <c r="GD5" s="9"/>
+      <c r="GE5" s="9"/>
+      <c r="GF5" s="9"/>
+      <c r="GG5" s="9"/>
+      <c r="GH5" s="9"/>
+      <c r="GI5" s="9"/>
+      <c r="GJ5" s="9"/>
+      <c r="GK5" s="9"/>
+      <c r="GL5" s="9"/>
+      <c r="GM5" s="9"/>
+      <c r="GN5" s="9"/>
+      <c r="GO5" s="9"/>
+      <c r="GP5" s="9"/>
+      <c r="GQ5" s="9"/>
+      <c r="GR5" s="9"/>
+      <c r="GS5" s="9"/>
+      <c r="GT5" s="9"/>
+      <c r="GU5" s="9"/>
+      <c r="GV5" s="9"/>
+      <c r="GW5" s="9"/>
+      <c r="GX5" s="9"/>
+      <c r="GY5" s="9"/>
+      <c r="GZ5" s="9"/>
+      <c r="HA5" s="9"/>
+      <c r="HB5" s="9"/>
+      <c r="HC5" s="9"/>
+      <c r="HD5" s="9"/>
+      <c r="HE5" s="9"/>
+      <c r="HF5" s="9"/>
+      <c r="HG5" s="9"/>
+      <c r="HH5" s="9"/>
+      <c r="HI5" s="9"/>
+      <c r="HJ5" s="9"/>
+      <c r="HK5" s="9"/>
+      <c r="HL5" s="9"/>
+      <c r="HM5" s="9"/>
+      <c r="HN5" s="9"/>
+      <c r="HO5" s="9"/>
+      <c r="HP5" s="9"/>
+      <c r="HQ5" s="9"/>
+      <c r="HR5" s="9"/>
+      <c r="HS5" s="9"/>
+      <c r="HT5" s="9"/>
+      <c r="HU5" s="9"/>
+      <c r="HV5" s="9"/>
+      <c r="HW5" s="9"/>
+      <c r="HX5" s="9"/>
+      <c r="HY5" s="9"/>
+      <c r="HZ5" s="9"/>
+      <c r="IA5" s="9"/>
+      <c r="IB5" s="9"/>
+      <c r="IC5" s="9"/>
+      <c r="ID5" s="9"/>
+      <c r="IE5" s="9"/>
+      <c r="IF5" s="9"/>
+      <c r="IG5" s="9"/>
+      <c r="IH5" s="9"/>
+      <c r="II5" s="9"/>
+      <c r="IJ5" s="9"/>
+      <c r="IK5" s="9"/>
+      <c r="IL5" s="9"/>
+      <c r="IM5" s="9"/>
+      <c r="IN5" s="9"/>
+      <c r="IO5" s="9"/>
+      <c r="IP5" s="9"/>
+      <c r="IQ5" s="9"/>
+      <c r="IR5" s="9"/>
+      <c r="IS5" s="9"/>
+      <c r="IT5" s="9"/>
+      <c r="IU5" s="10"/>
     </row>
     <row r="6" ht="13.65" customHeight="1">
       <c r="A6" s="8"/>
@@ -1825,7 +3025,247 @@
       <c r="L6" s="9"/>
       <c r="M6" s="9"/>
       <c r="N6" s="9"/>
-      <c r="O6" s="10"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9"/>
+      <c r="AD6" s="9"/>
+      <c r="AE6" s="9"/>
+      <c r="AF6" s="9"/>
+      <c r="AG6" s="9"/>
+      <c r="AH6" s="9"/>
+      <c r="AI6" s="9"/>
+      <c r="AJ6" s="9"/>
+      <c r="AK6" s="9"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+      <c r="BI6" s="9"/>
+      <c r="BJ6" s="9"/>
+      <c r="BK6" s="9"/>
+      <c r="BL6" s="9"/>
+      <c r="BM6" s="9"/>
+      <c r="BN6" s="9"/>
+      <c r="BO6" s="9"/>
+      <c r="BP6" s="9"/>
+      <c r="BQ6" s="9"/>
+      <c r="BR6" s="9"/>
+      <c r="BS6" s="9"/>
+      <c r="BT6" s="9"/>
+      <c r="BU6" s="9"/>
+      <c r="BV6" s="9"/>
+      <c r="BW6" s="9"/>
+      <c r="BX6" s="9"/>
+      <c r="BY6" s="9"/>
+      <c r="BZ6" s="9"/>
+      <c r="CA6" s="9"/>
+      <c r="CB6" s="9"/>
+      <c r="CC6" s="9"/>
+      <c r="CD6" s="9"/>
+      <c r="CE6" s="9"/>
+      <c r="CF6" s="9"/>
+      <c r="CG6" s="9"/>
+      <c r="CH6" s="9"/>
+      <c r="CI6" s="9"/>
+      <c r="CJ6" s="9"/>
+      <c r="CK6" s="9"/>
+      <c r="CL6" s="9"/>
+      <c r="CM6" s="9"/>
+      <c r="CN6" s="9"/>
+      <c r="CO6" s="9"/>
+      <c r="CP6" s="9"/>
+      <c r="CQ6" s="9"/>
+      <c r="CR6" s="9"/>
+      <c r="CS6" s="9"/>
+      <c r="CT6" s="9"/>
+      <c r="CU6" s="9"/>
+      <c r="CV6" s="9"/>
+      <c r="CW6" s="9"/>
+      <c r="CX6" s="9"/>
+      <c r="CY6" s="9"/>
+      <c r="CZ6" s="9"/>
+      <c r="DA6" s="9"/>
+      <c r="DB6" s="9"/>
+      <c r="DC6" s="9"/>
+      <c r="DD6" s="9"/>
+      <c r="DE6" s="9"/>
+      <c r="DF6" s="9"/>
+      <c r="DG6" s="9"/>
+      <c r="DH6" s="9"/>
+      <c r="DI6" s="9"/>
+      <c r="DJ6" s="9"/>
+      <c r="DK6" s="9"/>
+      <c r="DL6" s="9"/>
+      <c r="DM6" s="9"/>
+      <c r="DN6" s="9"/>
+      <c r="DO6" s="9"/>
+      <c r="DP6" s="9"/>
+      <c r="DQ6" s="9"/>
+      <c r="DR6" s="9"/>
+      <c r="DS6" s="9"/>
+      <c r="DT6" s="9"/>
+      <c r="DU6" s="9"/>
+      <c r="DV6" s="9"/>
+      <c r="DW6" s="9"/>
+      <c r="DX6" s="9"/>
+      <c r="DY6" s="9"/>
+      <c r="DZ6" s="9"/>
+      <c r="EA6" s="9"/>
+      <c r="EB6" s="9"/>
+      <c r="EC6" s="9"/>
+      <c r="ED6" s="9"/>
+      <c r="EE6" s="9"/>
+      <c r="EF6" s="9"/>
+      <c r="EG6" s="9"/>
+      <c r="EH6" s="9"/>
+      <c r="EI6" s="9"/>
+      <c r="EJ6" s="9"/>
+      <c r="EK6" s="9"/>
+      <c r="EL6" s="9"/>
+      <c r="EM6" s="9"/>
+      <c r="EN6" s="9"/>
+      <c r="EO6" s="9"/>
+      <c r="EP6" s="9"/>
+      <c r="EQ6" s="9"/>
+      <c r="ER6" s="9"/>
+      <c r="ES6" s="9"/>
+      <c r="ET6" s="9"/>
+      <c r="EU6" s="9"/>
+      <c r="EV6" s="9"/>
+      <c r="EW6" s="9"/>
+      <c r="EX6" s="9"/>
+      <c r="EY6" s="9"/>
+      <c r="EZ6" s="9"/>
+      <c r="FA6" s="9"/>
+      <c r="FB6" s="9"/>
+      <c r="FC6" s="9"/>
+      <c r="FD6" s="9"/>
+      <c r="FE6" s="9"/>
+      <c r="FF6" s="9"/>
+      <c r="FG6" s="9"/>
+      <c r="FH6" s="9"/>
+      <c r="FI6" s="9"/>
+      <c r="FJ6" s="9"/>
+      <c r="FK6" s="9"/>
+      <c r="FL6" s="9"/>
+      <c r="FM6" s="9"/>
+      <c r="FN6" s="9"/>
+      <c r="FO6" s="9"/>
+      <c r="FP6" s="9"/>
+      <c r="FQ6" s="9"/>
+      <c r="FR6" s="9"/>
+      <c r="FS6" s="9"/>
+      <c r="FT6" s="9"/>
+      <c r="FU6" s="9"/>
+      <c r="FV6" s="9"/>
+      <c r="FW6" s="9"/>
+      <c r="FX6" s="9"/>
+      <c r="FY6" s="9"/>
+      <c r="FZ6" s="9"/>
+      <c r="GA6" s="9"/>
+      <c r="GB6" s="9"/>
+      <c r="GC6" s="9"/>
+      <c r="GD6" s="9"/>
+      <c r="GE6" s="9"/>
+      <c r="GF6" s="9"/>
+      <c r="GG6" s="9"/>
+      <c r="GH6" s="9"/>
+      <c r="GI6" s="9"/>
+      <c r="GJ6" s="9"/>
+      <c r="GK6" s="9"/>
+      <c r="GL6" s="9"/>
+      <c r="GM6" s="9"/>
+      <c r="GN6" s="9"/>
+      <c r="GO6" s="9"/>
+      <c r="GP6" s="9"/>
+      <c r="GQ6" s="9"/>
+      <c r="GR6" s="9"/>
+      <c r="GS6" s="9"/>
+      <c r="GT6" s="9"/>
+      <c r="GU6" s="9"/>
+      <c r="GV6" s="9"/>
+      <c r="GW6" s="9"/>
+      <c r="GX6" s="9"/>
+      <c r="GY6" s="9"/>
+      <c r="GZ6" s="9"/>
+      <c r="HA6" s="9"/>
+      <c r="HB6" s="9"/>
+      <c r="HC6" s="9"/>
+      <c r="HD6" s="9"/>
+      <c r="HE6" s="9"/>
+      <c r="HF6" s="9"/>
+      <c r="HG6" s="9"/>
+      <c r="HH6" s="9"/>
+      <c r="HI6" s="9"/>
+      <c r="HJ6" s="9"/>
+      <c r="HK6" s="9"/>
+      <c r="HL6" s="9"/>
+      <c r="HM6" s="9"/>
+      <c r="HN6" s="9"/>
+      <c r="HO6" s="9"/>
+      <c r="HP6" s="9"/>
+      <c r="HQ6" s="9"/>
+      <c r="HR6" s="9"/>
+      <c r="HS6" s="9"/>
+      <c r="HT6" s="9"/>
+      <c r="HU6" s="9"/>
+      <c r="HV6" s="9"/>
+      <c r="HW6" s="9"/>
+      <c r="HX6" s="9"/>
+      <c r="HY6" s="9"/>
+      <c r="HZ6" s="9"/>
+      <c r="IA6" s="9"/>
+      <c r="IB6" s="9"/>
+      <c r="IC6" s="9"/>
+      <c r="ID6" s="9"/>
+      <c r="IE6" s="9"/>
+      <c r="IF6" s="9"/>
+      <c r="IG6" s="9"/>
+      <c r="IH6" s="9"/>
+      <c r="II6" s="9"/>
+      <c r="IJ6" s="9"/>
+      <c r="IK6" s="9"/>
+      <c r="IL6" s="9"/>
+      <c r="IM6" s="9"/>
+      <c r="IN6" s="9"/>
+      <c r="IO6" s="9"/>
+      <c r="IP6" s="9"/>
+      <c r="IQ6" s="9"/>
+      <c r="IR6" s="9"/>
+      <c r="IS6" s="9"/>
+      <c r="IT6" s="9"/>
+      <c r="IU6" s="10"/>
     </row>
     <row r="7" ht="13.65" customHeight="1">
       <c r="A7" s="8"/>
@@ -1842,7 +3282,247 @@
       <c r="L7" s="9"/>
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
-      <c r="O7" s="10"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="9"/>
+      <c r="AC7" s="9"/>
+      <c r="AD7" s="9"/>
+      <c r="AE7" s="9"/>
+      <c r="AF7" s="9"/>
+      <c r="AG7" s="9"/>
+      <c r="AH7" s="9"/>
+      <c r="AI7" s="9"/>
+      <c r="AJ7" s="9"/>
+      <c r="AK7" s="9"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+      <c r="BI7" s="9"/>
+      <c r="BJ7" s="9"/>
+      <c r="BK7" s="9"/>
+      <c r="BL7" s="9"/>
+      <c r="BM7" s="9"/>
+      <c r="BN7" s="9"/>
+      <c r="BO7" s="9"/>
+      <c r="BP7" s="9"/>
+      <c r="BQ7" s="9"/>
+      <c r="BR7" s="9"/>
+      <c r="BS7" s="9"/>
+      <c r="BT7" s="9"/>
+      <c r="BU7" s="9"/>
+      <c r="BV7" s="9"/>
+      <c r="BW7" s="9"/>
+      <c r="BX7" s="9"/>
+      <c r="BY7" s="9"/>
+      <c r="BZ7" s="9"/>
+      <c r="CA7" s="9"/>
+      <c r="CB7" s="9"/>
+      <c r="CC7" s="9"/>
+      <c r="CD7" s="9"/>
+      <c r="CE7" s="9"/>
+      <c r="CF7" s="9"/>
+      <c r="CG7" s="9"/>
+      <c r="CH7" s="9"/>
+      <c r="CI7" s="9"/>
+      <c r="CJ7" s="9"/>
+      <c r="CK7" s="9"/>
+      <c r="CL7" s="9"/>
+      <c r="CM7" s="9"/>
+      <c r="CN7" s="9"/>
+      <c r="CO7" s="9"/>
+      <c r="CP7" s="9"/>
+      <c r="CQ7" s="9"/>
+      <c r="CR7" s="9"/>
+      <c r="CS7" s="9"/>
+      <c r="CT7" s="9"/>
+      <c r="CU7" s="9"/>
+      <c r="CV7" s="9"/>
+      <c r="CW7" s="9"/>
+      <c r="CX7" s="9"/>
+      <c r="CY7" s="9"/>
+      <c r="CZ7" s="9"/>
+      <c r="DA7" s="9"/>
+      <c r="DB7" s="9"/>
+      <c r="DC7" s="9"/>
+      <c r="DD7" s="9"/>
+      <c r="DE7" s="9"/>
+      <c r="DF7" s="9"/>
+      <c r="DG7" s="9"/>
+      <c r="DH7" s="9"/>
+      <c r="DI7" s="9"/>
+      <c r="DJ7" s="9"/>
+      <c r="DK7" s="9"/>
+      <c r="DL7" s="9"/>
+      <c r="DM7" s="9"/>
+      <c r="DN7" s="9"/>
+      <c r="DO7" s="9"/>
+      <c r="DP7" s="9"/>
+      <c r="DQ7" s="9"/>
+      <c r="DR7" s="9"/>
+      <c r="DS7" s="9"/>
+      <c r="DT7" s="9"/>
+      <c r="DU7" s="9"/>
+      <c r="DV7" s="9"/>
+      <c r="DW7" s="9"/>
+      <c r="DX7" s="9"/>
+      <c r="DY7" s="9"/>
+      <c r="DZ7" s="9"/>
+      <c r="EA7" s="9"/>
+      <c r="EB7" s="9"/>
+      <c r="EC7" s="9"/>
+      <c r="ED7" s="9"/>
+      <c r="EE7" s="9"/>
+      <c r="EF7" s="9"/>
+      <c r="EG7" s="9"/>
+      <c r="EH7" s="9"/>
+      <c r="EI7" s="9"/>
+      <c r="EJ7" s="9"/>
+      <c r="EK7" s="9"/>
+      <c r="EL7" s="9"/>
+      <c r="EM7" s="9"/>
+      <c r="EN7" s="9"/>
+      <c r="EO7" s="9"/>
+      <c r="EP7" s="9"/>
+      <c r="EQ7" s="9"/>
+      <c r="ER7" s="9"/>
+      <c r="ES7" s="9"/>
+      <c r="ET7" s="9"/>
+      <c r="EU7" s="9"/>
+      <c r="EV7" s="9"/>
+      <c r="EW7" s="9"/>
+      <c r="EX7" s="9"/>
+      <c r="EY7" s="9"/>
+      <c r="EZ7" s="9"/>
+      <c r="FA7" s="9"/>
+      <c r="FB7" s="9"/>
+      <c r="FC7" s="9"/>
+      <c r="FD7" s="9"/>
+      <c r="FE7" s="9"/>
+      <c r="FF7" s="9"/>
+      <c r="FG7" s="9"/>
+      <c r="FH7" s="9"/>
+      <c r="FI7" s="9"/>
+      <c r="FJ7" s="9"/>
+      <c r="FK7" s="9"/>
+      <c r="FL7" s="9"/>
+      <c r="FM7" s="9"/>
+      <c r="FN7" s="9"/>
+      <c r="FO7" s="9"/>
+      <c r="FP7" s="9"/>
+      <c r="FQ7" s="9"/>
+      <c r="FR7" s="9"/>
+      <c r="FS7" s="9"/>
+      <c r="FT7" s="9"/>
+      <c r="FU7" s="9"/>
+      <c r="FV7" s="9"/>
+      <c r="FW7" s="9"/>
+      <c r="FX7" s="9"/>
+      <c r="FY7" s="9"/>
+      <c r="FZ7" s="9"/>
+      <c r="GA7" s="9"/>
+      <c r="GB7" s="9"/>
+      <c r="GC7" s="9"/>
+      <c r="GD7" s="9"/>
+      <c r="GE7" s="9"/>
+      <c r="GF7" s="9"/>
+      <c r="GG7" s="9"/>
+      <c r="GH7" s="9"/>
+      <c r="GI7" s="9"/>
+      <c r="GJ7" s="9"/>
+      <c r="GK7" s="9"/>
+      <c r="GL7" s="9"/>
+      <c r="GM7" s="9"/>
+      <c r="GN7" s="9"/>
+      <c r="GO7" s="9"/>
+      <c r="GP7" s="9"/>
+      <c r="GQ7" s="9"/>
+      <c r="GR7" s="9"/>
+      <c r="GS7" s="9"/>
+      <c r="GT7" s="9"/>
+      <c r="GU7" s="9"/>
+      <c r="GV7" s="9"/>
+      <c r="GW7" s="9"/>
+      <c r="GX7" s="9"/>
+      <c r="GY7" s="9"/>
+      <c r="GZ7" s="9"/>
+      <c r="HA7" s="9"/>
+      <c r="HB7" s="9"/>
+      <c r="HC7" s="9"/>
+      <c r="HD7" s="9"/>
+      <c r="HE7" s="9"/>
+      <c r="HF7" s="9"/>
+      <c r="HG7" s="9"/>
+      <c r="HH7" s="9"/>
+      <c r="HI7" s="9"/>
+      <c r="HJ7" s="9"/>
+      <c r="HK7" s="9"/>
+      <c r="HL7" s="9"/>
+      <c r="HM7" s="9"/>
+      <c r="HN7" s="9"/>
+      <c r="HO7" s="9"/>
+      <c r="HP7" s="9"/>
+      <c r="HQ7" s="9"/>
+      <c r="HR7" s="9"/>
+      <c r="HS7" s="9"/>
+      <c r="HT7" s="9"/>
+      <c r="HU7" s="9"/>
+      <c r="HV7" s="9"/>
+      <c r="HW7" s="9"/>
+      <c r="HX7" s="9"/>
+      <c r="HY7" s="9"/>
+      <c r="HZ7" s="9"/>
+      <c r="IA7" s="9"/>
+      <c r="IB7" s="9"/>
+      <c r="IC7" s="9"/>
+      <c r="ID7" s="9"/>
+      <c r="IE7" s="9"/>
+      <c r="IF7" s="9"/>
+      <c r="IG7" s="9"/>
+      <c r="IH7" s="9"/>
+      <c r="II7" s="9"/>
+      <c r="IJ7" s="9"/>
+      <c r="IK7" s="9"/>
+      <c r="IL7" s="9"/>
+      <c r="IM7" s="9"/>
+      <c r="IN7" s="9"/>
+      <c r="IO7" s="9"/>
+      <c r="IP7" s="9"/>
+      <c r="IQ7" s="9"/>
+      <c r="IR7" s="9"/>
+      <c r="IS7" s="9"/>
+      <c r="IT7" s="9"/>
+      <c r="IU7" s="10"/>
     </row>
     <row r="8" ht="13.65" customHeight="1">
       <c r="A8" s="8"/>
@@ -1859,7 +3539,247 @@
       <c r="L8" s="9"/>
       <c r="M8" s="9"/>
       <c r="N8" s="9"/>
-      <c r="O8" s="10"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="9"/>
+      <c r="AF8" s="9"/>
+      <c r="AG8" s="9"/>
+      <c r="AH8" s="9"/>
+      <c r="AI8" s="9"/>
+      <c r="AJ8" s="9"/>
+      <c r="AK8" s="9"/>
+      <c r="AL8" s="9"/>
+      <c r="AM8" s="9"/>
+      <c r="AN8" s="9"/>
+      <c r="AO8" s="9"/>
+      <c r="AP8" s="9"/>
+      <c r="AQ8" s="9"/>
+      <c r="AR8" s="9"/>
+      <c r="AS8" s="9"/>
+      <c r="AT8" s="9"/>
+      <c r="AU8" s="9"/>
+      <c r="AV8" s="9"/>
+      <c r="AW8" s="9"/>
+      <c r="AX8" s="9"/>
+      <c r="AY8" s="9"/>
+      <c r="AZ8" s="9"/>
+      <c r="BA8" s="9"/>
+      <c r="BB8" s="9"/>
+      <c r="BC8" s="9"/>
+      <c r="BD8" s="9"/>
+      <c r="BE8" s="9"/>
+      <c r="BF8" s="9"/>
+      <c r="BG8" s="9"/>
+      <c r="BH8" s="9"/>
+      <c r="BI8" s="9"/>
+      <c r="BJ8" s="9"/>
+      <c r="BK8" s="9"/>
+      <c r="BL8" s="9"/>
+      <c r="BM8" s="9"/>
+      <c r="BN8" s="9"/>
+      <c r="BO8" s="9"/>
+      <c r="BP8" s="9"/>
+      <c r="BQ8" s="9"/>
+      <c r="BR8" s="9"/>
+      <c r="BS8" s="9"/>
+      <c r="BT8" s="9"/>
+      <c r="BU8" s="9"/>
+      <c r="BV8" s="9"/>
+      <c r="BW8" s="9"/>
+      <c r="BX8" s="9"/>
+      <c r="BY8" s="9"/>
+      <c r="BZ8" s="9"/>
+      <c r="CA8" s="9"/>
+      <c r="CB8" s="9"/>
+      <c r="CC8" s="9"/>
+      <c r="CD8" s="9"/>
+      <c r="CE8" s="9"/>
+      <c r="CF8" s="9"/>
+      <c r="CG8" s="9"/>
+      <c r="CH8" s="9"/>
+      <c r="CI8" s="9"/>
+      <c r="CJ8" s="9"/>
+      <c r="CK8" s="9"/>
+      <c r="CL8" s="9"/>
+      <c r="CM8" s="9"/>
+      <c r="CN8" s="9"/>
+      <c r="CO8" s="9"/>
+      <c r="CP8" s="9"/>
+      <c r="CQ8" s="9"/>
+      <c r="CR8" s="9"/>
+      <c r="CS8" s="9"/>
+      <c r="CT8" s="9"/>
+      <c r="CU8" s="9"/>
+      <c r="CV8" s="9"/>
+      <c r="CW8" s="9"/>
+      <c r="CX8" s="9"/>
+      <c r="CY8" s="9"/>
+      <c r="CZ8" s="9"/>
+      <c r="DA8" s="9"/>
+      <c r="DB8" s="9"/>
+      <c r="DC8" s="9"/>
+      <c r="DD8" s="9"/>
+      <c r="DE8" s="9"/>
+      <c r="DF8" s="9"/>
+      <c r="DG8" s="9"/>
+      <c r="DH8" s="9"/>
+      <c r="DI8" s="9"/>
+      <c r="DJ8" s="9"/>
+      <c r="DK8" s="9"/>
+      <c r="DL8" s="9"/>
+      <c r="DM8" s="9"/>
+      <c r="DN8" s="9"/>
+      <c r="DO8" s="9"/>
+      <c r="DP8" s="9"/>
+      <c r="DQ8" s="9"/>
+      <c r="DR8" s="9"/>
+      <c r="DS8" s="9"/>
+      <c r="DT8" s="9"/>
+      <c r="DU8" s="9"/>
+      <c r="DV8" s="9"/>
+      <c r="DW8" s="9"/>
+      <c r="DX8" s="9"/>
+      <c r="DY8" s="9"/>
+      <c r="DZ8" s="9"/>
+      <c r="EA8" s="9"/>
+      <c r="EB8" s="9"/>
+      <c r="EC8" s="9"/>
+      <c r="ED8" s="9"/>
+      <c r="EE8" s="9"/>
+      <c r="EF8" s="9"/>
+      <c r="EG8" s="9"/>
+      <c r="EH8" s="9"/>
+      <c r="EI8" s="9"/>
+      <c r="EJ8" s="9"/>
+      <c r="EK8" s="9"/>
+      <c r="EL8" s="9"/>
+      <c r="EM8" s="9"/>
+      <c r="EN8" s="9"/>
+      <c r="EO8" s="9"/>
+      <c r="EP8" s="9"/>
+      <c r="EQ8" s="9"/>
+      <c r="ER8" s="9"/>
+      <c r="ES8" s="9"/>
+      <c r="ET8" s="9"/>
+      <c r="EU8" s="9"/>
+      <c r="EV8" s="9"/>
+      <c r="EW8" s="9"/>
+      <c r="EX8" s="9"/>
+      <c r="EY8" s="9"/>
+      <c r="EZ8" s="9"/>
+      <c r="FA8" s="9"/>
+      <c r="FB8" s="9"/>
+      <c r="FC8" s="9"/>
+      <c r="FD8" s="9"/>
+      <c r="FE8" s="9"/>
+      <c r="FF8" s="9"/>
+      <c r="FG8" s="9"/>
+      <c r="FH8" s="9"/>
+      <c r="FI8" s="9"/>
+      <c r="FJ8" s="9"/>
+      <c r="FK8" s="9"/>
+      <c r="FL8" s="9"/>
+      <c r="FM8" s="9"/>
+      <c r="FN8" s="9"/>
+      <c r="FO8" s="9"/>
+      <c r="FP8" s="9"/>
+      <c r="FQ8" s="9"/>
+      <c r="FR8" s="9"/>
+      <c r="FS8" s="9"/>
+      <c r="FT8" s="9"/>
+      <c r="FU8" s="9"/>
+      <c r="FV8" s="9"/>
+      <c r="FW8" s="9"/>
+      <c r="FX8" s="9"/>
+      <c r="FY8" s="9"/>
+      <c r="FZ8" s="9"/>
+      <c r="GA8" s="9"/>
+      <c r="GB8" s="9"/>
+      <c r="GC8" s="9"/>
+      <c r="GD8" s="9"/>
+      <c r="GE8" s="9"/>
+      <c r="GF8" s="9"/>
+      <c r="GG8" s="9"/>
+      <c r="GH8" s="9"/>
+      <c r="GI8" s="9"/>
+      <c r="GJ8" s="9"/>
+      <c r="GK8" s="9"/>
+      <c r="GL8" s="9"/>
+      <c r="GM8" s="9"/>
+      <c r="GN8" s="9"/>
+      <c r="GO8" s="9"/>
+      <c r="GP8" s="9"/>
+      <c r="GQ8" s="9"/>
+      <c r="GR8" s="9"/>
+      <c r="GS8" s="9"/>
+      <c r="GT8" s="9"/>
+      <c r="GU8" s="9"/>
+      <c r="GV8" s="9"/>
+      <c r="GW8" s="9"/>
+      <c r="GX8" s="9"/>
+      <c r="GY8" s="9"/>
+      <c r="GZ8" s="9"/>
+      <c r="HA8" s="9"/>
+      <c r="HB8" s="9"/>
+      <c r="HC8" s="9"/>
+      <c r="HD8" s="9"/>
+      <c r="HE8" s="9"/>
+      <c r="HF8" s="9"/>
+      <c r="HG8" s="9"/>
+      <c r="HH8" s="9"/>
+      <c r="HI8" s="9"/>
+      <c r="HJ8" s="9"/>
+      <c r="HK8" s="9"/>
+      <c r="HL8" s="9"/>
+      <c r="HM8" s="9"/>
+      <c r="HN8" s="9"/>
+      <c r="HO8" s="9"/>
+      <c r="HP8" s="9"/>
+      <c r="HQ8" s="9"/>
+      <c r="HR8" s="9"/>
+      <c r="HS8" s="9"/>
+      <c r="HT8" s="9"/>
+      <c r="HU8" s="9"/>
+      <c r="HV8" s="9"/>
+      <c r="HW8" s="9"/>
+      <c r="HX8" s="9"/>
+      <c r="HY8" s="9"/>
+      <c r="HZ8" s="9"/>
+      <c r="IA8" s="9"/>
+      <c r="IB8" s="9"/>
+      <c r="IC8" s="9"/>
+      <c r="ID8" s="9"/>
+      <c r="IE8" s="9"/>
+      <c r="IF8" s="9"/>
+      <c r="IG8" s="9"/>
+      <c r="IH8" s="9"/>
+      <c r="II8" s="9"/>
+      <c r="IJ8" s="9"/>
+      <c r="IK8" s="9"/>
+      <c r="IL8" s="9"/>
+      <c r="IM8" s="9"/>
+      <c r="IN8" s="9"/>
+      <c r="IO8" s="9"/>
+      <c r="IP8" s="9"/>
+      <c r="IQ8" s="9"/>
+      <c r="IR8" s="9"/>
+      <c r="IS8" s="9"/>
+      <c r="IT8" s="9"/>
+      <c r="IU8" s="10"/>
     </row>
     <row r="9" ht="13.65" customHeight="1">
       <c r="A9" s="8"/>
@@ -1876,7 +3796,247 @@
       <c r="L9" s="9"/>
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
-      <c r="O9" s="10"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="9"/>
+      <c r="AB9" s="9"/>
+      <c r="AC9" s="9"/>
+      <c r="AD9" s="9"/>
+      <c r="AE9" s="9"/>
+      <c r="AF9" s="9"/>
+      <c r="AG9" s="9"/>
+      <c r="AH9" s="9"/>
+      <c r="AI9" s="9"/>
+      <c r="AJ9" s="9"/>
+      <c r="AK9" s="9"/>
+      <c r="AL9" s="9"/>
+      <c r="AM9" s="9"/>
+      <c r="AN9" s="9"/>
+      <c r="AO9" s="9"/>
+      <c r="AP9" s="9"/>
+      <c r="AQ9" s="9"/>
+      <c r="AR9" s="9"/>
+      <c r="AS9" s="9"/>
+      <c r="AT9" s="9"/>
+      <c r="AU9" s="9"/>
+      <c r="AV9" s="9"/>
+      <c r="AW9" s="9"/>
+      <c r="AX9" s="9"/>
+      <c r="AY9" s="9"/>
+      <c r="AZ9" s="9"/>
+      <c r="BA9" s="9"/>
+      <c r="BB9" s="9"/>
+      <c r="BC9" s="9"/>
+      <c r="BD9" s="9"/>
+      <c r="BE9" s="9"/>
+      <c r="BF9" s="9"/>
+      <c r="BG9" s="9"/>
+      <c r="BH9" s="9"/>
+      <c r="BI9" s="9"/>
+      <c r="BJ9" s="9"/>
+      <c r="BK9" s="9"/>
+      <c r="BL9" s="9"/>
+      <c r="BM9" s="9"/>
+      <c r="BN9" s="9"/>
+      <c r="BO9" s="9"/>
+      <c r="BP9" s="9"/>
+      <c r="BQ9" s="9"/>
+      <c r="BR9" s="9"/>
+      <c r="BS9" s="9"/>
+      <c r="BT9" s="9"/>
+      <c r="BU9" s="9"/>
+      <c r="BV9" s="9"/>
+      <c r="BW9" s="9"/>
+      <c r="BX9" s="9"/>
+      <c r="BY9" s="9"/>
+      <c r="BZ9" s="9"/>
+      <c r="CA9" s="9"/>
+      <c r="CB9" s="9"/>
+      <c r="CC9" s="9"/>
+      <c r="CD9" s="9"/>
+      <c r="CE9" s="9"/>
+      <c r="CF9" s="9"/>
+      <c r="CG9" s="9"/>
+      <c r="CH9" s="9"/>
+      <c r="CI9" s="9"/>
+      <c r="CJ9" s="9"/>
+      <c r="CK9" s="9"/>
+      <c r="CL9" s="9"/>
+      <c r="CM9" s="9"/>
+      <c r="CN9" s="9"/>
+      <c r="CO9" s="9"/>
+      <c r="CP9" s="9"/>
+      <c r="CQ9" s="9"/>
+      <c r="CR9" s="9"/>
+      <c r="CS9" s="9"/>
+      <c r="CT9" s="9"/>
+      <c r="CU9" s="9"/>
+      <c r="CV9" s="9"/>
+      <c r="CW9" s="9"/>
+      <c r="CX9" s="9"/>
+      <c r="CY9" s="9"/>
+      <c r="CZ9" s="9"/>
+      <c r="DA9" s="9"/>
+      <c r="DB9" s="9"/>
+      <c r="DC9" s="9"/>
+      <c r="DD9" s="9"/>
+      <c r="DE9" s="9"/>
+      <c r="DF9" s="9"/>
+      <c r="DG9" s="9"/>
+      <c r="DH9" s="9"/>
+      <c r="DI9" s="9"/>
+      <c r="DJ9" s="9"/>
+      <c r="DK9" s="9"/>
+      <c r="DL9" s="9"/>
+      <c r="DM9" s="9"/>
+      <c r="DN9" s="9"/>
+      <c r="DO9" s="9"/>
+      <c r="DP9" s="9"/>
+      <c r="DQ9" s="9"/>
+      <c r="DR9" s="9"/>
+      <c r="DS9" s="9"/>
+      <c r="DT9" s="9"/>
+      <c r="DU9" s="9"/>
+      <c r="DV9" s="9"/>
+      <c r="DW9" s="9"/>
+      <c r="DX9" s="9"/>
+      <c r="DY9" s="9"/>
+      <c r="DZ9" s="9"/>
+      <c r="EA9" s="9"/>
+      <c r="EB9" s="9"/>
+      <c r="EC9" s="9"/>
+      <c r="ED9" s="9"/>
+      <c r="EE9" s="9"/>
+      <c r="EF9" s="9"/>
+      <c r="EG9" s="9"/>
+      <c r="EH9" s="9"/>
+      <c r="EI9" s="9"/>
+      <c r="EJ9" s="9"/>
+      <c r="EK9" s="9"/>
+      <c r="EL9" s="9"/>
+      <c r="EM9" s="9"/>
+      <c r="EN9" s="9"/>
+      <c r="EO9" s="9"/>
+      <c r="EP9" s="9"/>
+      <c r="EQ9" s="9"/>
+      <c r="ER9" s="9"/>
+      <c r="ES9" s="9"/>
+      <c r="ET9" s="9"/>
+      <c r="EU9" s="9"/>
+      <c r="EV9" s="9"/>
+      <c r="EW9" s="9"/>
+      <c r="EX9" s="9"/>
+      <c r="EY9" s="9"/>
+      <c r="EZ9" s="9"/>
+      <c r="FA9" s="9"/>
+      <c r="FB9" s="9"/>
+      <c r="FC9" s="9"/>
+      <c r="FD9" s="9"/>
+      <c r="FE9" s="9"/>
+      <c r="FF9" s="9"/>
+      <c r="FG9" s="9"/>
+      <c r="FH9" s="9"/>
+      <c r="FI9" s="9"/>
+      <c r="FJ9" s="9"/>
+      <c r="FK9" s="9"/>
+      <c r="FL9" s="9"/>
+      <c r="FM9" s="9"/>
+      <c r="FN9" s="9"/>
+      <c r="FO9" s="9"/>
+      <c r="FP9" s="9"/>
+      <c r="FQ9" s="9"/>
+      <c r="FR9" s="9"/>
+      <c r="FS9" s="9"/>
+      <c r="FT9" s="9"/>
+      <c r="FU9" s="9"/>
+      <c r="FV9" s="9"/>
+      <c r="FW9" s="9"/>
+      <c r="FX9" s="9"/>
+      <c r="FY9" s="9"/>
+      <c r="FZ9" s="9"/>
+      <c r="GA9" s="9"/>
+      <c r="GB9" s="9"/>
+      <c r="GC9" s="9"/>
+      <c r="GD9" s="9"/>
+      <c r="GE9" s="9"/>
+      <c r="GF9" s="9"/>
+      <c r="GG9" s="9"/>
+      <c r="GH9" s="9"/>
+      <c r="GI9" s="9"/>
+      <c r="GJ9" s="9"/>
+      <c r="GK9" s="9"/>
+      <c r="GL9" s="9"/>
+      <c r="GM9" s="9"/>
+      <c r="GN9" s="9"/>
+      <c r="GO9" s="9"/>
+      <c r="GP9" s="9"/>
+      <c r="GQ9" s="9"/>
+      <c r="GR9" s="9"/>
+      <c r="GS9" s="9"/>
+      <c r="GT9" s="9"/>
+      <c r="GU9" s="9"/>
+      <c r="GV9" s="9"/>
+      <c r="GW9" s="9"/>
+      <c r="GX9" s="9"/>
+      <c r="GY9" s="9"/>
+      <c r="GZ9" s="9"/>
+      <c r="HA9" s="9"/>
+      <c r="HB9" s="9"/>
+      <c r="HC9" s="9"/>
+      <c r="HD9" s="9"/>
+      <c r="HE9" s="9"/>
+      <c r="HF9" s="9"/>
+      <c r="HG9" s="9"/>
+      <c r="HH9" s="9"/>
+      <c r="HI9" s="9"/>
+      <c r="HJ9" s="9"/>
+      <c r="HK9" s="9"/>
+      <c r="HL9" s="9"/>
+      <c r="HM9" s="9"/>
+      <c r="HN9" s="9"/>
+      <c r="HO9" s="9"/>
+      <c r="HP9" s="9"/>
+      <c r="HQ9" s="9"/>
+      <c r="HR9" s="9"/>
+      <c r="HS9" s="9"/>
+      <c r="HT9" s="9"/>
+      <c r="HU9" s="9"/>
+      <c r="HV9" s="9"/>
+      <c r="HW9" s="9"/>
+      <c r="HX9" s="9"/>
+      <c r="HY9" s="9"/>
+      <c r="HZ9" s="9"/>
+      <c r="IA9" s="9"/>
+      <c r="IB9" s="9"/>
+      <c r="IC9" s="9"/>
+      <c r="ID9" s="9"/>
+      <c r="IE9" s="9"/>
+      <c r="IF9" s="9"/>
+      <c r="IG9" s="9"/>
+      <c r="IH9" s="9"/>
+      <c r="II9" s="9"/>
+      <c r="IJ9" s="9"/>
+      <c r="IK9" s="9"/>
+      <c r="IL9" s="9"/>
+      <c r="IM9" s="9"/>
+      <c r="IN9" s="9"/>
+      <c r="IO9" s="9"/>
+      <c r="IP9" s="9"/>
+      <c r="IQ9" s="9"/>
+      <c r="IR9" s="9"/>
+      <c r="IS9" s="9"/>
+      <c r="IT9" s="9"/>
+      <c r="IU9" s="10"/>
     </row>
     <row r="10" ht="13.65" customHeight="1">
       <c r="A10" s="11"/>
@@ -1893,7 +4053,247 @@
       <c r="L10" s="12"/>
       <c r="M10" s="12"/>
       <c r="N10" s="12"/>
-      <c r="O10" s="13"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="12"/>
+      <c r="V10" s="12"/>
+      <c r="W10" s="12"/>
+      <c r="X10" s="12"/>
+      <c r="Y10" s="12"/>
+      <c r="Z10" s="12"/>
+      <c r="AA10" s="12"/>
+      <c r="AB10" s="12"/>
+      <c r="AC10" s="12"/>
+      <c r="AD10" s="12"/>
+      <c r="AE10" s="12"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+      <c r="BI10" s="12"/>
+      <c r="BJ10" s="12"/>
+      <c r="BK10" s="12"/>
+      <c r="BL10" s="12"/>
+      <c r="BM10" s="12"/>
+      <c r="BN10" s="12"/>
+      <c r="BO10" s="12"/>
+      <c r="BP10" s="12"/>
+      <c r="BQ10" s="12"/>
+      <c r="BR10" s="12"/>
+      <c r="BS10" s="12"/>
+      <c r="BT10" s="12"/>
+      <c r="BU10" s="12"/>
+      <c r="BV10" s="12"/>
+      <c r="BW10" s="12"/>
+      <c r="BX10" s="12"/>
+      <c r="BY10" s="12"/>
+      <c r="BZ10" s="12"/>
+      <c r="CA10" s="12"/>
+      <c r="CB10" s="12"/>
+      <c r="CC10" s="12"/>
+      <c r="CD10" s="12"/>
+      <c r="CE10" s="12"/>
+      <c r="CF10" s="12"/>
+      <c r="CG10" s="12"/>
+      <c r="CH10" s="12"/>
+      <c r="CI10" s="12"/>
+      <c r="CJ10" s="12"/>
+      <c r="CK10" s="12"/>
+      <c r="CL10" s="12"/>
+      <c r="CM10" s="12"/>
+      <c r="CN10" s="12"/>
+      <c r="CO10" s="12"/>
+      <c r="CP10" s="12"/>
+      <c r="CQ10" s="12"/>
+      <c r="CR10" s="12"/>
+      <c r="CS10" s="12"/>
+      <c r="CT10" s="12"/>
+      <c r="CU10" s="12"/>
+      <c r="CV10" s="12"/>
+      <c r="CW10" s="12"/>
+      <c r="CX10" s="12"/>
+      <c r="CY10" s="12"/>
+      <c r="CZ10" s="12"/>
+      <c r="DA10" s="12"/>
+      <c r="DB10" s="12"/>
+      <c r="DC10" s="12"/>
+      <c r="DD10" s="12"/>
+      <c r="DE10" s="12"/>
+      <c r="DF10" s="12"/>
+      <c r="DG10" s="12"/>
+      <c r="DH10" s="12"/>
+      <c r="DI10" s="12"/>
+      <c r="DJ10" s="12"/>
+      <c r="DK10" s="12"/>
+      <c r="DL10" s="12"/>
+      <c r="DM10" s="12"/>
+      <c r="DN10" s="12"/>
+      <c r="DO10" s="12"/>
+      <c r="DP10" s="12"/>
+      <c r="DQ10" s="12"/>
+      <c r="DR10" s="12"/>
+      <c r="DS10" s="12"/>
+      <c r="DT10" s="12"/>
+      <c r="DU10" s="12"/>
+      <c r="DV10" s="12"/>
+      <c r="DW10" s="12"/>
+      <c r="DX10" s="12"/>
+      <c r="DY10" s="12"/>
+      <c r="DZ10" s="12"/>
+      <c r="EA10" s="12"/>
+      <c r="EB10" s="12"/>
+      <c r="EC10" s="12"/>
+      <c r="ED10" s="12"/>
+      <c r="EE10" s="12"/>
+      <c r="EF10" s="12"/>
+      <c r="EG10" s="12"/>
+      <c r="EH10" s="12"/>
+      <c r="EI10" s="12"/>
+      <c r="EJ10" s="12"/>
+      <c r="EK10" s="12"/>
+      <c r="EL10" s="12"/>
+      <c r="EM10" s="12"/>
+      <c r="EN10" s="12"/>
+      <c r="EO10" s="12"/>
+      <c r="EP10" s="12"/>
+      <c r="EQ10" s="12"/>
+      <c r="ER10" s="12"/>
+      <c r="ES10" s="12"/>
+      <c r="ET10" s="12"/>
+      <c r="EU10" s="12"/>
+      <c r="EV10" s="12"/>
+      <c r="EW10" s="12"/>
+      <c r="EX10" s="12"/>
+      <c r="EY10" s="12"/>
+      <c r="EZ10" s="12"/>
+      <c r="FA10" s="12"/>
+      <c r="FB10" s="12"/>
+      <c r="FC10" s="12"/>
+      <c r="FD10" s="12"/>
+      <c r="FE10" s="12"/>
+      <c r="FF10" s="12"/>
+      <c r="FG10" s="12"/>
+      <c r="FH10" s="12"/>
+      <c r="FI10" s="12"/>
+      <c r="FJ10" s="12"/>
+      <c r="FK10" s="12"/>
+      <c r="FL10" s="12"/>
+      <c r="FM10" s="12"/>
+      <c r="FN10" s="12"/>
+      <c r="FO10" s="12"/>
+      <c r="FP10" s="12"/>
+      <c r="FQ10" s="12"/>
+      <c r="FR10" s="12"/>
+      <c r="FS10" s="12"/>
+      <c r="FT10" s="12"/>
+      <c r="FU10" s="12"/>
+      <c r="FV10" s="12"/>
+      <c r="FW10" s="12"/>
+      <c r="FX10" s="12"/>
+      <c r="FY10" s="12"/>
+      <c r="FZ10" s="12"/>
+      <c r="GA10" s="12"/>
+      <c r="GB10" s="12"/>
+      <c r="GC10" s="12"/>
+      <c r="GD10" s="12"/>
+      <c r="GE10" s="12"/>
+      <c r="GF10" s="12"/>
+      <c r="GG10" s="12"/>
+      <c r="GH10" s="12"/>
+      <c r="GI10" s="12"/>
+      <c r="GJ10" s="12"/>
+      <c r="GK10" s="12"/>
+      <c r="GL10" s="12"/>
+      <c r="GM10" s="12"/>
+      <c r="GN10" s="12"/>
+      <c r="GO10" s="12"/>
+      <c r="GP10" s="12"/>
+      <c r="GQ10" s="12"/>
+      <c r="GR10" s="12"/>
+      <c r="GS10" s="12"/>
+      <c r="GT10" s="12"/>
+      <c r="GU10" s="12"/>
+      <c r="GV10" s="12"/>
+      <c r="GW10" s="12"/>
+      <c r="GX10" s="12"/>
+      <c r="GY10" s="12"/>
+      <c r="GZ10" s="12"/>
+      <c r="HA10" s="12"/>
+      <c r="HB10" s="12"/>
+      <c r="HC10" s="12"/>
+      <c r="HD10" s="12"/>
+      <c r="HE10" s="12"/>
+      <c r="HF10" s="12"/>
+      <c r="HG10" s="12"/>
+      <c r="HH10" s="12"/>
+      <c r="HI10" s="12"/>
+      <c r="HJ10" s="12"/>
+      <c r="HK10" s="12"/>
+      <c r="HL10" s="12"/>
+      <c r="HM10" s="12"/>
+      <c r="HN10" s="12"/>
+      <c r="HO10" s="12"/>
+      <c r="HP10" s="12"/>
+      <c r="HQ10" s="12"/>
+      <c r="HR10" s="12"/>
+      <c r="HS10" s="12"/>
+      <c r="HT10" s="12"/>
+      <c r="HU10" s="12"/>
+      <c r="HV10" s="12"/>
+      <c r="HW10" s="12"/>
+      <c r="HX10" s="12"/>
+      <c r="HY10" s="12"/>
+      <c r="HZ10" s="12"/>
+      <c r="IA10" s="12"/>
+      <c r="IB10" s="12"/>
+      <c r="IC10" s="12"/>
+      <c r="ID10" s="12"/>
+      <c r="IE10" s="12"/>
+      <c r="IF10" s="12"/>
+      <c r="IG10" s="12"/>
+      <c r="IH10" s="12"/>
+      <c r="II10" s="12"/>
+      <c r="IJ10" s="12"/>
+      <c r="IK10" s="12"/>
+      <c r="IL10" s="12"/>
+      <c r="IM10" s="12"/>
+      <c r="IN10" s="12"/>
+      <c r="IO10" s="12"/>
+      <c r="IP10" s="12"/>
+      <c r="IQ10" s="12"/>
+      <c r="IR10" s="12"/>
+      <c r="IS10" s="12"/>
+      <c r="IT10" s="12"/>
+      <c r="IU10" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212706711\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212706711\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{EFC5EA00-700A-4E2B-B35B-08148A2F3CC4}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{6D8ECEBF-94CC-42BB-BBAE-AB6CD640FE99}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>所属院区</t>
   </si>
@@ -233,24 +233,6 @@
     <t>1.在datalist sheet中带有*标记的列为必填项。</t>
   </si>
   <si>
-    <t>2.“科室1”、“科室2”和“科室3”分别表示“科室层级1”、“科室层级2”和“科室层级3”</t>
-  </si>
-  <si>
-    <t>3.角色列需要输入以下角色名称，否则系统找不到相对应的名称，不导入该条数据</t>
-  </si>
-  <si>
-    <t>4.多个角色用逗号分隔(不区分大小写)，多个角色中其中有一条角色名称输入有误，则不导入该条数据</t>
-  </si>
-  <si>
-    <t>5.从系统导出时，会带有UUID列，此列不可更改，系统会根据UUID更新相应字段内容</t>
-  </si>
-  <si>
-    <t>6.可见范围中，输入除本人所在科室以外的其他科室名称，可见多个科室用逗号分隔</t>
-  </si>
-  <si>
-    <t>7.可见范围只支持科室的设定，院区、医院等不支持</t>
-  </si>
-  <si>
     <t>角色名称</t>
   </si>
   <si>
@@ -289,6 +271,34 @@
   </si>
   <si>
     <t>所属集团*</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.角色列需要输入以下角色名称，否则系统找不到相对应的名称，不导入该条数据</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.“科室1”、“科室2”和“科室3”分别表示“科室层级1”、“科室层级2”和“科室层级3”</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.多个角色用逗号分隔(不区分大小写)，多个角色中其中有一条角色名称输入有误，则不导入该条数据</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.从系统导出时，会带有UUID列，此列不可更改，系统会根据UUID更新相应字段内容</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.可见范围中，输入除本人所在科室以外的其他科室名称，可见多个科室用逗号分隔</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.可见范围只支持科室的设定，院区、医院等不支持</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.若角色中同时填入“仅报修权限账号”和其他角色，则只导入“仅报修权限账号”角色</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -349,7 +359,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -493,11 +503,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -532,6 +551,7 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1711,10 +1731,10 @@
   <sheetData>
     <row r="1" spans="1:255" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
@@ -2291,7 +2311,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:IV22"/>
+  <dimension ref="A1:IV23"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="108.7109375" style="11" customWidth="1"/>
@@ -2325,7 +2345,7 @@
     </row>
     <row r="4" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="13"/>
@@ -2334,7 +2354,7 @@
     </row>
     <row r="5" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="13"/>
@@ -2342,17 +2362,17 @@
       <c r="E5" s="13"/>
     </row>
     <row r="6" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="15"/>
+      <c r="A6" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="12"/>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
     </row>
     <row r="7" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="13"/>
@@ -2361,7 +2381,7 @@
     </row>
     <row r="8" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="13"/>
@@ -2370,7 +2390,7 @@
     </row>
     <row r="9" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="13"/>
@@ -2378,40 +2398,40 @@
       <c r="E9" s="13"/>
     </row>
     <row r="10" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="16"/>
-      <c r="B10" s="12"/>
+      <c r="A10" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="15"/>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
     </row>
-    <row r="11" spans="1:5" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="21" t="s">
-        <v>33</v>
-      </c>
+    <row r="11" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="16"/>
       <c r="B11" s="12"/>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
     </row>
-    <row r="12" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="17"/>
+    <row r="12" spans="1:5" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="12"/>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
     </row>
-    <row r="13" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="18"/>
+    <row r="13" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="20"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
     </row>
     <row r="14" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B14" s="18"/>
       <c r="C14" s="13"/>
@@ -2420,7 +2440,7 @@
     </row>
     <row r="15" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B15" s="18"/>
       <c r="C15" s="13"/>
@@ -2429,7 +2449,7 @@
     </row>
     <row r="16" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="13"/>
@@ -2438,7 +2458,7 @@
     </row>
     <row r="17" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B17" s="18"/>
       <c r="C17" s="13"/>
@@ -2447,7 +2467,7 @@
     </row>
     <row r="18" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="14" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B18" s="18"/>
       <c r="C18" s="13"/>
@@ -2456,7 +2476,7 @@
     </row>
     <row r="19" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B19" s="18"/>
       <c r="C19" s="13"/>
@@ -2465,7 +2485,7 @@
     </row>
     <row r="20" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="13"/>
@@ -2474,26 +2494,35 @@
     </row>
     <row r="21" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="14" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
     </row>
-    <row r="22" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="15"/>
+        <v>36</v>
+      </c>
+      <c r="B22" s="18"/>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
     </row>
+    <row r="23" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="15"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212706711\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{6D8ECEBF-94CC-42BB-BBAE-AB6CD640FE99}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{C79B8DB6-6162-476A-AF1A-F2445909CCB5}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -359,7 +359,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -439,19 +439,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="11"/>
       </left>
@@ -479,44 +466,24 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="8"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color indexed="11"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color indexed="11"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="11"/>
+        <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -535,23 +502,21 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2311,213 +2276,121 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:IV23"/>
+  <dimension ref="A1:IR23"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="108.7109375" style="11" customWidth="1"/>
-    <col min="2" max="256" width="8.85546875" style="11" customWidth="1"/>
+    <col min="2" max="252" width="8.85546875" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:1" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
     </row>
-    <row r="2" spans="1:5" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+    <row r="2" spans="1:1" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="16"/>
     </row>
-    <row r="3" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="s">
+    <row r="3" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
     </row>
-    <row r="4" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
+    <row r="4" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
     </row>
-    <row r="5" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
     </row>
-    <row r="6" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="22" t="s">
+    <row r="6" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
     </row>
-    <row r="7" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
     </row>
-    <row r="8" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
+    <row r="8" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
     </row>
-    <row r="9" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="14" t="s">
+    <row r="9" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
     </row>
-    <row r="10" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="14" t="s">
+    <row r="10" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
     </row>
-    <row r="11" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="16"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
+    <row r="11" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="18"/>
     </row>
-    <row r="12" spans="1:5" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="21" t="s">
+    <row r="12" spans="1:1" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
     </row>
-    <row r="13" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
+    <row r="13" spans="1:1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="14"/>
     </row>
-    <row r="14" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="14" t="s">
+    <row r="14" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
     </row>
-    <row r="15" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="14" t="s">
+    <row r="15" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
     </row>
-    <row r="16" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="14" t="s">
+    <row r="16" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
     </row>
-    <row r="17" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="14" t="s">
+    <row r="17" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
     </row>
-    <row r="18" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="14" t="s">
+    <row r="18" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
     </row>
-    <row r="19" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="14" t="s">
+    <row r="19" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
     </row>
-    <row r="20" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="14" t="s">
+    <row r="20" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="14" t="s">
+    <row r="21" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
     </row>
-    <row r="22" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="14" t="s">
+    <row r="22" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
     </row>
-    <row r="23" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="14" t="s">
+    <row r="23" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="19126"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212706711\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{C79B8DB6-6162-476A-AF1A-F2445909CCB5}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28360" windowHeight="10220"/>
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId1"/>
     <sheet name="填写说明" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47">
+  <si>
+    <t>所属集团</t>
+  </si>
+  <si>
+    <t>所属医院</t>
+  </si>
   <si>
     <t>所属院区</t>
   </si>
@@ -70,7 +70,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>新增医院</t>
@@ -80,7 +79,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>A</t>
     </r>
@@ -94,7 +93,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>新增层级</t>
@@ -104,7 +102,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>1</t>
     </r>
@@ -113,7 +111,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>科室</t>
@@ -123,7 +120,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>1</t>
     </r>
@@ -134,7 +131,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>新增层级</t>
@@ -144,7 +140,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>2</t>
     </r>
@@ -153,7 +149,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>科室</t>
@@ -163,7 +158,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>1</t>
     </r>
@@ -174,7 +169,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>新增层级</t>
@@ -184,7 +178,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>3</t>
     </r>
@@ -193,7 +187,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>科室</t>
@@ -203,7 +196,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>1</t>
     </r>
@@ -233,6 +226,27 @@
     <t>1.在datalist sheet中带有*标记的列为必填项。</t>
   </si>
   <si>
+    <t>2.“科室1”、“科室2”和“科室3”分别表示“科室层级1”、“科室层级2”和“科室层级3”</t>
+  </si>
+  <si>
+    <t>3.角色列需要输入以下角色名称，否则系统找不到相对应的名称，不导入该条数据</t>
+  </si>
+  <si>
+    <t>4.若角色中同时填入“仅报修权限账号”和其他角色，则只导入“仅报修权限账号”角色</t>
+  </si>
+  <si>
+    <t>5.多个角色用逗号分隔(不区分大小写)，多个角色中其中有一条角色名称输入有误，则不导入该条数据</t>
+  </si>
+  <si>
+    <t>6.从系统导出时，会带有UUID列，此列不可更改，系统会根据UUID更新相应字段内容</t>
+  </si>
+  <si>
+    <t>7.可见范围中，输入除本人所在科室以外的其他科室名称，可见多个科室用逗号分隔</t>
+  </si>
+  <si>
+    <t>8.可见范围只支持科室的设定，院区、医院等不支持</t>
+  </si>
+  <si>
     <t>角色名称</t>
   </si>
   <si>
@@ -264,82 +278,196 @@
   </si>
   <si>
     <t>设备调剂管理人员</t>
-  </si>
-  <si>
-    <t>所属医院</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>所属集团*</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.角色列需要输入以下角色名称，否则系统找不到相对应的名称，不导入该条数据</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.“科室1”、“科室2”和“科室3”分别表示“科室层级1”、“科室层级2”和“科室层级3”</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>5.多个角色用逗号分隔(不区分大小写)，多个角色中其中有一条角色名称输入有误，则不导入该条数据</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.从系统导出时，会带有UUID列，此列不可更改，系统会根据UUID更新相应字段内容</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>7.可见范围中，输入除本人所在科室以外的其他科室名称，可见多个科室用逗号分隔</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>8.可见范围只支持科室的设定，院区、医院等不支持</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.若角色中同时填入“仅报修权限账号”和其他角色，则只导入“仅报修权限账号”角色</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -349,17 +477,203 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="10"/>
-        <bgColor auto="1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
-        <bgColor auto="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -371,42 +685,7 @@
       <left style="thin">
         <color indexed="11"/>
       </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
       <right/>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
       <top style="thin">
         <color indexed="11"/>
       </top>
@@ -423,19 +702,18 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
-        <color indexed="11"/>
+        <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -466,77 +744,394 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color indexed="11"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color indexed="11"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color indexed="11"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FF4D5D2C"/>
-      <rgbColor rgb="FFAAAAAA"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="004D5D2C"/>
+      <rgbColor rgb="00AAAAAA"/>
       <rgbColor rgb="000000FF"/>
       <rgbColor rgb="00FFFF00"/>
       <rgbColor rgb="00FF00FF"/>
@@ -594,9 +1189,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -802,8 +1394,6 @@
           <a:prstDash val="solid"/>
           <a:round/>
         </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
       </a:spPr>
       <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
@@ -823,7 +1413,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -853,7 +1442,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -879,7 +1467,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -905,7 +1492,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -931,7 +1517,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -957,7 +1542,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -983,7 +1567,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1009,7 +1592,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1035,7 +1617,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1061,7 +1642,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1097,8 +1677,6 @@
           <a:prstDash val="solid"/>
           <a:round/>
         </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
       </a:spPr>
       <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
@@ -1118,7 +1696,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1144,7 +1721,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1170,7 +1746,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1196,7 +1771,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1222,7 +1796,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1248,7 +1821,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1274,7 +1846,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1300,7 +1871,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1326,7 +1896,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1352,7 +1921,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1385,8 +1953,6 @@
           <a:noFill/>
           <a:miter lim="400000"/>
         </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
       </a:spPr>
       <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
@@ -1406,7 +1972,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1436,7 +2001,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1462,7 +2026,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1488,7 +2051,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1514,7 +2076,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1540,7 +2101,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1566,7 +2126,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1592,7 +2151,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1618,7 +2176,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1644,7 +2201,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1671,603 +2227,602 @@
       </a:style>
     </a:txDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr/>
   <dimension ref="A1:IU2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85714285714286" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="13.42578125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="14.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="9" width="8.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.2857142857143" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7142857142857" style="1" customWidth="1"/>
+    <col min="3" max="4" width="13.4285714285714" style="1" customWidth="1"/>
+    <col min="5" max="6" width="14.2857142857143" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7142857142857" style="1" customWidth="1"/>
+    <col min="8" max="9" width="8.85714285714286" style="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
-    <col min="11" max="12" width="8.85546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="24.7109375" style="1" customWidth="1"/>
+    <col min="11" max="12" width="8.85714285714286" style="1" customWidth="1"/>
+    <col min="13" max="13" width="24.7142857142857" style="1" customWidth="1"/>
     <col min="14" max="14" width="30" style="1" customWidth="1"/>
-    <col min="15" max="15" width="32.7109375" style="1" customWidth="1"/>
-    <col min="16" max="255" width="8.85546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="32.7142857142857" style="1" customWidth="1"/>
+    <col min="16" max="255" width="8.85714285714286" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:255" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="2" t="s">
+    <row r="1" ht="30.75" customHeight="1" spans="1:255">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4"/>
-      <c r="AD1" s="4"/>
-      <c r="AE1" s="4"/>
-      <c r="AF1" s="4"/>
-      <c r="AG1" s="4"/>
-      <c r="AH1" s="4"/>
-      <c r="AI1" s="4"/>
-      <c r="AJ1" s="4"/>
-      <c r="AK1" s="4"/>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
-      <c r="AP1" s="4"/>
-      <c r="AQ1" s="4"/>
-      <c r="AR1" s="4"/>
-      <c r="AS1" s="4"/>
-      <c r="AT1" s="4"/>
-      <c r="AU1" s="4"/>
-      <c r="AV1" s="4"/>
-      <c r="AW1" s="4"/>
-      <c r="AX1" s="4"/>
-      <c r="AY1" s="4"/>
-      <c r="AZ1" s="4"/>
-      <c r="BA1" s="4"/>
-      <c r="BB1" s="4"/>
-      <c r="BC1" s="4"/>
-      <c r="BD1" s="4"/>
-      <c r="BE1" s="4"/>
-      <c r="BF1" s="4"/>
-      <c r="BG1" s="4"/>
-      <c r="BH1" s="4"/>
-      <c r="BI1" s="4"/>
-      <c r="BJ1" s="4"/>
-      <c r="BK1" s="4"/>
-      <c r="BL1" s="4"/>
-      <c r="BM1" s="4"/>
-      <c r="BN1" s="4"/>
-      <c r="BO1" s="4"/>
-      <c r="BP1" s="4"/>
-      <c r="BQ1" s="4"/>
-      <c r="BR1" s="4"/>
-      <c r="BS1" s="4"/>
-      <c r="BT1" s="4"/>
-      <c r="BU1" s="4"/>
-      <c r="BV1" s="4"/>
-      <c r="BW1" s="4"/>
-      <c r="BX1" s="4"/>
-      <c r="BY1" s="4"/>
-      <c r="BZ1" s="4"/>
-      <c r="CA1" s="4"/>
-      <c r="CB1" s="4"/>
-      <c r="CC1" s="4"/>
-      <c r="CD1" s="4"/>
-      <c r="CE1" s="4"/>
-      <c r="CF1" s="4"/>
-      <c r="CG1" s="4"/>
-      <c r="CH1" s="4"/>
-      <c r="CI1" s="4"/>
-      <c r="CJ1" s="4"/>
-      <c r="CK1" s="4"/>
-      <c r="CL1" s="4"/>
-      <c r="CM1" s="4"/>
-      <c r="CN1" s="4"/>
-      <c r="CO1" s="4"/>
-      <c r="CP1" s="4"/>
-      <c r="CQ1" s="4"/>
-      <c r="CR1" s="4"/>
-      <c r="CS1" s="4"/>
-      <c r="CT1" s="4"/>
-      <c r="CU1" s="4"/>
-      <c r="CV1" s="4"/>
-      <c r="CW1" s="4"/>
-      <c r="CX1" s="4"/>
-      <c r="CY1" s="4"/>
-      <c r="CZ1" s="4"/>
-      <c r="DA1" s="4"/>
-      <c r="DB1" s="4"/>
-      <c r="DC1" s="4"/>
-      <c r="DD1" s="4"/>
-      <c r="DE1" s="4"/>
-      <c r="DF1" s="4"/>
-      <c r="DG1" s="4"/>
-      <c r="DH1" s="4"/>
-      <c r="DI1" s="4"/>
-      <c r="DJ1" s="4"/>
-      <c r="DK1" s="4"/>
-      <c r="DL1" s="4"/>
-      <c r="DM1" s="4"/>
-      <c r="DN1" s="4"/>
-      <c r="DO1" s="4"/>
-      <c r="DP1" s="4"/>
-      <c r="DQ1" s="4"/>
-      <c r="DR1" s="4"/>
-      <c r="DS1" s="4"/>
-      <c r="DT1" s="4"/>
-      <c r="DU1" s="4"/>
-      <c r="DV1" s="4"/>
-      <c r="DW1" s="4"/>
-      <c r="DX1" s="4"/>
-      <c r="DY1" s="4"/>
-      <c r="DZ1" s="4"/>
-      <c r="EA1" s="4"/>
-      <c r="EB1" s="4"/>
-      <c r="EC1" s="4"/>
-      <c r="ED1" s="4"/>
-      <c r="EE1" s="4"/>
-      <c r="EF1" s="4"/>
-      <c r="EG1" s="4"/>
-      <c r="EH1" s="4"/>
-      <c r="EI1" s="4"/>
-      <c r="EJ1" s="4"/>
-      <c r="EK1" s="4"/>
-      <c r="EL1" s="4"/>
-      <c r="EM1" s="4"/>
-      <c r="EN1" s="4"/>
-      <c r="EO1" s="4"/>
-      <c r="EP1" s="4"/>
-      <c r="EQ1" s="4"/>
-      <c r="ER1" s="4"/>
-      <c r="ES1" s="4"/>
-      <c r="ET1" s="4"/>
-      <c r="EU1" s="4"/>
-      <c r="EV1" s="4"/>
-      <c r="EW1" s="4"/>
-      <c r="EX1" s="4"/>
-      <c r="EY1" s="4"/>
-      <c r="EZ1" s="4"/>
-      <c r="FA1" s="4"/>
-      <c r="FB1" s="4"/>
-      <c r="FC1" s="4"/>
-      <c r="FD1" s="4"/>
-      <c r="FE1" s="4"/>
-      <c r="FF1" s="4"/>
-      <c r="FG1" s="4"/>
-      <c r="FH1" s="4"/>
-      <c r="FI1" s="4"/>
-      <c r="FJ1" s="4"/>
-      <c r="FK1" s="4"/>
-      <c r="FL1" s="4"/>
-      <c r="FM1" s="4"/>
-      <c r="FN1" s="4"/>
-      <c r="FO1" s="4"/>
-      <c r="FP1" s="4"/>
-      <c r="FQ1" s="4"/>
-      <c r="FR1" s="4"/>
-      <c r="FS1" s="4"/>
-      <c r="FT1" s="4"/>
-      <c r="FU1" s="4"/>
-      <c r="FV1" s="4"/>
-      <c r="FW1" s="4"/>
-      <c r="FX1" s="4"/>
-      <c r="FY1" s="4"/>
-      <c r="FZ1" s="4"/>
-      <c r="GA1" s="4"/>
-      <c r="GB1" s="4"/>
-      <c r="GC1" s="4"/>
-      <c r="GD1" s="4"/>
-      <c r="GE1" s="4"/>
-      <c r="GF1" s="4"/>
-      <c r="GG1" s="4"/>
-      <c r="GH1" s="4"/>
-      <c r="GI1" s="4"/>
-      <c r="GJ1" s="4"/>
-      <c r="GK1" s="4"/>
-      <c r="GL1" s="4"/>
-      <c r="GM1" s="4"/>
-      <c r="GN1" s="4"/>
-      <c r="GO1" s="4"/>
-      <c r="GP1" s="4"/>
-      <c r="GQ1" s="4"/>
-      <c r="GR1" s="4"/>
-      <c r="GS1" s="4"/>
-      <c r="GT1" s="4"/>
-      <c r="GU1" s="4"/>
-      <c r="GV1" s="4"/>
-      <c r="GW1" s="4"/>
-      <c r="GX1" s="4"/>
-      <c r="GY1" s="4"/>
-      <c r="GZ1" s="4"/>
-      <c r="HA1" s="4"/>
-      <c r="HB1" s="4"/>
-      <c r="HC1" s="4"/>
-      <c r="HD1" s="4"/>
-      <c r="HE1" s="4"/>
-      <c r="HF1" s="4"/>
-      <c r="HG1" s="4"/>
-      <c r="HH1" s="4"/>
-      <c r="HI1" s="4"/>
-      <c r="HJ1" s="4"/>
-      <c r="HK1" s="4"/>
-      <c r="HL1" s="4"/>
-      <c r="HM1" s="4"/>
-      <c r="HN1" s="4"/>
-      <c r="HO1" s="4"/>
-      <c r="HP1" s="4"/>
-      <c r="HQ1" s="4"/>
-      <c r="HR1" s="4"/>
-      <c r="HS1" s="4"/>
-      <c r="HT1" s="4"/>
-      <c r="HU1" s="4"/>
-      <c r="HV1" s="4"/>
-      <c r="HW1" s="4"/>
-      <c r="HX1" s="4"/>
-      <c r="HY1" s="4"/>
-      <c r="HZ1" s="4"/>
-      <c r="IA1" s="4"/>
-      <c r="IB1" s="4"/>
-      <c r="IC1" s="4"/>
-      <c r="ID1" s="4"/>
-      <c r="IE1" s="4"/>
-      <c r="IF1" s="4"/>
-      <c r="IG1" s="4"/>
-      <c r="IH1" s="4"/>
-      <c r="II1" s="4"/>
-      <c r="IJ1" s="4"/>
-      <c r="IK1" s="4"/>
-      <c r="IL1" s="4"/>
-      <c r="IM1" s="4"/>
-      <c r="IN1" s="4"/>
-      <c r="IO1" s="4"/>
-      <c r="IP1" s="4"/>
-      <c r="IQ1" s="4"/>
-      <c r="IR1" s="4"/>
-      <c r="IS1" s="4"/>
-      <c r="IT1" s="4"/>
-      <c r="IU1" s="5"/>
+      <c r="N1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="14"/>
+      <c r="AG1" s="14"/>
+      <c r="AH1" s="14"/>
+      <c r="AI1" s="14"/>
+      <c r="AJ1" s="14"/>
+      <c r="AK1" s="14"/>
+      <c r="AL1" s="14"/>
+      <c r="AM1" s="14"/>
+      <c r="AN1" s="14"/>
+      <c r="AO1" s="14"/>
+      <c r="AP1" s="14"/>
+      <c r="AQ1" s="14"/>
+      <c r="AR1" s="14"/>
+      <c r="AS1" s="14"/>
+      <c r="AT1" s="14"/>
+      <c r="AU1" s="14"/>
+      <c r="AV1" s="14"/>
+      <c r="AW1" s="14"/>
+      <c r="AX1" s="14"/>
+      <c r="AY1" s="14"/>
+      <c r="AZ1" s="14"/>
+      <c r="BA1" s="14"/>
+      <c r="BB1" s="14"/>
+      <c r="BC1" s="14"/>
+      <c r="BD1" s="14"/>
+      <c r="BE1" s="14"/>
+      <c r="BF1" s="14"/>
+      <c r="BG1" s="14"/>
+      <c r="BH1" s="14"/>
+      <c r="BI1" s="14"/>
+      <c r="BJ1" s="14"/>
+      <c r="BK1" s="14"/>
+      <c r="BL1" s="14"/>
+      <c r="BM1" s="14"/>
+      <c r="BN1" s="14"/>
+      <c r="BO1" s="14"/>
+      <c r="BP1" s="14"/>
+      <c r="BQ1" s="14"/>
+      <c r="BR1" s="14"/>
+      <c r="BS1" s="14"/>
+      <c r="BT1" s="14"/>
+      <c r="BU1" s="14"/>
+      <c r="BV1" s="14"/>
+      <c r="BW1" s="14"/>
+      <c r="BX1" s="14"/>
+      <c r="BY1" s="14"/>
+      <c r="BZ1" s="14"/>
+      <c r="CA1" s="14"/>
+      <c r="CB1" s="14"/>
+      <c r="CC1" s="14"/>
+      <c r="CD1" s="14"/>
+      <c r="CE1" s="14"/>
+      <c r="CF1" s="14"/>
+      <c r="CG1" s="14"/>
+      <c r="CH1" s="14"/>
+      <c r="CI1" s="14"/>
+      <c r="CJ1" s="14"/>
+      <c r="CK1" s="14"/>
+      <c r="CL1" s="14"/>
+      <c r="CM1" s="14"/>
+      <c r="CN1" s="14"/>
+      <c r="CO1" s="14"/>
+      <c r="CP1" s="14"/>
+      <c r="CQ1" s="14"/>
+      <c r="CR1" s="14"/>
+      <c r="CS1" s="14"/>
+      <c r="CT1" s="14"/>
+      <c r="CU1" s="14"/>
+      <c r="CV1" s="14"/>
+      <c r="CW1" s="14"/>
+      <c r="CX1" s="14"/>
+      <c r="CY1" s="14"/>
+      <c r="CZ1" s="14"/>
+      <c r="DA1" s="14"/>
+      <c r="DB1" s="14"/>
+      <c r="DC1" s="14"/>
+      <c r="DD1" s="14"/>
+      <c r="DE1" s="14"/>
+      <c r="DF1" s="14"/>
+      <c r="DG1" s="14"/>
+      <c r="DH1" s="14"/>
+      <c r="DI1" s="14"/>
+      <c r="DJ1" s="14"/>
+      <c r="DK1" s="14"/>
+      <c r="DL1" s="14"/>
+      <c r="DM1" s="14"/>
+      <c r="DN1" s="14"/>
+      <c r="DO1" s="14"/>
+      <c r="DP1" s="14"/>
+      <c r="DQ1" s="14"/>
+      <c r="DR1" s="14"/>
+      <c r="DS1" s="14"/>
+      <c r="DT1" s="14"/>
+      <c r="DU1" s="14"/>
+      <c r="DV1" s="14"/>
+      <c r="DW1" s="14"/>
+      <c r="DX1" s="14"/>
+      <c r="DY1" s="14"/>
+      <c r="DZ1" s="14"/>
+      <c r="EA1" s="14"/>
+      <c r="EB1" s="14"/>
+      <c r="EC1" s="14"/>
+      <c r="ED1" s="14"/>
+      <c r="EE1" s="14"/>
+      <c r="EF1" s="14"/>
+      <c r="EG1" s="14"/>
+      <c r="EH1" s="14"/>
+      <c r="EI1" s="14"/>
+      <c r="EJ1" s="14"/>
+      <c r="EK1" s="14"/>
+      <c r="EL1" s="14"/>
+      <c r="EM1" s="14"/>
+      <c r="EN1" s="14"/>
+      <c r="EO1" s="14"/>
+      <c r="EP1" s="14"/>
+      <c r="EQ1" s="14"/>
+      <c r="ER1" s="14"/>
+      <c r="ES1" s="14"/>
+      <c r="ET1" s="14"/>
+      <c r="EU1" s="14"/>
+      <c r="EV1" s="14"/>
+      <c r="EW1" s="14"/>
+      <c r="EX1" s="14"/>
+      <c r="EY1" s="14"/>
+      <c r="EZ1" s="14"/>
+      <c r="FA1" s="14"/>
+      <c r="FB1" s="14"/>
+      <c r="FC1" s="14"/>
+      <c r="FD1" s="14"/>
+      <c r="FE1" s="14"/>
+      <c r="FF1" s="14"/>
+      <c r="FG1" s="14"/>
+      <c r="FH1" s="14"/>
+      <c r="FI1" s="14"/>
+      <c r="FJ1" s="14"/>
+      <c r="FK1" s="14"/>
+      <c r="FL1" s="14"/>
+      <c r="FM1" s="14"/>
+      <c r="FN1" s="14"/>
+      <c r="FO1" s="14"/>
+      <c r="FP1" s="14"/>
+      <c r="FQ1" s="14"/>
+      <c r="FR1" s="14"/>
+      <c r="FS1" s="14"/>
+      <c r="FT1" s="14"/>
+      <c r="FU1" s="14"/>
+      <c r="FV1" s="14"/>
+      <c r="FW1" s="14"/>
+      <c r="FX1" s="14"/>
+      <c r="FY1" s="14"/>
+      <c r="FZ1" s="14"/>
+      <c r="GA1" s="14"/>
+      <c r="GB1" s="14"/>
+      <c r="GC1" s="14"/>
+      <c r="GD1" s="14"/>
+      <c r="GE1" s="14"/>
+      <c r="GF1" s="14"/>
+      <c r="GG1" s="14"/>
+      <c r="GH1" s="14"/>
+      <c r="GI1" s="14"/>
+      <c r="GJ1" s="14"/>
+      <c r="GK1" s="14"/>
+      <c r="GL1" s="14"/>
+      <c r="GM1" s="14"/>
+      <c r="GN1" s="14"/>
+      <c r="GO1" s="14"/>
+      <c r="GP1" s="14"/>
+      <c r="GQ1" s="14"/>
+      <c r="GR1" s="14"/>
+      <c r="GS1" s="14"/>
+      <c r="GT1" s="14"/>
+      <c r="GU1" s="14"/>
+      <c r="GV1" s="14"/>
+      <c r="GW1" s="14"/>
+      <c r="GX1" s="14"/>
+      <c r="GY1" s="14"/>
+      <c r="GZ1" s="14"/>
+      <c r="HA1" s="14"/>
+      <c r="HB1" s="14"/>
+      <c r="HC1" s="14"/>
+      <c r="HD1" s="14"/>
+      <c r="HE1" s="14"/>
+      <c r="HF1" s="14"/>
+      <c r="HG1" s="14"/>
+      <c r="HH1" s="14"/>
+      <c r="HI1" s="14"/>
+      <c r="HJ1" s="14"/>
+      <c r="HK1" s="14"/>
+      <c r="HL1" s="14"/>
+      <c r="HM1" s="14"/>
+      <c r="HN1" s="14"/>
+      <c r="HO1" s="14"/>
+      <c r="HP1" s="14"/>
+      <c r="HQ1" s="14"/>
+      <c r="HR1" s="14"/>
+      <c r="HS1" s="14"/>
+      <c r="HT1" s="14"/>
+      <c r="HU1" s="14"/>
+      <c r="HV1" s="14"/>
+      <c r="HW1" s="14"/>
+      <c r="HX1" s="14"/>
+      <c r="HY1" s="14"/>
+      <c r="HZ1" s="14"/>
+      <c r="IA1" s="14"/>
+      <c r="IB1" s="14"/>
+      <c r="IC1" s="14"/>
+      <c r="ID1" s="14"/>
+      <c r="IE1" s="14"/>
+      <c r="IF1" s="14"/>
+      <c r="IG1" s="14"/>
+      <c r="IH1" s="14"/>
+      <c r="II1" s="14"/>
+      <c r="IJ1" s="14"/>
+      <c r="IK1" s="14"/>
+      <c r="IL1" s="14"/>
+      <c r="IM1" s="14"/>
+      <c r="IN1" s="14"/>
+      <c r="IO1" s="14"/>
+      <c r="IP1" s="14"/>
+      <c r="IQ1" s="14"/>
+      <c r="IR1" s="14"/>
+      <c r="IS1" s="14"/>
+      <c r="IT1" s="14"/>
+      <c r="IU1" s="16"/>
     </row>
-    <row r="2" spans="1:255" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="6" t="s">
+    <row r="2" ht="34.5" customHeight="1" spans="1:255">
+      <c r="A2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="B2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="C2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="D2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="E2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6" t="s">
+      <c r="F2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="G2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="H2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="K2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="L2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="6"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
-      <c r="AE2" s="9"/>
-      <c r="AF2" s="9"/>
-      <c r="AG2" s="9"/>
-      <c r="AH2" s="9"/>
-      <c r="AI2" s="9"/>
-      <c r="AJ2" s="9"/>
-      <c r="AK2" s="9"/>
-      <c r="AL2" s="9"/>
-      <c r="AM2" s="9"/>
-      <c r="AN2" s="9"/>
-      <c r="AO2" s="9"/>
-      <c r="AP2" s="9"/>
-      <c r="AQ2" s="9"/>
-      <c r="AR2" s="9"/>
-      <c r="AS2" s="9"/>
-      <c r="AT2" s="9"/>
-      <c r="AU2" s="9"/>
-      <c r="AV2" s="9"/>
-      <c r="AW2" s="9"/>
-      <c r="AX2" s="9"/>
-      <c r="AY2" s="9"/>
-      <c r="AZ2" s="9"/>
-      <c r="BA2" s="9"/>
-      <c r="BB2" s="9"/>
-      <c r="BC2" s="9"/>
-      <c r="BD2" s="9"/>
-      <c r="BE2" s="9"/>
-      <c r="BF2" s="9"/>
-      <c r="BG2" s="9"/>
-      <c r="BH2" s="9"/>
-      <c r="BI2" s="9"/>
-      <c r="BJ2" s="9"/>
-      <c r="BK2" s="9"/>
-      <c r="BL2" s="9"/>
-      <c r="BM2" s="9"/>
-      <c r="BN2" s="9"/>
-      <c r="BO2" s="9"/>
-      <c r="BP2" s="9"/>
-      <c r="BQ2" s="9"/>
-      <c r="BR2" s="9"/>
-      <c r="BS2" s="9"/>
-      <c r="BT2" s="9"/>
-      <c r="BU2" s="9"/>
-      <c r="BV2" s="9"/>
-      <c r="BW2" s="9"/>
-      <c r="BX2" s="9"/>
-      <c r="BY2" s="9"/>
-      <c r="BZ2" s="9"/>
-      <c r="CA2" s="9"/>
-      <c r="CB2" s="9"/>
-      <c r="CC2" s="9"/>
-      <c r="CD2" s="9"/>
-      <c r="CE2" s="9"/>
-      <c r="CF2" s="9"/>
-      <c r="CG2" s="9"/>
-      <c r="CH2" s="9"/>
-      <c r="CI2" s="9"/>
-      <c r="CJ2" s="9"/>
-      <c r="CK2" s="9"/>
-      <c r="CL2" s="9"/>
-      <c r="CM2" s="9"/>
-      <c r="CN2" s="9"/>
-      <c r="CO2" s="9"/>
-      <c r="CP2" s="9"/>
-      <c r="CQ2" s="9"/>
-      <c r="CR2" s="9"/>
-      <c r="CS2" s="9"/>
-      <c r="CT2" s="9"/>
-      <c r="CU2" s="9"/>
-      <c r="CV2" s="9"/>
-      <c r="CW2" s="9"/>
-      <c r="CX2" s="9"/>
-      <c r="CY2" s="9"/>
-      <c r="CZ2" s="9"/>
-      <c r="DA2" s="9"/>
-      <c r="DB2" s="9"/>
-      <c r="DC2" s="9"/>
-      <c r="DD2" s="9"/>
-      <c r="DE2" s="9"/>
-      <c r="DF2" s="9"/>
-      <c r="DG2" s="9"/>
-      <c r="DH2" s="9"/>
-      <c r="DI2" s="9"/>
-      <c r="DJ2" s="9"/>
-      <c r="DK2" s="9"/>
-      <c r="DL2" s="9"/>
-      <c r="DM2" s="9"/>
-      <c r="DN2" s="9"/>
-      <c r="DO2" s="9"/>
-      <c r="DP2" s="9"/>
-      <c r="DQ2" s="9"/>
-      <c r="DR2" s="9"/>
-      <c r="DS2" s="9"/>
-      <c r="DT2" s="9"/>
-      <c r="DU2" s="9"/>
-      <c r="DV2" s="9"/>
-      <c r="DW2" s="9"/>
-      <c r="DX2" s="9"/>
-      <c r="DY2" s="9"/>
-      <c r="DZ2" s="9"/>
-      <c r="EA2" s="9"/>
-      <c r="EB2" s="9"/>
-      <c r="EC2" s="9"/>
-      <c r="ED2" s="9"/>
-      <c r="EE2" s="9"/>
-      <c r="EF2" s="9"/>
-      <c r="EG2" s="9"/>
-      <c r="EH2" s="9"/>
-      <c r="EI2" s="9"/>
-      <c r="EJ2" s="9"/>
-      <c r="EK2" s="9"/>
-      <c r="EL2" s="9"/>
-      <c r="EM2" s="9"/>
-      <c r="EN2" s="9"/>
-      <c r="EO2" s="9"/>
-      <c r="EP2" s="9"/>
-      <c r="EQ2" s="9"/>
-      <c r="ER2" s="9"/>
-      <c r="ES2" s="9"/>
-      <c r="ET2" s="9"/>
-      <c r="EU2" s="9"/>
-      <c r="EV2" s="9"/>
-      <c r="EW2" s="9"/>
-      <c r="EX2" s="9"/>
-      <c r="EY2" s="9"/>
-      <c r="EZ2" s="9"/>
-      <c r="FA2" s="9"/>
-      <c r="FB2" s="9"/>
-      <c r="FC2" s="9"/>
-      <c r="FD2" s="9"/>
-      <c r="FE2" s="9"/>
-      <c r="FF2" s="9"/>
-      <c r="FG2" s="9"/>
-      <c r="FH2" s="9"/>
-      <c r="FI2" s="9"/>
-      <c r="FJ2" s="9"/>
-      <c r="FK2" s="9"/>
-      <c r="FL2" s="9"/>
-      <c r="FM2" s="9"/>
-      <c r="FN2" s="9"/>
-      <c r="FO2" s="9"/>
-      <c r="FP2" s="9"/>
-      <c r="FQ2" s="9"/>
-      <c r="FR2" s="9"/>
-      <c r="FS2" s="9"/>
-      <c r="FT2" s="9"/>
-      <c r="FU2" s="9"/>
-      <c r="FV2" s="9"/>
-      <c r="FW2" s="9"/>
-      <c r="FX2" s="9"/>
-      <c r="FY2" s="9"/>
-      <c r="FZ2" s="9"/>
-      <c r="GA2" s="9"/>
-      <c r="GB2" s="9"/>
-      <c r="GC2" s="9"/>
-      <c r="GD2" s="9"/>
-      <c r="GE2" s="9"/>
-      <c r="GF2" s="9"/>
-      <c r="GG2" s="9"/>
-      <c r="GH2" s="9"/>
-      <c r="GI2" s="9"/>
-      <c r="GJ2" s="9"/>
-      <c r="GK2" s="9"/>
-      <c r="GL2" s="9"/>
-      <c r="GM2" s="9"/>
-      <c r="GN2" s="9"/>
-      <c r="GO2" s="9"/>
-      <c r="GP2" s="9"/>
-      <c r="GQ2" s="9"/>
-      <c r="GR2" s="9"/>
-      <c r="GS2" s="9"/>
-      <c r="GT2" s="9"/>
-      <c r="GU2" s="9"/>
-      <c r="GV2" s="9"/>
-      <c r="GW2" s="9"/>
-      <c r="GX2" s="9"/>
-      <c r="GY2" s="9"/>
-      <c r="GZ2" s="9"/>
-      <c r="HA2" s="9"/>
-      <c r="HB2" s="9"/>
-      <c r="HC2" s="9"/>
-      <c r="HD2" s="9"/>
-      <c r="HE2" s="9"/>
-      <c r="HF2" s="9"/>
-      <c r="HG2" s="9"/>
-      <c r="HH2" s="9"/>
-      <c r="HI2" s="9"/>
-      <c r="HJ2" s="9"/>
-      <c r="HK2" s="9"/>
-      <c r="HL2" s="9"/>
-      <c r="HM2" s="9"/>
-      <c r="HN2" s="9"/>
-      <c r="HO2" s="9"/>
-      <c r="HP2" s="9"/>
-      <c r="HQ2" s="9"/>
-      <c r="HR2" s="9"/>
-      <c r="HS2" s="9"/>
-      <c r="HT2" s="9"/>
-      <c r="HU2" s="9"/>
-      <c r="HV2" s="9"/>
-      <c r="HW2" s="9"/>
-      <c r="HX2" s="9"/>
-      <c r="HY2" s="9"/>
-      <c r="HZ2" s="9"/>
-      <c r="IA2" s="9"/>
-      <c r="IB2" s="9"/>
-      <c r="IC2" s="9"/>
-      <c r="ID2" s="9"/>
-      <c r="IE2" s="9"/>
-      <c r="IF2" s="9"/>
-      <c r="IG2" s="9"/>
-      <c r="IH2" s="9"/>
-      <c r="II2" s="9"/>
-      <c r="IJ2" s="9"/>
-      <c r="IK2" s="9"/>
-      <c r="IL2" s="9"/>
-      <c r="IM2" s="9"/>
-      <c r="IN2" s="9"/>
-      <c r="IO2" s="9"/>
-      <c r="IP2" s="9"/>
-      <c r="IQ2" s="9"/>
-      <c r="IR2" s="9"/>
-      <c r="IS2" s="9"/>
-      <c r="IT2" s="9"/>
-      <c r="IU2" s="10"/>
+      <c r="M2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="10"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
+      <c r="AH2" s="15"/>
+      <c r="AI2" s="15"/>
+      <c r="AJ2" s="15"/>
+      <c r="AK2" s="15"/>
+      <c r="AL2" s="15"/>
+      <c r="AM2" s="15"/>
+      <c r="AN2" s="15"/>
+      <c r="AO2" s="15"/>
+      <c r="AP2" s="15"/>
+      <c r="AQ2" s="15"/>
+      <c r="AR2" s="15"/>
+      <c r="AS2" s="15"/>
+      <c r="AT2" s="15"/>
+      <c r="AU2" s="15"/>
+      <c r="AV2" s="15"/>
+      <c r="AW2" s="15"/>
+      <c r="AX2" s="15"/>
+      <c r="AY2" s="15"/>
+      <c r="AZ2" s="15"/>
+      <c r="BA2" s="15"/>
+      <c r="BB2" s="15"/>
+      <c r="BC2" s="15"/>
+      <c r="BD2" s="15"/>
+      <c r="BE2" s="15"/>
+      <c r="BF2" s="15"/>
+      <c r="BG2" s="15"/>
+      <c r="BH2" s="15"/>
+      <c r="BI2" s="15"/>
+      <c r="BJ2" s="15"/>
+      <c r="BK2" s="15"/>
+      <c r="BL2" s="15"/>
+      <c r="BM2" s="15"/>
+      <c r="BN2" s="15"/>
+      <c r="BO2" s="15"/>
+      <c r="BP2" s="15"/>
+      <c r="BQ2" s="15"/>
+      <c r="BR2" s="15"/>
+      <c r="BS2" s="15"/>
+      <c r="BT2" s="15"/>
+      <c r="BU2" s="15"/>
+      <c r="BV2" s="15"/>
+      <c r="BW2" s="15"/>
+      <c r="BX2" s="15"/>
+      <c r="BY2" s="15"/>
+      <c r="BZ2" s="15"/>
+      <c r="CA2" s="15"/>
+      <c r="CB2" s="15"/>
+      <c r="CC2" s="15"/>
+      <c r="CD2" s="15"/>
+      <c r="CE2" s="15"/>
+      <c r="CF2" s="15"/>
+      <c r="CG2" s="15"/>
+      <c r="CH2" s="15"/>
+      <c r="CI2" s="15"/>
+      <c r="CJ2" s="15"/>
+      <c r="CK2" s="15"/>
+      <c r="CL2" s="15"/>
+      <c r="CM2" s="15"/>
+      <c r="CN2" s="15"/>
+      <c r="CO2" s="15"/>
+      <c r="CP2" s="15"/>
+      <c r="CQ2" s="15"/>
+      <c r="CR2" s="15"/>
+      <c r="CS2" s="15"/>
+      <c r="CT2" s="15"/>
+      <c r="CU2" s="15"/>
+      <c r="CV2" s="15"/>
+      <c r="CW2" s="15"/>
+      <c r="CX2" s="15"/>
+      <c r="CY2" s="15"/>
+      <c r="CZ2" s="15"/>
+      <c r="DA2" s="15"/>
+      <c r="DB2" s="15"/>
+      <c r="DC2" s="15"/>
+      <c r="DD2" s="15"/>
+      <c r="DE2" s="15"/>
+      <c r="DF2" s="15"/>
+      <c r="DG2" s="15"/>
+      <c r="DH2" s="15"/>
+      <c r="DI2" s="15"/>
+      <c r="DJ2" s="15"/>
+      <c r="DK2" s="15"/>
+      <c r="DL2" s="15"/>
+      <c r="DM2" s="15"/>
+      <c r="DN2" s="15"/>
+      <c r="DO2" s="15"/>
+      <c r="DP2" s="15"/>
+      <c r="DQ2" s="15"/>
+      <c r="DR2" s="15"/>
+      <c r="DS2" s="15"/>
+      <c r="DT2" s="15"/>
+      <c r="DU2" s="15"/>
+      <c r="DV2" s="15"/>
+      <c r="DW2" s="15"/>
+      <c r="DX2" s="15"/>
+      <c r="DY2" s="15"/>
+      <c r="DZ2" s="15"/>
+      <c r="EA2" s="15"/>
+      <c r="EB2" s="15"/>
+      <c r="EC2" s="15"/>
+      <c r="ED2" s="15"/>
+      <c r="EE2" s="15"/>
+      <c r="EF2" s="15"/>
+      <c r="EG2" s="15"/>
+      <c r="EH2" s="15"/>
+      <c r="EI2" s="15"/>
+      <c r="EJ2" s="15"/>
+      <c r="EK2" s="15"/>
+      <c r="EL2" s="15"/>
+      <c r="EM2" s="15"/>
+      <c r="EN2" s="15"/>
+      <c r="EO2" s="15"/>
+      <c r="EP2" s="15"/>
+      <c r="EQ2" s="15"/>
+      <c r="ER2" s="15"/>
+      <c r="ES2" s="15"/>
+      <c r="ET2" s="15"/>
+      <c r="EU2" s="15"/>
+      <c r="EV2" s="15"/>
+      <c r="EW2" s="15"/>
+      <c r="EX2" s="15"/>
+      <c r="EY2" s="15"/>
+      <c r="EZ2" s="15"/>
+      <c r="FA2" s="15"/>
+      <c r="FB2" s="15"/>
+      <c r="FC2" s="15"/>
+      <c r="FD2" s="15"/>
+      <c r="FE2" s="15"/>
+      <c r="FF2" s="15"/>
+      <c r="FG2" s="15"/>
+      <c r="FH2" s="15"/>
+      <c r="FI2" s="15"/>
+      <c r="FJ2" s="15"/>
+      <c r="FK2" s="15"/>
+      <c r="FL2" s="15"/>
+      <c r="FM2" s="15"/>
+      <c r="FN2" s="15"/>
+      <c r="FO2" s="15"/>
+      <c r="FP2" s="15"/>
+      <c r="FQ2" s="15"/>
+      <c r="FR2" s="15"/>
+      <c r="FS2" s="15"/>
+      <c r="FT2" s="15"/>
+      <c r="FU2" s="15"/>
+      <c r="FV2" s="15"/>
+      <c r="FW2" s="15"/>
+      <c r="FX2" s="15"/>
+      <c r="FY2" s="15"/>
+      <c r="FZ2" s="15"/>
+      <c r="GA2" s="15"/>
+      <c r="GB2" s="15"/>
+      <c r="GC2" s="15"/>
+      <c r="GD2" s="15"/>
+      <c r="GE2" s="15"/>
+      <c r="GF2" s="15"/>
+      <c r="GG2" s="15"/>
+      <c r="GH2" s="15"/>
+      <c r="GI2" s="15"/>
+      <c r="GJ2" s="15"/>
+      <c r="GK2" s="15"/>
+      <c r="GL2" s="15"/>
+      <c r="GM2" s="15"/>
+      <c r="GN2" s="15"/>
+      <c r="GO2" s="15"/>
+      <c r="GP2" s="15"/>
+      <c r="GQ2" s="15"/>
+      <c r="GR2" s="15"/>
+      <c r="GS2" s="15"/>
+      <c r="GT2" s="15"/>
+      <c r="GU2" s="15"/>
+      <c r="GV2" s="15"/>
+      <c r="GW2" s="15"/>
+      <c r="GX2" s="15"/>
+      <c r="GY2" s="15"/>
+      <c r="GZ2" s="15"/>
+      <c r="HA2" s="15"/>
+      <c r="HB2" s="15"/>
+      <c r="HC2" s="15"/>
+      <c r="HD2" s="15"/>
+      <c r="HE2" s="15"/>
+      <c r="HF2" s="15"/>
+      <c r="HG2" s="15"/>
+      <c r="HH2" s="15"/>
+      <c r="HI2" s="15"/>
+      <c r="HJ2" s="15"/>
+      <c r="HK2" s="15"/>
+      <c r="HL2" s="15"/>
+      <c r="HM2" s="15"/>
+      <c r="HN2" s="15"/>
+      <c r="HO2" s="15"/>
+      <c r="HP2" s="15"/>
+      <c r="HQ2" s="15"/>
+      <c r="HR2" s="15"/>
+      <c r="HS2" s="15"/>
+      <c r="HT2" s="15"/>
+      <c r="HU2" s="15"/>
+      <c r="HV2" s="15"/>
+      <c r="HW2" s="15"/>
+      <c r="HX2" s="15"/>
+      <c r="HY2" s="15"/>
+      <c r="HZ2" s="15"/>
+      <c r="IA2" s="15"/>
+      <c r="IB2" s="15"/>
+      <c r="IC2" s="15"/>
+      <c r="ID2" s="15"/>
+      <c r="IE2" s="15"/>
+      <c r="IF2" s="15"/>
+      <c r="IG2" s="15"/>
+      <c r="IH2" s="15"/>
+      <c r="II2" s="15"/>
+      <c r="IJ2" s="15"/>
+      <c r="IK2" s="15"/>
+      <c r="IL2" s="15"/>
+      <c r="IM2" s="15"/>
+      <c r="IN2" s="15"/>
+      <c r="IO2" s="15"/>
+      <c r="IP2" s="15"/>
+      <c r="IQ2" s="15"/>
+      <c r="IR2" s="15"/>
+      <c r="IS2" s="15"/>
+      <c r="IT2" s="15"/>
+      <c r="IU2" s="17"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -2275,121 +2830,122 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:IR23"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr/>
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr defaultColWidth="8.85714285714286" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="108.7109375" style="11" customWidth="1"/>
-    <col min="2" max="252" width="8.85546875" style="11" customWidth="1"/>
+    <col min="1" max="1" width="108.714285714286" style="1" customWidth="1"/>
+    <col min="2" max="252" width="8.85714285714286" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
-        <v>25</v>
+    <row r="1" ht="13.7" customHeight="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="16"/>
+    <row r="2" ht="13.7" customHeight="1" spans="1:1">
+      <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
-        <v>26</v>
+    <row r="3" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A3" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+    <row r="4" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A4" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A5" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A6" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A7" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A8" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A9" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A10" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A11" s="5"/>
+    </row>
+    <row r="12" ht="13.7" customHeight="1" spans="1:1">
+      <c r="A12" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" ht="12" customHeight="1" spans="1:1">
+      <c r="A13" s="7"/>
+    </row>
+    <row r="14" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A14" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A15" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A16" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A17" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A18" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
-        <v>40</v>
+    <row r="19" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A19" s="8" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="17" t="s">
+    <row r="20" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A20" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A21" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A22" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" ht="13.5" customHeight="1" spans="1:1">
+      <c r="A23" s="8" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-    </row>
-    <row r="12" spans="1:1" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
-    </row>
-    <row r="14" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2397,9 +2953,8 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A12:A13"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10610"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qtang/Desktop/APM/Git/hc-apm-web/src/src/main/webapp/portal/uaa/userAccount/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{87CDB458-3D9E-1A47-9D14-BC578FD393EE}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28360" windowHeight="10220"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="28360" windowHeight="10220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId1"/>
@@ -15,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
   <si>
     <t>所属集团</t>
   </si>
@@ -279,18 +285,15 @@
   <si>
     <t>设备调剂管理人员</t>
   </si>
+  <si>
+    <t>初始密码</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -309,165 +312,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -486,194 +332,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="18">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -786,269 +446,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1065,58 +471,23 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
-    <cellStyle name="Total" xfId="25" builtinId="25"/>
-    <cellStyle name="Output" xfId="26" builtinId="21"/>
-    <cellStyle name="Currency" xfId="27" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
-    <cellStyle name="Note" xfId="29" builtinId="10"/>
-    <cellStyle name="Input" xfId="30" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
-    <cellStyle name="Good" xfId="33" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
-    <cellStyle name="Title" xfId="39" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
-    <cellStyle name="Comma" xfId="44" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
-    <cellStyle name="Percent" xfId="47" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
@@ -1189,6 +560,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2227,602 +1601,606 @@
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
-  <dimension ref="A1:IU2"/>
-  <sheetFormatPr defaultColWidth="8.85714285714286" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:IV2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.2857142857143" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7142857142857" style="1" customWidth="1"/>
-    <col min="3" max="4" width="13.4285714285714" style="1" customWidth="1"/>
-    <col min="5" max="6" width="14.2857142857143" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7142857142857" style="1" customWidth="1"/>
-    <col min="8" max="9" width="8.85714285714286" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="13.5" style="1" customWidth="1"/>
+    <col min="5" max="6" width="14.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="8.83203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
-    <col min="11" max="12" width="8.85714285714286" style="1" customWidth="1"/>
-    <col min="13" max="13" width="24.7142857142857" style="1" customWidth="1"/>
-    <col min="14" max="14" width="30" style="1" customWidth="1"/>
-    <col min="15" max="15" width="32.7142857142857" style="1" customWidth="1"/>
-    <col min="16" max="255" width="8.85714285714286" style="1" customWidth="1"/>
+    <col min="11" max="12" width="8.83203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="24.6640625" style="1" customWidth="1"/>
+    <col min="14" max="15" width="30" style="1" customWidth="1"/>
+    <col min="16" max="16" width="32.6640625" style="1" customWidth="1"/>
+    <col min="17" max="256" width="8.83203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30.75" customHeight="1" spans="1:255">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:256" ht="30.75" customHeight="1">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="14"/>
-      <c r="AB1" s="14"/>
-      <c r="AC1" s="14"/>
-      <c r="AD1" s="14"/>
-      <c r="AE1" s="14"/>
-      <c r="AF1" s="14"/>
-      <c r="AG1" s="14"/>
-      <c r="AH1" s="14"/>
-      <c r="AI1" s="14"/>
-      <c r="AJ1" s="14"/>
-      <c r="AK1" s="14"/>
-      <c r="AL1" s="14"/>
-      <c r="AM1" s="14"/>
-      <c r="AN1" s="14"/>
-      <c r="AO1" s="14"/>
-      <c r="AP1" s="14"/>
-      <c r="AQ1" s="14"/>
-      <c r="AR1" s="14"/>
-      <c r="AS1" s="14"/>
-      <c r="AT1" s="14"/>
-      <c r="AU1" s="14"/>
-      <c r="AV1" s="14"/>
-      <c r="AW1" s="14"/>
-      <c r="AX1" s="14"/>
-      <c r="AY1" s="14"/>
-      <c r="AZ1" s="14"/>
-      <c r="BA1" s="14"/>
-      <c r="BB1" s="14"/>
-      <c r="BC1" s="14"/>
-      <c r="BD1" s="14"/>
-      <c r="BE1" s="14"/>
-      <c r="BF1" s="14"/>
-      <c r="BG1" s="14"/>
-      <c r="BH1" s="14"/>
-      <c r="BI1" s="14"/>
-      <c r="BJ1" s="14"/>
-      <c r="BK1" s="14"/>
-      <c r="BL1" s="14"/>
-      <c r="BM1" s="14"/>
-      <c r="BN1" s="14"/>
-      <c r="BO1" s="14"/>
-      <c r="BP1" s="14"/>
-      <c r="BQ1" s="14"/>
-      <c r="BR1" s="14"/>
-      <c r="BS1" s="14"/>
-      <c r="BT1" s="14"/>
-      <c r="BU1" s="14"/>
-      <c r="BV1" s="14"/>
-      <c r="BW1" s="14"/>
-      <c r="BX1" s="14"/>
-      <c r="BY1" s="14"/>
-      <c r="BZ1" s="14"/>
-      <c r="CA1" s="14"/>
-      <c r="CB1" s="14"/>
-      <c r="CC1" s="14"/>
-      <c r="CD1" s="14"/>
-      <c r="CE1" s="14"/>
-      <c r="CF1" s="14"/>
-      <c r="CG1" s="14"/>
-      <c r="CH1" s="14"/>
-      <c r="CI1" s="14"/>
-      <c r="CJ1" s="14"/>
-      <c r="CK1" s="14"/>
-      <c r="CL1" s="14"/>
-      <c r="CM1" s="14"/>
-      <c r="CN1" s="14"/>
-      <c r="CO1" s="14"/>
-      <c r="CP1" s="14"/>
-      <c r="CQ1" s="14"/>
-      <c r="CR1" s="14"/>
-      <c r="CS1" s="14"/>
-      <c r="CT1" s="14"/>
-      <c r="CU1" s="14"/>
-      <c r="CV1" s="14"/>
-      <c r="CW1" s="14"/>
-      <c r="CX1" s="14"/>
-      <c r="CY1" s="14"/>
-      <c r="CZ1" s="14"/>
-      <c r="DA1" s="14"/>
-      <c r="DB1" s="14"/>
-      <c r="DC1" s="14"/>
-      <c r="DD1" s="14"/>
-      <c r="DE1" s="14"/>
-      <c r="DF1" s="14"/>
-      <c r="DG1" s="14"/>
-      <c r="DH1" s="14"/>
-      <c r="DI1" s="14"/>
-      <c r="DJ1" s="14"/>
-      <c r="DK1" s="14"/>
-      <c r="DL1" s="14"/>
-      <c r="DM1" s="14"/>
-      <c r="DN1" s="14"/>
-      <c r="DO1" s="14"/>
-      <c r="DP1" s="14"/>
-      <c r="DQ1" s="14"/>
-      <c r="DR1" s="14"/>
-      <c r="DS1" s="14"/>
-      <c r="DT1" s="14"/>
-      <c r="DU1" s="14"/>
-      <c r="DV1" s="14"/>
-      <c r="DW1" s="14"/>
-      <c r="DX1" s="14"/>
-      <c r="DY1" s="14"/>
-      <c r="DZ1" s="14"/>
-      <c r="EA1" s="14"/>
-      <c r="EB1" s="14"/>
-      <c r="EC1" s="14"/>
-      <c r="ED1" s="14"/>
-      <c r="EE1" s="14"/>
-      <c r="EF1" s="14"/>
-      <c r="EG1" s="14"/>
-      <c r="EH1" s="14"/>
-      <c r="EI1" s="14"/>
-      <c r="EJ1" s="14"/>
-      <c r="EK1" s="14"/>
-      <c r="EL1" s="14"/>
-      <c r="EM1" s="14"/>
-      <c r="EN1" s="14"/>
-      <c r="EO1" s="14"/>
-      <c r="EP1" s="14"/>
-      <c r="EQ1" s="14"/>
-      <c r="ER1" s="14"/>
-      <c r="ES1" s="14"/>
-      <c r="ET1" s="14"/>
-      <c r="EU1" s="14"/>
-      <c r="EV1" s="14"/>
-      <c r="EW1" s="14"/>
-      <c r="EX1" s="14"/>
-      <c r="EY1" s="14"/>
-      <c r="EZ1" s="14"/>
-      <c r="FA1" s="14"/>
-      <c r="FB1" s="14"/>
-      <c r="FC1" s="14"/>
-      <c r="FD1" s="14"/>
-      <c r="FE1" s="14"/>
-      <c r="FF1" s="14"/>
-      <c r="FG1" s="14"/>
-      <c r="FH1" s="14"/>
-      <c r="FI1" s="14"/>
-      <c r="FJ1" s="14"/>
-      <c r="FK1" s="14"/>
-      <c r="FL1" s="14"/>
-      <c r="FM1" s="14"/>
-      <c r="FN1" s="14"/>
-      <c r="FO1" s="14"/>
-      <c r="FP1" s="14"/>
-      <c r="FQ1" s="14"/>
-      <c r="FR1" s="14"/>
-      <c r="FS1" s="14"/>
-      <c r="FT1" s="14"/>
-      <c r="FU1" s="14"/>
-      <c r="FV1" s="14"/>
-      <c r="FW1" s="14"/>
-      <c r="FX1" s="14"/>
-      <c r="FY1" s="14"/>
-      <c r="FZ1" s="14"/>
-      <c r="GA1" s="14"/>
-      <c r="GB1" s="14"/>
-      <c r="GC1" s="14"/>
-      <c r="GD1" s="14"/>
-      <c r="GE1" s="14"/>
-      <c r="GF1" s="14"/>
-      <c r="GG1" s="14"/>
-      <c r="GH1" s="14"/>
-      <c r="GI1" s="14"/>
-      <c r="GJ1" s="14"/>
-      <c r="GK1" s="14"/>
-      <c r="GL1" s="14"/>
-      <c r="GM1" s="14"/>
-      <c r="GN1" s="14"/>
-      <c r="GO1" s="14"/>
-      <c r="GP1" s="14"/>
-      <c r="GQ1" s="14"/>
-      <c r="GR1" s="14"/>
-      <c r="GS1" s="14"/>
-      <c r="GT1" s="14"/>
-      <c r="GU1" s="14"/>
-      <c r="GV1" s="14"/>
-      <c r="GW1" s="14"/>
-      <c r="GX1" s="14"/>
-      <c r="GY1" s="14"/>
-      <c r="GZ1" s="14"/>
-      <c r="HA1" s="14"/>
-      <c r="HB1" s="14"/>
-      <c r="HC1" s="14"/>
-      <c r="HD1" s="14"/>
-      <c r="HE1" s="14"/>
-      <c r="HF1" s="14"/>
-      <c r="HG1" s="14"/>
-      <c r="HH1" s="14"/>
-      <c r="HI1" s="14"/>
-      <c r="HJ1" s="14"/>
-      <c r="HK1" s="14"/>
-      <c r="HL1" s="14"/>
-      <c r="HM1" s="14"/>
-      <c r="HN1" s="14"/>
-      <c r="HO1" s="14"/>
-      <c r="HP1" s="14"/>
-      <c r="HQ1" s="14"/>
-      <c r="HR1" s="14"/>
-      <c r="HS1" s="14"/>
-      <c r="HT1" s="14"/>
-      <c r="HU1" s="14"/>
-      <c r="HV1" s="14"/>
-      <c r="HW1" s="14"/>
-      <c r="HX1" s="14"/>
-      <c r="HY1" s="14"/>
-      <c r="HZ1" s="14"/>
-      <c r="IA1" s="14"/>
-      <c r="IB1" s="14"/>
-      <c r="IC1" s="14"/>
-      <c r="ID1" s="14"/>
-      <c r="IE1" s="14"/>
-      <c r="IF1" s="14"/>
-      <c r="IG1" s="14"/>
-      <c r="IH1" s="14"/>
-      <c r="II1" s="14"/>
-      <c r="IJ1" s="14"/>
-      <c r="IK1" s="14"/>
-      <c r="IL1" s="14"/>
-      <c r="IM1" s="14"/>
-      <c r="IN1" s="14"/>
-      <c r="IO1" s="14"/>
-      <c r="IP1" s="14"/>
-      <c r="IQ1" s="14"/>
-      <c r="IR1" s="14"/>
-      <c r="IS1" s="14"/>
-      <c r="IT1" s="14"/>
-      <c r="IU1" s="16"/>
-    </row>
-    <row r="2" ht="34.5" customHeight="1" spans="1:255">
-      <c r="A2" s="10" t="s">
+      <c r="Q1" s="7"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="10"/>
+      <c r="AD1" s="10"/>
+      <c r="AE1" s="10"/>
+      <c r="AF1" s="10"/>
+      <c r="AG1" s="10"/>
+      <c r="AH1" s="10"/>
+      <c r="AI1" s="10"/>
+      <c r="AJ1" s="10"/>
+      <c r="AK1" s="10"/>
+      <c r="AL1" s="10"/>
+      <c r="AM1" s="10"/>
+      <c r="AN1" s="10"/>
+      <c r="AO1" s="10"/>
+      <c r="AP1" s="10"/>
+      <c r="AQ1" s="10"/>
+      <c r="AR1" s="10"/>
+      <c r="AS1" s="10"/>
+      <c r="AT1" s="10"/>
+      <c r="AU1" s="10"/>
+      <c r="AV1" s="10"/>
+      <c r="AW1" s="10"/>
+      <c r="AX1" s="10"/>
+      <c r="AY1" s="10"/>
+      <c r="AZ1" s="10"/>
+      <c r="BA1" s="10"/>
+      <c r="BB1" s="10"/>
+      <c r="BC1" s="10"/>
+      <c r="BD1" s="10"/>
+      <c r="BE1" s="10"/>
+      <c r="BF1" s="10"/>
+      <c r="BG1" s="10"/>
+      <c r="BH1" s="10"/>
+      <c r="BI1" s="10"/>
+      <c r="BJ1" s="10"/>
+      <c r="BK1" s="10"/>
+      <c r="BL1" s="10"/>
+      <c r="BM1" s="10"/>
+      <c r="BN1" s="10"/>
+      <c r="BO1" s="10"/>
+      <c r="BP1" s="10"/>
+      <c r="BQ1" s="10"/>
+      <c r="BR1" s="10"/>
+      <c r="BS1" s="10"/>
+      <c r="BT1" s="10"/>
+      <c r="BU1" s="10"/>
+      <c r="BV1" s="10"/>
+      <c r="BW1" s="10"/>
+      <c r="BX1" s="10"/>
+      <c r="BY1" s="10"/>
+      <c r="BZ1" s="10"/>
+      <c r="CA1" s="10"/>
+      <c r="CB1" s="10"/>
+      <c r="CC1" s="10"/>
+      <c r="CD1" s="10"/>
+      <c r="CE1" s="10"/>
+      <c r="CF1" s="10"/>
+      <c r="CG1" s="10"/>
+      <c r="CH1" s="10"/>
+      <c r="CI1" s="10"/>
+      <c r="CJ1" s="10"/>
+      <c r="CK1" s="10"/>
+      <c r="CL1" s="10"/>
+      <c r="CM1" s="10"/>
+      <c r="CN1" s="10"/>
+      <c r="CO1" s="10"/>
+      <c r="CP1" s="10"/>
+      <c r="CQ1" s="10"/>
+      <c r="CR1" s="10"/>
+      <c r="CS1" s="10"/>
+      <c r="CT1" s="10"/>
+      <c r="CU1" s="10"/>
+      <c r="CV1" s="10"/>
+      <c r="CW1" s="10"/>
+      <c r="CX1" s="10"/>
+      <c r="CY1" s="10"/>
+      <c r="CZ1" s="10"/>
+      <c r="DA1" s="10"/>
+      <c r="DB1" s="10"/>
+      <c r="DC1" s="10"/>
+      <c r="DD1" s="10"/>
+      <c r="DE1" s="10"/>
+      <c r="DF1" s="10"/>
+      <c r="DG1" s="10"/>
+      <c r="DH1" s="10"/>
+      <c r="DI1" s="10"/>
+      <c r="DJ1" s="10"/>
+      <c r="DK1" s="10"/>
+      <c r="DL1" s="10"/>
+      <c r="DM1" s="10"/>
+      <c r="DN1" s="10"/>
+      <c r="DO1" s="10"/>
+      <c r="DP1" s="10"/>
+      <c r="DQ1" s="10"/>
+      <c r="DR1" s="10"/>
+      <c r="DS1" s="10"/>
+      <c r="DT1" s="10"/>
+      <c r="DU1" s="10"/>
+      <c r="DV1" s="10"/>
+      <c r="DW1" s="10"/>
+      <c r="DX1" s="10"/>
+      <c r="DY1" s="10"/>
+      <c r="DZ1" s="10"/>
+      <c r="EA1" s="10"/>
+      <c r="EB1" s="10"/>
+      <c r="EC1" s="10"/>
+      <c r="ED1" s="10"/>
+      <c r="EE1" s="10"/>
+      <c r="EF1" s="10"/>
+      <c r="EG1" s="10"/>
+      <c r="EH1" s="10"/>
+      <c r="EI1" s="10"/>
+      <c r="EJ1" s="10"/>
+      <c r="EK1" s="10"/>
+      <c r="EL1" s="10"/>
+      <c r="EM1" s="10"/>
+      <c r="EN1" s="10"/>
+      <c r="EO1" s="10"/>
+      <c r="EP1" s="10"/>
+      <c r="EQ1" s="10"/>
+      <c r="ER1" s="10"/>
+      <c r="ES1" s="10"/>
+      <c r="ET1" s="10"/>
+      <c r="EU1" s="10"/>
+      <c r="EV1" s="10"/>
+      <c r="EW1" s="10"/>
+      <c r="EX1" s="10"/>
+      <c r="EY1" s="10"/>
+      <c r="EZ1" s="10"/>
+      <c r="FA1" s="10"/>
+      <c r="FB1" s="10"/>
+      <c r="FC1" s="10"/>
+      <c r="FD1" s="10"/>
+      <c r="FE1" s="10"/>
+      <c r="FF1" s="10"/>
+      <c r="FG1" s="10"/>
+      <c r="FH1" s="10"/>
+      <c r="FI1" s="10"/>
+      <c r="FJ1" s="10"/>
+      <c r="FK1" s="10"/>
+      <c r="FL1" s="10"/>
+      <c r="FM1" s="10"/>
+      <c r="FN1" s="10"/>
+      <c r="FO1" s="10"/>
+      <c r="FP1" s="10"/>
+      <c r="FQ1" s="10"/>
+      <c r="FR1" s="10"/>
+      <c r="FS1" s="10"/>
+      <c r="FT1" s="10"/>
+      <c r="FU1" s="10"/>
+      <c r="FV1" s="10"/>
+      <c r="FW1" s="10"/>
+      <c r="FX1" s="10"/>
+      <c r="FY1" s="10"/>
+      <c r="FZ1" s="10"/>
+      <c r="GA1" s="10"/>
+      <c r="GB1" s="10"/>
+      <c r="GC1" s="10"/>
+      <c r="GD1" s="10"/>
+      <c r="GE1" s="10"/>
+      <c r="GF1" s="10"/>
+      <c r="GG1" s="10"/>
+      <c r="GH1" s="10"/>
+      <c r="GI1" s="10"/>
+      <c r="GJ1" s="10"/>
+      <c r="GK1" s="10"/>
+      <c r="GL1" s="10"/>
+      <c r="GM1" s="10"/>
+      <c r="GN1" s="10"/>
+      <c r="GO1" s="10"/>
+      <c r="GP1" s="10"/>
+      <c r="GQ1" s="10"/>
+      <c r="GR1" s="10"/>
+      <c r="GS1" s="10"/>
+      <c r="GT1" s="10"/>
+      <c r="GU1" s="10"/>
+      <c r="GV1" s="10"/>
+      <c r="GW1" s="10"/>
+      <c r="GX1" s="10"/>
+      <c r="GY1" s="10"/>
+      <c r="GZ1" s="10"/>
+      <c r="HA1" s="10"/>
+      <c r="HB1" s="10"/>
+      <c r="HC1" s="10"/>
+      <c r="HD1" s="10"/>
+      <c r="HE1" s="10"/>
+      <c r="HF1" s="10"/>
+      <c r="HG1" s="10"/>
+      <c r="HH1" s="10"/>
+      <c r="HI1" s="10"/>
+      <c r="HJ1" s="10"/>
+      <c r="HK1" s="10"/>
+      <c r="HL1" s="10"/>
+      <c r="HM1" s="10"/>
+      <c r="HN1" s="10"/>
+      <c r="HO1" s="10"/>
+      <c r="HP1" s="10"/>
+      <c r="HQ1" s="10"/>
+      <c r="HR1" s="10"/>
+      <c r="HS1" s="10"/>
+      <c r="HT1" s="10"/>
+      <c r="HU1" s="10"/>
+      <c r="HV1" s="10"/>
+      <c r="HW1" s="10"/>
+      <c r="HX1" s="10"/>
+      <c r="HY1" s="10"/>
+      <c r="HZ1" s="10"/>
+      <c r="IA1" s="10"/>
+      <c r="IB1" s="10"/>
+      <c r="IC1" s="10"/>
+      <c r="ID1" s="10"/>
+      <c r="IE1" s="10"/>
+      <c r="IF1" s="10"/>
+      <c r="IG1" s="10"/>
+      <c r="IH1" s="10"/>
+      <c r="II1" s="10"/>
+      <c r="IJ1" s="10"/>
+      <c r="IK1" s="10"/>
+      <c r="IL1" s="10"/>
+      <c r="IM1" s="10"/>
+      <c r="IN1" s="10"/>
+      <c r="IO1" s="10"/>
+      <c r="IP1" s="10"/>
+      <c r="IQ1" s="10"/>
+      <c r="IR1" s="10"/>
+      <c r="IS1" s="10"/>
+      <c r="IT1" s="10"/>
+      <c r="IU1" s="10"/>
+      <c r="IV1" s="12"/>
+    </row>
+    <row r="2" spans="1:256" ht="34.5" customHeight="1">
+      <c r="A2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10" t="s">
+      <c r="I2" s="6"/>
+      <c r="J2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="N2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="10"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="15"/>
-      <c r="AJ2" s="15"/>
-      <c r="AK2" s="15"/>
-      <c r="AL2" s="15"/>
-      <c r="AM2" s="15"/>
-      <c r="AN2" s="15"/>
-      <c r="AO2" s="15"/>
-      <c r="AP2" s="15"/>
-      <c r="AQ2" s="15"/>
-      <c r="AR2" s="15"/>
-      <c r="AS2" s="15"/>
-      <c r="AT2" s="15"/>
-      <c r="AU2" s="15"/>
-      <c r="AV2" s="15"/>
-      <c r="AW2" s="15"/>
-      <c r="AX2" s="15"/>
-      <c r="AY2" s="15"/>
-      <c r="AZ2" s="15"/>
-      <c r="BA2" s="15"/>
-      <c r="BB2" s="15"/>
-      <c r="BC2" s="15"/>
-      <c r="BD2" s="15"/>
-      <c r="BE2" s="15"/>
-      <c r="BF2" s="15"/>
-      <c r="BG2" s="15"/>
-      <c r="BH2" s="15"/>
-      <c r="BI2" s="15"/>
-      <c r="BJ2" s="15"/>
-      <c r="BK2" s="15"/>
-      <c r="BL2" s="15"/>
-      <c r="BM2" s="15"/>
-      <c r="BN2" s="15"/>
-      <c r="BO2" s="15"/>
-      <c r="BP2" s="15"/>
-      <c r="BQ2" s="15"/>
-      <c r="BR2" s="15"/>
-      <c r="BS2" s="15"/>
-      <c r="BT2" s="15"/>
-      <c r="BU2" s="15"/>
-      <c r="BV2" s="15"/>
-      <c r="BW2" s="15"/>
-      <c r="BX2" s="15"/>
-      <c r="BY2" s="15"/>
-      <c r="BZ2" s="15"/>
-      <c r="CA2" s="15"/>
-      <c r="CB2" s="15"/>
-      <c r="CC2" s="15"/>
-      <c r="CD2" s="15"/>
-      <c r="CE2" s="15"/>
-      <c r="CF2" s="15"/>
-      <c r="CG2" s="15"/>
-      <c r="CH2" s="15"/>
-      <c r="CI2" s="15"/>
-      <c r="CJ2" s="15"/>
-      <c r="CK2" s="15"/>
-      <c r="CL2" s="15"/>
-      <c r="CM2" s="15"/>
-      <c r="CN2" s="15"/>
-      <c r="CO2" s="15"/>
-      <c r="CP2" s="15"/>
-      <c r="CQ2" s="15"/>
-      <c r="CR2" s="15"/>
-      <c r="CS2" s="15"/>
-      <c r="CT2" s="15"/>
-      <c r="CU2" s="15"/>
-      <c r="CV2" s="15"/>
-      <c r="CW2" s="15"/>
-      <c r="CX2" s="15"/>
-      <c r="CY2" s="15"/>
-      <c r="CZ2" s="15"/>
-      <c r="DA2" s="15"/>
-      <c r="DB2" s="15"/>
-      <c r="DC2" s="15"/>
-      <c r="DD2" s="15"/>
-      <c r="DE2" s="15"/>
-      <c r="DF2" s="15"/>
-      <c r="DG2" s="15"/>
-      <c r="DH2" s="15"/>
-      <c r="DI2" s="15"/>
-      <c r="DJ2" s="15"/>
-      <c r="DK2" s="15"/>
-      <c r="DL2" s="15"/>
-      <c r="DM2" s="15"/>
-      <c r="DN2" s="15"/>
-      <c r="DO2" s="15"/>
-      <c r="DP2" s="15"/>
-      <c r="DQ2" s="15"/>
-      <c r="DR2" s="15"/>
-      <c r="DS2" s="15"/>
-      <c r="DT2" s="15"/>
-      <c r="DU2" s="15"/>
-      <c r="DV2" s="15"/>
-      <c r="DW2" s="15"/>
-      <c r="DX2" s="15"/>
-      <c r="DY2" s="15"/>
-      <c r="DZ2" s="15"/>
-      <c r="EA2" s="15"/>
-      <c r="EB2" s="15"/>
-      <c r="EC2" s="15"/>
-      <c r="ED2" s="15"/>
-      <c r="EE2" s="15"/>
-      <c r="EF2" s="15"/>
-      <c r="EG2" s="15"/>
-      <c r="EH2" s="15"/>
-      <c r="EI2" s="15"/>
-      <c r="EJ2" s="15"/>
-      <c r="EK2" s="15"/>
-      <c r="EL2" s="15"/>
-      <c r="EM2" s="15"/>
-      <c r="EN2" s="15"/>
-      <c r="EO2" s="15"/>
-      <c r="EP2" s="15"/>
-      <c r="EQ2" s="15"/>
-      <c r="ER2" s="15"/>
-      <c r="ES2" s="15"/>
-      <c r="ET2" s="15"/>
-      <c r="EU2" s="15"/>
-      <c r="EV2" s="15"/>
-      <c r="EW2" s="15"/>
-      <c r="EX2" s="15"/>
-      <c r="EY2" s="15"/>
-      <c r="EZ2" s="15"/>
-      <c r="FA2" s="15"/>
-      <c r="FB2" s="15"/>
-      <c r="FC2" s="15"/>
-      <c r="FD2" s="15"/>
-      <c r="FE2" s="15"/>
-      <c r="FF2" s="15"/>
-      <c r="FG2" s="15"/>
-      <c r="FH2" s="15"/>
-      <c r="FI2" s="15"/>
-      <c r="FJ2" s="15"/>
-      <c r="FK2" s="15"/>
-      <c r="FL2" s="15"/>
-      <c r="FM2" s="15"/>
-      <c r="FN2" s="15"/>
-      <c r="FO2" s="15"/>
-      <c r="FP2" s="15"/>
-      <c r="FQ2" s="15"/>
-      <c r="FR2" s="15"/>
-      <c r="FS2" s="15"/>
-      <c r="FT2" s="15"/>
-      <c r="FU2" s="15"/>
-      <c r="FV2" s="15"/>
-      <c r="FW2" s="15"/>
-      <c r="FX2" s="15"/>
-      <c r="FY2" s="15"/>
-      <c r="FZ2" s="15"/>
-      <c r="GA2" s="15"/>
-      <c r="GB2" s="15"/>
-      <c r="GC2" s="15"/>
-      <c r="GD2" s="15"/>
-      <c r="GE2" s="15"/>
-      <c r="GF2" s="15"/>
-      <c r="GG2" s="15"/>
-      <c r="GH2" s="15"/>
-      <c r="GI2" s="15"/>
-      <c r="GJ2" s="15"/>
-      <c r="GK2" s="15"/>
-      <c r="GL2" s="15"/>
-      <c r="GM2" s="15"/>
-      <c r="GN2" s="15"/>
-      <c r="GO2" s="15"/>
-      <c r="GP2" s="15"/>
-      <c r="GQ2" s="15"/>
-      <c r="GR2" s="15"/>
-      <c r="GS2" s="15"/>
-      <c r="GT2" s="15"/>
-      <c r="GU2" s="15"/>
-      <c r="GV2" s="15"/>
-      <c r="GW2" s="15"/>
-      <c r="GX2" s="15"/>
-      <c r="GY2" s="15"/>
-      <c r="GZ2" s="15"/>
-      <c r="HA2" s="15"/>
-      <c r="HB2" s="15"/>
-      <c r="HC2" s="15"/>
-      <c r="HD2" s="15"/>
-      <c r="HE2" s="15"/>
-      <c r="HF2" s="15"/>
-      <c r="HG2" s="15"/>
-      <c r="HH2" s="15"/>
-      <c r="HI2" s="15"/>
-      <c r="HJ2" s="15"/>
-      <c r="HK2" s="15"/>
-      <c r="HL2" s="15"/>
-      <c r="HM2" s="15"/>
-      <c r="HN2" s="15"/>
-      <c r="HO2" s="15"/>
-      <c r="HP2" s="15"/>
-      <c r="HQ2" s="15"/>
-      <c r="HR2" s="15"/>
-      <c r="HS2" s="15"/>
-      <c r="HT2" s="15"/>
-      <c r="HU2" s="15"/>
-      <c r="HV2" s="15"/>
-      <c r="HW2" s="15"/>
-      <c r="HX2" s="15"/>
-      <c r="HY2" s="15"/>
-      <c r="HZ2" s="15"/>
-      <c r="IA2" s="15"/>
-      <c r="IB2" s="15"/>
-      <c r="IC2" s="15"/>
-      <c r="ID2" s="15"/>
-      <c r="IE2" s="15"/>
-      <c r="IF2" s="15"/>
-      <c r="IG2" s="15"/>
-      <c r="IH2" s="15"/>
-      <c r="II2" s="15"/>
-      <c r="IJ2" s="15"/>
-      <c r="IK2" s="15"/>
-      <c r="IL2" s="15"/>
-      <c r="IM2" s="15"/>
-      <c r="IN2" s="15"/>
-      <c r="IO2" s="15"/>
-      <c r="IP2" s="15"/>
-      <c r="IQ2" s="15"/>
-      <c r="IR2" s="15"/>
-      <c r="IS2" s="15"/>
-      <c r="IT2" s="15"/>
-      <c r="IU2" s="17"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
+      <c r="AE2" s="11"/>
+      <c r="AF2" s="11"/>
+      <c r="AG2" s="11"/>
+      <c r="AH2" s="11"/>
+      <c r="AI2" s="11"/>
+      <c r="AJ2" s="11"/>
+      <c r="AK2" s="11"/>
+      <c r="AL2" s="11"/>
+      <c r="AM2" s="11"/>
+      <c r="AN2" s="11"/>
+      <c r="AO2" s="11"/>
+      <c r="AP2" s="11"/>
+      <c r="AQ2" s="11"/>
+      <c r="AR2" s="11"/>
+      <c r="AS2" s="11"/>
+      <c r="AT2" s="11"/>
+      <c r="AU2" s="11"/>
+      <c r="AV2" s="11"/>
+      <c r="AW2" s="11"/>
+      <c r="AX2" s="11"/>
+      <c r="AY2" s="11"/>
+      <c r="AZ2" s="11"/>
+      <c r="BA2" s="11"/>
+      <c r="BB2" s="11"/>
+      <c r="BC2" s="11"/>
+      <c r="BD2" s="11"/>
+      <c r="BE2" s="11"/>
+      <c r="BF2" s="11"/>
+      <c r="BG2" s="11"/>
+      <c r="BH2" s="11"/>
+      <c r="BI2" s="11"/>
+      <c r="BJ2" s="11"/>
+      <c r="BK2" s="11"/>
+      <c r="BL2" s="11"/>
+      <c r="BM2" s="11"/>
+      <c r="BN2" s="11"/>
+      <c r="BO2" s="11"/>
+      <c r="BP2" s="11"/>
+      <c r="BQ2" s="11"/>
+      <c r="BR2" s="11"/>
+      <c r="BS2" s="11"/>
+      <c r="BT2" s="11"/>
+      <c r="BU2" s="11"/>
+      <c r="BV2" s="11"/>
+      <c r="BW2" s="11"/>
+      <c r="BX2" s="11"/>
+      <c r="BY2" s="11"/>
+      <c r="BZ2" s="11"/>
+      <c r="CA2" s="11"/>
+      <c r="CB2" s="11"/>
+      <c r="CC2" s="11"/>
+      <c r="CD2" s="11"/>
+      <c r="CE2" s="11"/>
+      <c r="CF2" s="11"/>
+      <c r="CG2" s="11"/>
+      <c r="CH2" s="11"/>
+      <c r="CI2" s="11"/>
+      <c r="CJ2" s="11"/>
+      <c r="CK2" s="11"/>
+      <c r="CL2" s="11"/>
+      <c r="CM2" s="11"/>
+      <c r="CN2" s="11"/>
+      <c r="CO2" s="11"/>
+      <c r="CP2" s="11"/>
+      <c r="CQ2" s="11"/>
+      <c r="CR2" s="11"/>
+      <c r="CS2" s="11"/>
+      <c r="CT2" s="11"/>
+      <c r="CU2" s="11"/>
+      <c r="CV2" s="11"/>
+      <c r="CW2" s="11"/>
+      <c r="CX2" s="11"/>
+      <c r="CY2" s="11"/>
+      <c r="CZ2" s="11"/>
+      <c r="DA2" s="11"/>
+      <c r="DB2" s="11"/>
+      <c r="DC2" s="11"/>
+      <c r="DD2" s="11"/>
+      <c r="DE2" s="11"/>
+      <c r="DF2" s="11"/>
+      <c r="DG2" s="11"/>
+      <c r="DH2" s="11"/>
+      <c r="DI2" s="11"/>
+      <c r="DJ2" s="11"/>
+      <c r="DK2" s="11"/>
+      <c r="DL2" s="11"/>
+      <c r="DM2" s="11"/>
+      <c r="DN2" s="11"/>
+      <c r="DO2" s="11"/>
+      <c r="DP2" s="11"/>
+      <c r="DQ2" s="11"/>
+      <c r="DR2" s="11"/>
+      <c r="DS2" s="11"/>
+      <c r="DT2" s="11"/>
+      <c r="DU2" s="11"/>
+      <c r="DV2" s="11"/>
+      <c r="DW2" s="11"/>
+      <c r="DX2" s="11"/>
+      <c r="DY2" s="11"/>
+      <c r="DZ2" s="11"/>
+      <c r="EA2" s="11"/>
+      <c r="EB2" s="11"/>
+      <c r="EC2" s="11"/>
+      <c r="ED2" s="11"/>
+      <c r="EE2" s="11"/>
+      <c r="EF2" s="11"/>
+      <c r="EG2" s="11"/>
+      <c r="EH2" s="11"/>
+      <c r="EI2" s="11"/>
+      <c r="EJ2" s="11"/>
+      <c r="EK2" s="11"/>
+      <c r="EL2" s="11"/>
+      <c r="EM2" s="11"/>
+      <c r="EN2" s="11"/>
+      <c r="EO2" s="11"/>
+      <c r="EP2" s="11"/>
+      <c r="EQ2" s="11"/>
+      <c r="ER2" s="11"/>
+      <c r="ES2" s="11"/>
+      <c r="ET2" s="11"/>
+      <c r="EU2" s="11"/>
+      <c r="EV2" s="11"/>
+      <c r="EW2" s="11"/>
+      <c r="EX2" s="11"/>
+      <c r="EY2" s="11"/>
+      <c r="EZ2" s="11"/>
+      <c r="FA2" s="11"/>
+      <c r="FB2" s="11"/>
+      <c r="FC2" s="11"/>
+      <c r="FD2" s="11"/>
+      <c r="FE2" s="11"/>
+      <c r="FF2" s="11"/>
+      <c r="FG2" s="11"/>
+      <c r="FH2" s="11"/>
+      <c r="FI2" s="11"/>
+      <c r="FJ2" s="11"/>
+      <c r="FK2" s="11"/>
+      <c r="FL2" s="11"/>
+      <c r="FM2" s="11"/>
+      <c r="FN2" s="11"/>
+      <c r="FO2" s="11"/>
+      <c r="FP2" s="11"/>
+      <c r="FQ2" s="11"/>
+      <c r="FR2" s="11"/>
+      <c r="FS2" s="11"/>
+      <c r="FT2" s="11"/>
+      <c r="FU2" s="11"/>
+      <c r="FV2" s="11"/>
+      <c r="FW2" s="11"/>
+      <c r="FX2" s="11"/>
+      <c r="FY2" s="11"/>
+      <c r="FZ2" s="11"/>
+      <c r="GA2" s="11"/>
+      <c r="GB2" s="11"/>
+      <c r="GC2" s="11"/>
+      <c r="GD2" s="11"/>
+      <c r="GE2" s="11"/>
+      <c r="GF2" s="11"/>
+      <c r="GG2" s="11"/>
+      <c r="GH2" s="11"/>
+      <c r="GI2" s="11"/>
+      <c r="GJ2" s="11"/>
+      <c r="GK2" s="11"/>
+      <c r="GL2" s="11"/>
+      <c r="GM2" s="11"/>
+      <c r="GN2" s="11"/>
+      <c r="GO2" s="11"/>
+      <c r="GP2" s="11"/>
+      <c r="GQ2" s="11"/>
+      <c r="GR2" s="11"/>
+      <c r="GS2" s="11"/>
+      <c r="GT2" s="11"/>
+      <c r="GU2" s="11"/>
+      <c r="GV2" s="11"/>
+      <c r="GW2" s="11"/>
+      <c r="GX2" s="11"/>
+      <c r="GY2" s="11"/>
+      <c r="GZ2" s="11"/>
+      <c r="HA2" s="11"/>
+      <c r="HB2" s="11"/>
+      <c r="HC2" s="11"/>
+      <c r="HD2" s="11"/>
+      <c r="HE2" s="11"/>
+      <c r="HF2" s="11"/>
+      <c r="HG2" s="11"/>
+      <c r="HH2" s="11"/>
+      <c r="HI2" s="11"/>
+      <c r="HJ2" s="11"/>
+      <c r="HK2" s="11"/>
+      <c r="HL2" s="11"/>
+      <c r="HM2" s="11"/>
+      <c r="HN2" s="11"/>
+      <c r="HO2" s="11"/>
+      <c r="HP2" s="11"/>
+      <c r="HQ2" s="11"/>
+      <c r="HR2" s="11"/>
+      <c r="HS2" s="11"/>
+      <c r="HT2" s="11"/>
+      <c r="HU2" s="11"/>
+      <c r="HV2" s="11"/>
+      <c r="HW2" s="11"/>
+      <c r="HX2" s="11"/>
+      <c r="HY2" s="11"/>
+      <c r="HZ2" s="11"/>
+      <c r="IA2" s="11"/>
+      <c r="IB2" s="11"/>
+      <c r="IC2" s="11"/>
+      <c r="ID2" s="11"/>
+      <c r="IE2" s="11"/>
+      <c r="IF2" s="11"/>
+      <c r="IG2" s="11"/>
+      <c r="IH2" s="11"/>
+      <c r="II2" s="11"/>
+      <c r="IJ2" s="11"/>
+      <c r="IK2" s="11"/>
+      <c r="IL2" s="11"/>
+      <c r="IM2" s="11"/>
+      <c r="IN2" s="11"/>
+      <c r="IO2" s="11"/>
+      <c r="IP2" s="11"/>
+      <c r="IQ2" s="11"/>
+      <c r="IR2" s="11"/>
+      <c r="IS2" s="11"/>
+      <c r="IT2" s="11"/>
+      <c r="IU2" s="11"/>
+      <c r="IV2" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -2830,121 +2208,120 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
-  <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultColWidth="8.85714285714286" defaultRowHeight="12.75" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:IR23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="108.714285714286" style="1" customWidth="1"/>
-    <col min="2" max="252" width="8.85714285714286" style="1" customWidth="1"/>
+    <col min="1" max="1" width="108.6640625" style="1" customWidth="1"/>
+    <col min="2" max="252" width="8.83203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.7" customHeight="1" spans="1:1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:1" ht="13.75" customHeight="1">
+      <c r="A1" s="14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" ht="13.7" customHeight="1" spans="1:1">
-      <c r="A2" s="3"/>
-    </row>
-    <row r="3" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A3" s="4" t="s">
+    <row r="2" spans="1:1" ht="13.75" customHeight="1">
+      <c r="A2" s="15"/>
+    </row>
+    <row r="3" spans="1:1" ht="16" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:1" ht="16" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:1" ht="16" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:1" ht="16" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:1" ht="16" customHeight="1">
+      <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:1" ht="16" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:1" ht="16" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:1" ht="16" customHeight="1">
+      <c r="A10" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A11" s="5"/>
-    </row>
-    <row r="12" ht="13.7" customHeight="1" spans="1:1">
-      <c r="A12" s="6" t="s">
+    <row r="11" spans="1:1" ht="16" customHeight="1">
+      <c r="A11" s="3"/>
+    </row>
+    <row r="12" spans="1:1" ht="13.75" customHeight="1">
+      <c r="A12" s="16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" ht="12" customHeight="1" spans="1:1">
-      <c r="A13" s="7"/>
-    </row>
-    <row r="14" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A14" s="8" t="s">
+    <row r="13" spans="1:1" ht="12" customHeight="1">
+      <c r="A13" s="17"/>
+    </row>
+    <row r="14" spans="1:1" ht="16" customHeight="1">
+      <c r="A14" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A15" s="8" t="s">
+    <row r="15" spans="1:1" ht="16" customHeight="1">
+      <c r="A15" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A16" s="8" t="s">
+    <row r="16" spans="1:1" ht="16" customHeight="1">
+      <c r="A16" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A17" s="8" t="s">
+    <row r="17" spans="1:1" ht="16" customHeight="1">
+      <c r="A17" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A18" s="8" t="s">
+    <row r="18" spans="1:1" ht="16" customHeight="1">
+      <c r="A18" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A19" s="8" t="s">
+    <row r="19" spans="1:1" ht="16" customHeight="1">
+      <c r="A19" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A20" s="8" t="s">
+    <row r="20" spans="1:1" ht="16" customHeight="1">
+      <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A21" s="8" t="s">
+    <row r="21" spans="1:1" ht="16" customHeight="1">
+      <c r="A21" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="22" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A22" s="8" t="s">
+    <row r="22" spans="1:1" ht="16" customHeight="1">
+      <c r="A22" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" ht="13.5" customHeight="1" spans="1:1">
-      <c r="A23" s="8" t="s">
+    <row r="23" spans="1:1" ht="13.5" customHeight="1">
+      <c r="A23" s="4" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2953,8 +2330,8 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A12:A13"/>
   </mergeCells>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qtang/Desktop/APM/Git/hc-apm-web/src/src/main/webapp/portal/uaa/userAccount/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{87CDB458-3D9E-1A47-9D14-BC578FD393EE}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{8FFE83AD-D314-014D-B918-DBE3F3CE4E0E}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="28360" windowHeight="10220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10610"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qtang/Desktop/APM/Git/hc-apm-web/src/src/main/webapp/portal/uaa/userAccount/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212670825\Desktop\APM\Git\hc-apm-web\src\src\main\webapp\portal\uaa\userAccount\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{8FFE83AD-D314-014D-B918-DBE3F3CE4E0E}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24859A24-79FC-4130-8276-00D5077D0C13}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="28360" windowHeight="10220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
   <si>
     <t>所属集团</t>
   </si>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t>初始密码</t>
+  </si>
+  <si>
+    <t>职务</t>
   </si>
 </sst>
 </file>
@@ -1607,24 +1610,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IV2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12.75" customHeight="1"/>
+  <dimension ref="A1:IW2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="13.5" style="1" customWidth="1"/>
+    <col min="3" max="4" width="13.44140625" style="1" customWidth="1"/>
     <col min="5" max="6" width="14.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
-    <col min="8" max="9" width="8.83203125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="8.77734375" style="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
-    <col min="11" max="12" width="8.83203125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="8.77734375" style="1" customWidth="1"/>
     <col min="13" max="13" width="24.6640625" style="1" customWidth="1"/>
-    <col min="14" max="15" width="30" style="1" customWidth="1"/>
-    <col min="16" max="16" width="32.6640625" style="1" customWidth="1"/>
-    <col min="17" max="256" width="8.83203125" style="1" customWidth="1"/>
+    <col min="14" max="16" width="30" style="1" customWidth="1"/>
+    <col min="17" max="17" width="32.6640625" style="1" customWidth="1"/>
+    <col min="18" max="257" width="8.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:256" ht="30.75" customHeight="1">
+    <row r="1" spans="1:257" ht="30.75" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1668,13 +1671,15 @@
         <v>13</v>
       </c>
       <c r="O1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="10"/>
+      <c r="R1" s="7"/>
       <c r="S1" s="10"/>
       <c r="T1" s="10"/>
       <c r="U1" s="10"/>
@@ -1912,9 +1917,10 @@
       <c r="IS1" s="10"/>
       <c r="IT1" s="10"/>
       <c r="IU1" s="10"/>
-      <c r="IV1" s="12"/>
-    </row>
-    <row r="2" spans="1:256" ht="34.5" customHeight="1">
+      <c r="IV1" s="10"/>
+      <c r="IW1" s="12"/>
+    </row>
+    <row r="2" spans="1:257" ht="34.5" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>15</v>
       </c>
@@ -1955,10 +1961,12 @@
       <c r="N2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="8"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="11"/>
+      <c r="O2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="9"/>
       <c r="S2" s="11"/>
       <c r="T2" s="11"/>
       <c r="U2" s="11"/>
@@ -2196,7 +2204,8 @@
       <c r="IS2" s="11"/>
       <c r="IT2" s="11"/>
       <c r="IU2" s="11"/>
-      <c r="IV2" s="13"/>
+      <c r="IV2" s="11"/>
+      <c r="IW2" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2210,64 +2219,64 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:IR23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="108.6640625" style="1" customWidth="1"/>
-    <col min="2" max="252" width="8.83203125" style="1" customWidth="1"/>
+    <col min="2" max="252" width="8.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="13.75" customHeight="1">
+    <row r="1" spans="1:1" ht="13.8" customHeight="1">
       <c r="A1" s="14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="13.75" customHeight="1">
+    <row r="2" spans="1:1" ht="13.8" customHeight="1">
       <c r="A2" s="15"/>
     </row>
-    <row r="3" spans="1:1" ht="16" customHeight="1">
+    <row r="3" spans="1:1" ht="16.05" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="16" customHeight="1">
+    <row r="4" spans="1:1" ht="16.05" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="16" customHeight="1">
+    <row r="5" spans="1:1" ht="16.05" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="16" customHeight="1">
+    <row r="6" spans="1:1" ht="16.05" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="16" customHeight="1">
+    <row r="7" spans="1:1" ht="16.05" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="16" customHeight="1">
+    <row r="8" spans="1:1" ht="16.05" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="16" customHeight="1">
+    <row r="9" spans="1:1" ht="16.05" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="16" customHeight="1">
+    <row r="10" spans="1:1" ht="16.05" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="16" customHeight="1">
+    <row r="11" spans="1:1" ht="16.05" customHeight="1">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:1" ht="13.75" customHeight="1">
+    <row r="12" spans="1:1" ht="13.8" customHeight="1">
       <c r="A12" s="16" t="s">
         <v>36</v>
       </c>
@@ -2275,47 +2284,47 @@
     <row r="13" spans="1:1" ht="12" customHeight="1">
       <c r="A13" s="17"/>
     </row>
-    <row r="14" spans="1:1" ht="16" customHeight="1">
+    <row r="14" spans="1:1" ht="16.05" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="16" customHeight="1">
+    <row r="15" spans="1:1" ht="16.05" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="16" customHeight="1">
+    <row r="16" spans="1:1" ht="16.05" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="16" customHeight="1">
+    <row r="17" spans="1:1" ht="16.05" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="16" customHeight="1">
+    <row r="18" spans="1:1" ht="16.05" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="16" customHeight="1">
+    <row r="19" spans="1:1" ht="16.05" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="16" customHeight="1">
+    <row r="20" spans="1:1" ht="16.05" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="16" customHeight="1">
+    <row r="21" spans="1:1" ht="16.05" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="16" customHeight="1">
+    <row r="22" spans="1:1" ht="16.05" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>45</v>
       </c>

--- a/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212670825\Desktop\APM\Git\hc-apm-web\src\src\main\webapp\portal\uaa\userAccount\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24859A24-79FC-4130-8276-00D5077D0C13}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCA2815-638A-4FB5-A2DC-30710618B7B9}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
   <si>
     <t>所属集团</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>职务</t>
+  </si>
+  <si>
+    <t>标签</t>
   </si>
 </sst>
 </file>
@@ -1610,7 +1613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IW2"/>
+  <dimension ref="A1:IX2"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.33203125" style="1" customWidth="1"/>
@@ -1622,12 +1625,12 @@
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
     <col min="11" max="12" width="8.77734375" style="1" customWidth="1"/>
     <col min="13" max="13" width="24.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16" width="30" style="1" customWidth="1"/>
-    <col min="17" max="17" width="32.6640625" style="1" customWidth="1"/>
-    <col min="18" max="257" width="8.77734375" style="1" customWidth="1"/>
+    <col min="14" max="17" width="30" style="1" customWidth="1"/>
+    <col min="18" max="18" width="32.6640625" style="1" customWidth="1"/>
+    <col min="19" max="258" width="8.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:257" ht="30.75" customHeight="1">
+    <row r="1" spans="1:258" ht="30.75" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1674,13 +1677,15 @@
         <v>48</v>
       </c>
       <c r="P1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="7"/>
-      <c r="S1" s="10"/>
+      <c r="S1" s="7"/>
       <c r="T1" s="10"/>
       <c r="U1" s="10"/>
       <c r="V1" s="10"/>
@@ -1918,9 +1923,10 @@
       <c r="IT1" s="10"/>
       <c r="IU1" s="10"/>
       <c r="IV1" s="10"/>
-      <c r="IW1" s="12"/>
-    </row>
-    <row r="2" spans="1:257" ht="34.5" customHeight="1">
+      <c r="IW1" s="10"/>
+      <c r="IX1" s="12"/>
+    </row>
+    <row r="2" spans="1:258" ht="34.5" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>15</v>
       </c>
@@ -1965,9 +1971,9 @@
         <v>43</v>
       </c>
       <c r="P2" s="8"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="11"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="9"/>
       <c r="T2" s="11"/>
       <c r="U2" s="11"/>
       <c r="V2" s="11"/>
@@ -2205,7 +2211,8 @@
       <c r="IT2" s="11"/>
       <c r="IU2" s="11"/>
       <c r="IV2" s="11"/>
-      <c r="IW2" s="13"/>
+      <c r="IW2" s="11"/>
+      <c r="IX2" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212670825\Desktop\APM\Git\hc-apm-web\src\src\main\webapp\portal\uaa\userAccount\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\zp\code\web\hc-apm-web-ib\src\src\main\webapp\portal\uaa\userAccount\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCA2815-638A-4FB5-A2DC-30710618B7B9}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA916DC9-9AB8-47D8-B24D-0BE529742578}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <t>所属集团</t>
   </si>
@@ -294,12 +294,18 @@
   <si>
     <t>标签</t>
   </si>
+  <si>
+    <t>所属代理商</t>
+  </si>
+  <si>
+    <t>XXXX</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -317,6 +323,12 @@
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="GE Inspira Sans"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -339,7 +351,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -452,11 +464,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -468,11 +521,9 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -488,6 +539,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1626,8 +1686,8 @@
     <col min="11" max="12" width="8.77734375" style="1" customWidth="1"/>
     <col min="13" max="13" width="24.6640625" style="1" customWidth="1"/>
     <col min="14" max="17" width="30" style="1" customWidth="1"/>
-    <col min="18" max="18" width="32.6640625" style="1" customWidth="1"/>
-    <col min="19" max="258" width="8.77734375" style="1" customWidth="1"/>
+    <col min="18" max="19" width="32.6640625" style="1" customWidth="1"/>
+    <col min="20" max="258" width="8.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:258" ht="30.75" customHeight="1">
@@ -1685,246 +1745,248 @@
       <c r="R1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="7"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="10"/>
-      <c r="AB1" s="10"/>
-      <c r="AC1" s="10"/>
-      <c r="AD1" s="10"/>
-      <c r="AE1" s="10"/>
-      <c r="AF1" s="10"/>
-      <c r="AG1" s="10"/>
-      <c r="AH1" s="10"/>
-      <c r="AI1" s="10"/>
-      <c r="AJ1" s="10"/>
-      <c r="AK1" s="10"/>
-      <c r="AL1" s="10"/>
-      <c r="AM1" s="10"/>
-      <c r="AN1" s="10"/>
-      <c r="AO1" s="10"/>
-      <c r="AP1" s="10"/>
-      <c r="AQ1" s="10"/>
-      <c r="AR1" s="10"/>
-      <c r="AS1" s="10"/>
-      <c r="AT1" s="10"/>
-      <c r="AU1" s="10"/>
-      <c r="AV1" s="10"/>
-      <c r="AW1" s="10"/>
-      <c r="AX1" s="10"/>
-      <c r="AY1" s="10"/>
-      <c r="AZ1" s="10"/>
-      <c r="BA1" s="10"/>
-      <c r="BB1" s="10"/>
-      <c r="BC1" s="10"/>
-      <c r="BD1" s="10"/>
-      <c r="BE1" s="10"/>
-      <c r="BF1" s="10"/>
-      <c r="BG1" s="10"/>
-      <c r="BH1" s="10"/>
-      <c r="BI1" s="10"/>
-      <c r="BJ1" s="10"/>
-      <c r="BK1" s="10"/>
-      <c r="BL1" s="10"/>
-      <c r="BM1" s="10"/>
-      <c r="BN1" s="10"/>
-      <c r="BO1" s="10"/>
-      <c r="BP1" s="10"/>
-      <c r="BQ1" s="10"/>
-      <c r="BR1" s="10"/>
-      <c r="BS1" s="10"/>
-      <c r="BT1" s="10"/>
-      <c r="BU1" s="10"/>
-      <c r="BV1" s="10"/>
-      <c r="BW1" s="10"/>
-      <c r="BX1" s="10"/>
-      <c r="BY1" s="10"/>
-      <c r="BZ1" s="10"/>
-      <c r="CA1" s="10"/>
-      <c r="CB1" s="10"/>
-      <c r="CC1" s="10"/>
-      <c r="CD1" s="10"/>
-      <c r="CE1" s="10"/>
-      <c r="CF1" s="10"/>
-      <c r="CG1" s="10"/>
-      <c r="CH1" s="10"/>
-      <c r="CI1" s="10"/>
-      <c r="CJ1" s="10"/>
-      <c r="CK1" s="10"/>
-      <c r="CL1" s="10"/>
-      <c r="CM1" s="10"/>
-      <c r="CN1" s="10"/>
-      <c r="CO1" s="10"/>
-      <c r="CP1" s="10"/>
-      <c r="CQ1" s="10"/>
-      <c r="CR1" s="10"/>
-      <c r="CS1" s="10"/>
-      <c r="CT1" s="10"/>
-      <c r="CU1" s="10"/>
-      <c r="CV1" s="10"/>
-      <c r="CW1" s="10"/>
-      <c r="CX1" s="10"/>
-      <c r="CY1" s="10"/>
-      <c r="CZ1" s="10"/>
-      <c r="DA1" s="10"/>
-      <c r="DB1" s="10"/>
-      <c r="DC1" s="10"/>
-      <c r="DD1" s="10"/>
-      <c r="DE1" s="10"/>
-      <c r="DF1" s="10"/>
-      <c r="DG1" s="10"/>
-      <c r="DH1" s="10"/>
-      <c r="DI1" s="10"/>
-      <c r="DJ1" s="10"/>
-      <c r="DK1" s="10"/>
-      <c r="DL1" s="10"/>
-      <c r="DM1" s="10"/>
-      <c r="DN1" s="10"/>
-      <c r="DO1" s="10"/>
-      <c r="DP1" s="10"/>
-      <c r="DQ1" s="10"/>
-      <c r="DR1" s="10"/>
-      <c r="DS1" s="10"/>
-      <c r="DT1" s="10"/>
-      <c r="DU1" s="10"/>
-      <c r="DV1" s="10"/>
-      <c r="DW1" s="10"/>
-      <c r="DX1" s="10"/>
-      <c r="DY1" s="10"/>
-      <c r="DZ1" s="10"/>
-      <c r="EA1" s="10"/>
-      <c r="EB1" s="10"/>
-      <c r="EC1" s="10"/>
-      <c r="ED1" s="10"/>
-      <c r="EE1" s="10"/>
-      <c r="EF1" s="10"/>
-      <c r="EG1" s="10"/>
-      <c r="EH1" s="10"/>
-      <c r="EI1" s="10"/>
-      <c r="EJ1" s="10"/>
-      <c r="EK1" s="10"/>
-      <c r="EL1" s="10"/>
-      <c r="EM1" s="10"/>
-      <c r="EN1" s="10"/>
-      <c r="EO1" s="10"/>
-      <c r="EP1" s="10"/>
-      <c r="EQ1" s="10"/>
-      <c r="ER1" s="10"/>
-      <c r="ES1" s="10"/>
-      <c r="ET1" s="10"/>
-      <c r="EU1" s="10"/>
-      <c r="EV1" s="10"/>
-      <c r="EW1" s="10"/>
-      <c r="EX1" s="10"/>
-      <c r="EY1" s="10"/>
-      <c r="EZ1" s="10"/>
-      <c r="FA1" s="10"/>
-      <c r="FB1" s="10"/>
-      <c r="FC1" s="10"/>
-      <c r="FD1" s="10"/>
-      <c r="FE1" s="10"/>
-      <c r="FF1" s="10"/>
-      <c r="FG1" s="10"/>
-      <c r="FH1" s="10"/>
-      <c r="FI1" s="10"/>
-      <c r="FJ1" s="10"/>
-      <c r="FK1" s="10"/>
-      <c r="FL1" s="10"/>
-      <c r="FM1" s="10"/>
-      <c r="FN1" s="10"/>
-      <c r="FO1" s="10"/>
-      <c r="FP1" s="10"/>
-      <c r="FQ1" s="10"/>
-      <c r="FR1" s="10"/>
-      <c r="FS1" s="10"/>
-      <c r="FT1" s="10"/>
-      <c r="FU1" s="10"/>
-      <c r="FV1" s="10"/>
-      <c r="FW1" s="10"/>
-      <c r="FX1" s="10"/>
-      <c r="FY1" s="10"/>
-      <c r="FZ1" s="10"/>
-      <c r="GA1" s="10"/>
-      <c r="GB1" s="10"/>
-      <c r="GC1" s="10"/>
-      <c r="GD1" s="10"/>
-      <c r="GE1" s="10"/>
-      <c r="GF1" s="10"/>
-      <c r="GG1" s="10"/>
-      <c r="GH1" s="10"/>
-      <c r="GI1" s="10"/>
-      <c r="GJ1" s="10"/>
-      <c r="GK1" s="10"/>
-      <c r="GL1" s="10"/>
-      <c r="GM1" s="10"/>
-      <c r="GN1" s="10"/>
-      <c r="GO1" s="10"/>
-      <c r="GP1" s="10"/>
-      <c r="GQ1" s="10"/>
-      <c r="GR1" s="10"/>
-      <c r="GS1" s="10"/>
-      <c r="GT1" s="10"/>
-      <c r="GU1" s="10"/>
-      <c r="GV1" s="10"/>
-      <c r="GW1" s="10"/>
-      <c r="GX1" s="10"/>
-      <c r="GY1" s="10"/>
-      <c r="GZ1" s="10"/>
-      <c r="HA1" s="10"/>
-      <c r="HB1" s="10"/>
-      <c r="HC1" s="10"/>
-      <c r="HD1" s="10"/>
-      <c r="HE1" s="10"/>
-      <c r="HF1" s="10"/>
-      <c r="HG1" s="10"/>
-      <c r="HH1" s="10"/>
-      <c r="HI1" s="10"/>
-      <c r="HJ1" s="10"/>
-      <c r="HK1" s="10"/>
-      <c r="HL1" s="10"/>
-      <c r="HM1" s="10"/>
-      <c r="HN1" s="10"/>
-      <c r="HO1" s="10"/>
-      <c r="HP1" s="10"/>
-      <c r="HQ1" s="10"/>
-      <c r="HR1" s="10"/>
-      <c r="HS1" s="10"/>
-      <c r="HT1" s="10"/>
-      <c r="HU1" s="10"/>
-      <c r="HV1" s="10"/>
-      <c r="HW1" s="10"/>
-      <c r="HX1" s="10"/>
-      <c r="HY1" s="10"/>
-      <c r="HZ1" s="10"/>
-      <c r="IA1" s="10"/>
-      <c r="IB1" s="10"/>
-      <c r="IC1" s="10"/>
-      <c r="ID1" s="10"/>
-      <c r="IE1" s="10"/>
-      <c r="IF1" s="10"/>
-      <c r="IG1" s="10"/>
-      <c r="IH1" s="10"/>
-      <c r="II1" s="10"/>
-      <c r="IJ1" s="10"/>
-      <c r="IK1" s="10"/>
-      <c r="IL1" s="10"/>
-      <c r="IM1" s="10"/>
-      <c r="IN1" s="10"/>
-      <c r="IO1" s="10"/>
-      <c r="IP1" s="10"/>
-      <c r="IQ1" s="10"/>
-      <c r="IR1" s="10"/>
-      <c r="IS1" s="10"/>
-      <c r="IT1" s="10"/>
-      <c r="IU1" s="10"/>
-      <c r="IV1" s="10"/>
-      <c r="IW1" s="10"/>
-      <c r="IX1" s="12"/>
+      <c r="S1" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="8"/>
+      <c r="AA1" s="8"/>
+      <c r="AB1" s="8"/>
+      <c r="AC1" s="8"/>
+      <c r="AD1" s="8"/>
+      <c r="AE1" s="8"/>
+      <c r="AF1" s="8"/>
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="8"/>
+      <c r="AI1" s="8"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="8"/>
+      <c r="AL1" s="8"/>
+      <c r="AM1" s="8"/>
+      <c r="AN1" s="8"/>
+      <c r="AO1" s="8"/>
+      <c r="AP1" s="8"/>
+      <c r="AQ1" s="8"/>
+      <c r="AR1" s="8"/>
+      <c r="AS1" s="8"/>
+      <c r="AT1" s="8"/>
+      <c r="AU1" s="8"/>
+      <c r="AV1" s="8"/>
+      <c r="AW1" s="8"/>
+      <c r="AX1" s="8"/>
+      <c r="AY1" s="8"/>
+      <c r="AZ1" s="8"/>
+      <c r="BA1" s="8"/>
+      <c r="BB1" s="8"/>
+      <c r="BC1" s="8"/>
+      <c r="BD1" s="8"/>
+      <c r="BE1" s="8"/>
+      <c r="BF1" s="8"/>
+      <c r="BG1" s="8"/>
+      <c r="BH1" s="8"/>
+      <c r="BI1" s="8"/>
+      <c r="BJ1" s="8"/>
+      <c r="BK1" s="8"/>
+      <c r="BL1" s="8"/>
+      <c r="BM1" s="8"/>
+      <c r="BN1" s="8"/>
+      <c r="BO1" s="8"/>
+      <c r="BP1" s="8"/>
+      <c r="BQ1" s="8"/>
+      <c r="BR1" s="8"/>
+      <c r="BS1" s="8"/>
+      <c r="BT1" s="8"/>
+      <c r="BU1" s="8"/>
+      <c r="BV1" s="8"/>
+      <c r="BW1" s="8"/>
+      <c r="BX1" s="8"/>
+      <c r="BY1" s="8"/>
+      <c r="BZ1" s="8"/>
+      <c r="CA1" s="8"/>
+      <c r="CB1" s="8"/>
+      <c r="CC1" s="8"/>
+      <c r="CD1" s="8"/>
+      <c r="CE1" s="8"/>
+      <c r="CF1" s="8"/>
+      <c r="CG1" s="8"/>
+      <c r="CH1" s="8"/>
+      <c r="CI1" s="8"/>
+      <c r="CJ1" s="8"/>
+      <c r="CK1" s="8"/>
+      <c r="CL1" s="8"/>
+      <c r="CM1" s="8"/>
+      <c r="CN1" s="8"/>
+      <c r="CO1" s="8"/>
+      <c r="CP1" s="8"/>
+      <c r="CQ1" s="8"/>
+      <c r="CR1" s="8"/>
+      <c r="CS1" s="8"/>
+      <c r="CT1" s="8"/>
+      <c r="CU1" s="8"/>
+      <c r="CV1" s="8"/>
+      <c r="CW1" s="8"/>
+      <c r="CX1" s="8"/>
+      <c r="CY1" s="8"/>
+      <c r="CZ1" s="8"/>
+      <c r="DA1" s="8"/>
+      <c r="DB1" s="8"/>
+      <c r="DC1" s="8"/>
+      <c r="DD1" s="8"/>
+      <c r="DE1" s="8"/>
+      <c r="DF1" s="8"/>
+      <c r="DG1" s="8"/>
+      <c r="DH1" s="8"/>
+      <c r="DI1" s="8"/>
+      <c r="DJ1" s="8"/>
+      <c r="DK1" s="8"/>
+      <c r="DL1" s="8"/>
+      <c r="DM1" s="8"/>
+      <c r="DN1" s="8"/>
+      <c r="DO1" s="8"/>
+      <c r="DP1" s="8"/>
+      <c r="DQ1" s="8"/>
+      <c r="DR1" s="8"/>
+      <c r="DS1" s="8"/>
+      <c r="DT1" s="8"/>
+      <c r="DU1" s="8"/>
+      <c r="DV1" s="8"/>
+      <c r="DW1" s="8"/>
+      <c r="DX1" s="8"/>
+      <c r="DY1" s="8"/>
+      <c r="DZ1" s="8"/>
+      <c r="EA1" s="8"/>
+      <c r="EB1" s="8"/>
+      <c r="EC1" s="8"/>
+      <c r="ED1" s="8"/>
+      <c r="EE1" s="8"/>
+      <c r="EF1" s="8"/>
+      <c r="EG1" s="8"/>
+      <c r="EH1" s="8"/>
+      <c r="EI1" s="8"/>
+      <c r="EJ1" s="8"/>
+      <c r="EK1" s="8"/>
+      <c r="EL1" s="8"/>
+      <c r="EM1" s="8"/>
+      <c r="EN1" s="8"/>
+      <c r="EO1" s="8"/>
+      <c r="EP1" s="8"/>
+      <c r="EQ1" s="8"/>
+      <c r="ER1" s="8"/>
+      <c r="ES1" s="8"/>
+      <c r="ET1" s="8"/>
+      <c r="EU1" s="8"/>
+      <c r="EV1" s="8"/>
+      <c r="EW1" s="8"/>
+      <c r="EX1" s="8"/>
+      <c r="EY1" s="8"/>
+      <c r="EZ1" s="8"/>
+      <c r="FA1" s="8"/>
+      <c r="FB1" s="8"/>
+      <c r="FC1" s="8"/>
+      <c r="FD1" s="8"/>
+      <c r="FE1" s="8"/>
+      <c r="FF1" s="8"/>
+      <c r="FG1" s="8"/>
+      <c r="FH1" s="8"/>
+      <c r="FI1" s="8"/>
+      <c r="FJ1" s="8"/>
+      <c r="FK1" s="8"/>
+      <c r="FL1" s="8"/>
+      <c r="FM1" s="8"/>
+      <c r="FN1" s="8"/>
+      <c r="FO1" s="8"/>
+      <c r="FP1" s="8"/>
+      <c r="FQ1" s="8"/>
+      <c r="FR1" s="8"/>
+      <c r="FS1" s="8"/>
+      <c r="FT1" s="8"/>
+      <c r="FU1" s="8"/>
+      <c r="FV1" s="8"/>
+      <c r="FW1" s="8"/>
+      <c r="FX1" s="8"/>
+      <c r="FY1" s="8"/>
+      <c r="FZ1" s="8"/>
+      <c r="GA1" s="8"/>
+      <c r="GB1" s="8"/>
+      <c r="GC1" s="8"/>
+      <c r="GD1" s="8"/>
+      <c r="GE1" s="8"/>
+      <c r="GF1" s="8"/>
+      <c r="GG1" s="8"/>
+      <c r="GH1" s="8"/>
+      <c r="GI1" s="8"/>
+      <c r="GJ1" s="8"/>
+      <c r="GK1" s="8"/>
+      <c r="GL1" s="8"/>
+      <c r="GM1" s="8"/>
+      <c r="GN1" s="8"/>
+      <c r="GO1" s="8"/>
+      <c r="GP1" s="8"/>
+      <c r="GQ1" s="8"/>
+      <c r="GR1" s="8"/>
+      <c r="GS1" s="8"/>
+      <c r="GT1" s="8"/>
+      <c r="GU1" s="8"/>
+      <c r="GV1" s="8"/>
+      <c r="GW1" s="8"/>
+      <c r="GX1" s="8"/>
+      <c r="GY1" s="8"/>
+      <c r="GZ1" s="8"/>
+      <c r="HA1" s="8"/>
+      <c r="HB1" s="8"/>
+      <c r="HC1" s="8"/>
+      <c r="HD1" s="8"/>
+      <c r="HE1" s="8"/>
+      <c r="HF1" s="8"/>
+      <c r="HG1" s="8"/>
+      <c r="HH1" s="8"/>
+      <c r="HI1" s="8"/>
+      <c r="HJ1" s="8"/>
+      <c r="HK1" s="8"/>
+      <c r="HL1" s="8"/>
+      <c r="HM1" s="8"/>
+      <c r="HN1" s="8"/>
+      <c r="HO1" s="8"/>
+      <c r="HP1" s="8"/>
+      <c r="HQ1" s="8"/>
+      <c r="HR1" s="8"/>
+      <c r="HS1" s="8"/>
+      <c r="HT1" s="8"/>
+      <c r="HU1" s="8"/>
+      <c r="HV1" s="8"/>
+      <c r="HW1" s="8"/>
+      <c r="HX1" s="8"/>
+      <c r="HY1" s="8"/>
+      <c r="HZ1" s="8"/>
+      <c r="IA1" s="8"/>
+      <c r="IB1" s="8"/>
+      <c r="IC1" s="8"/>
+      <c r="ID1" s="8"/>
+      <c r="IE1" s="8"/>
+      <c r="IF1" s="8"/>
+      <c r="IG1" s="8"/>
+      <c r="IH1" s="8"/>
+      <c r="II1" s="8"/>
+      <c r="IJ1" s="8"/>
+      <c r="IK1" s="8"/>
+      <c r="IL1" s="8"/>
+      <c r="IM1" s="8"/>
+      <c r="IN1" s="8"/>
+      <c r="IO1" s="8"/>
+      <c r="IP1" s="8"/>
+      <c r="IQ1" s="8"/>
+      <c r="IR1" s="8"/>
+      <c r="IS1" s="8"/>
+      <c r="IT1" s="8"/>
+      <c r="IU1" s="8"/>
+      <c r="IV1" s="8"/>
+      <c r="IW1" s="8"/>
+      <c r="IX1" s="10"/>
     </row>
     <row r="2" spans="1:258" ht="34.5" customHeight="1">
       <c r="A2" s="6" t="s">
@@ -1961,258 +2023,260 @@
       <c r="L2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="11"/>
-      <c r="AE2" s="11"/>
-      <c r="AF2" s="11"/>
-      <c r="AG2" s="11"/>
-      <c r="AH2" s="11"/>
-      <c r="AI2" s="11"/>
-      <c r="AJ2" s="11"/>
-      <c r="AK2" s="11"/>
-      <c r="AL2" s="11"/>
-      <c r="AM2" s="11"/>
-      <c r="AN2" s="11"/>
-      <c r="AO2" s="11"/>
-      <c r="AP2" s="11"/>
-      <c r="AQ2" s="11"/>
-      <c r="AR2" s="11"/>
-      <c r="AS2" s="11"/>
-      <c r="AT2" s="11"/>
-      <c r="AU2" s="11"/>
-      <c r="AV2" s="11"/>
-      <c r="AW2" s="11"/>
-      <c r="AX2" s="11"/>
-      <c r="AY2" s="11"/>
-      <c r="AZ2" s="11"/>
-      <c r="BA2" s="11"/>
-      <c r="BB2" s="11"/>
-      <c r="BC2" s="11"/>
-      <c r="BD2" s="11"/>
-      <c r="BE2" s="11"/>
-      <c r="BF2" s="11"/>
-      <c r="BG2" s="11"/>
-      <c r="BH2" s="11"/>
-      <c r="BI2" s="11"/>
-      <c r="BJ2" s="11"/>
-      <c r="BK2" s="11"/>
-      <c r="BL2" s="11"/>
-      <c r="BM2" s="11"/>
-      <c r="BN2" s="11"/>
-      <c r="BO2" s="11"/>
-      <c r="BP2" s="11"/>
-      <c r="BQ2" s="11"/>
-      <c r="BR2" s="11"/>
-      <c r="BS2" s="11"/>
-      <c r="BT2" s="11"/>
-      <c r="BU2" s="11"/>
-      <c r="BV2" s="11"/>
-      <c r="BW2" s="11"/>
-      <c r="BX2" s="11"/>
-      <c r="BY2" s="11"/>
-      <c r="BZ2" s="11"/>
-      <c r="CA2" s="11"/>
-      <c r="CB2" s="11"/>
-      <c r="CC2" s="11"/>
-      <c r="CD2" s="11"/>
-      <c r="CE2" s="11"/>
-      <c r="CF2" s="11"/>
-      <c r="CG2" s="11"/>
-      <c r="CH2" s="11"/>
-      <c r="CI2" s="11"/>
-      <c r="CJ2" s="11"/>
-      <c r="CK2" s="11"/>
-      <c r="CL2" s="11"/>
-      <c r="CM2" s="11"/>
-      <c r="CN2" s="11"/>
-      <c r="CO2" s="11"/>
-      <c r="CP2" s="11"/>
-      <c r="CQ2" s="11"/>
-      <c r="CR2" s="11"/>
-      <c r="CS2" s="11"/>
-      <c r="CT2" s="11"/>
-      <c r="CU2" s="11"/>
-      <c r="CV2" s="11"/>
-      <c r="CW2" s="11"/>
-      <c r="CX2" s="11"/>
-      <c r="CY2" s="11"/>
-      <c r="CZ2" s="11"/>
-      <c r="DA2" s="11"/>
-      <c r="DB2" s="11"/>
-      <c r="DC2" s="11"/>
-      <c r="DD2" s="11"/>
-      <c r="DE2" s="11"/>
-      <c r="DF2" s="11"/>
-      <c r="DG2" s="11"/>
-      <c r="DH2" s="11"/>
-      <c r="DI2" s="11"/>
-      <c r="DJ2" s="11"/>
-      <c r="DK2" s="11"/>
-      <c r="DL2" s="11"/>
-      <c r="DM2" s="11"/>
-      <c r="DN2" s="11"/>
-      <c r="DO2" s="11"/>
-      <c r="DP2" s="11"/>
-      <c r="DQ2" s="11"/>
-      <c r="DR2" s="11"/>
-      <c r="DS2" s="11"/>
-      <c r="DT2" s="11"/>
-      <c r="DU2" s="11"/>
-      <c r="DV2" s="11"/>
-      <c r="DW2" s="11"/>
-      <c r="DX2" s="11"/>
-      <c r="DY2" s="11"/>
-      <c r="DZ2" s="11"/>
-      <c r="EA2" s="11"/>
-      <c r="EB2" s="11"/>
-      <c r="EC2" s="11"/>
-      <c r="ED2" s="11"/>
-      <c r="EE2" s="11"/>
-      <c r="EF2" s="11"/>
-      <c r="EG2" s="11"/>
-      <c r="EH2" s="11"/>
-      <c r="EI2" s="11"/>
-      <c r="EJ2" s="11"/>
-      <c r="EK2" s="11"/>
-      <c r="EL2" s="11"/>
-      <c r="EM2" s="11"/>
-      <c r="EN2" s="11"/>
-      <c r="EO2" s="11"/>
-      <c r="EP2" s="11"/>
-      <c r="EQ2" s="11"/>
-      <c r="ER2" s="11"/>
-      <c r="ES2" s="11"/>
-      <c r="ET2" s="11"/>
-      <c r="EU2" s="11"/>
-      <c r="EV2" s="11"/>
-      <c r="EW2" s="11"/>
-      <c r="EX2" s="11"/>
-      <c r="EY2" s="11"/>
-      <c r="EZ2" s="11"/>
-      <c r="FA2" s="11"/>
-      <c r="FB2" s="11"/>
-      <c r="FC2" s="11"/>
-      <c r="FD2" s="11"/>
-      <c r="FE2" s="11"/>
-      <c r="FF2" s="11"/>
-      <c r="FG2" s="11"/>
-      <c r="FH2" s="11"/>
-      <c r="FI2" s="11"/>
-      <c r="FJ2" s="11"/>
-      <c r="FK2" s="11"/>
-      <c r="FL2" s="11"/>
-      <c r="FM2" s="11"/>
-      <c r="FN2" s="11"/>
-      <c r="FO2" s="11"/>
-      <c r="FP2" s="11"/>
-      <c r="FQ2" s="11"/>
-      <c r="FR2" s="11"/>
-      <c r="FS2" s="11"/>
-      <c r="FT2" s="11"/>
-      <c r="FU2" s="11"/>
-      <c r="FV2" s="11"/>
-      <c r="FW2" s="11"/>
-      <c r="FX2" s="11"/>
-      <c r="FY2" s="11"/>
-      <c r="FZ2" s="11"/>
-      <c r="GA2" s="11"/>
-      <c r="GB2" s="11"/>
-      <c r="GC2" s="11"/>
-      <c r="GD2" s="11"/>
-      <c r="GE2" s="11"/>
-      <c r="GF2" s="11"/>
-      <c r="GG2" s="11"/>
-      <c r="GH2" s="11"/>
-      <c r="GI2" s="11"/>
-      <c r="GJ2" s="11"/>
-      <c r="GK2" s="11"/>
-      <c r="GL2" s="11"/>
-      <c r="GM2" s="11"/>
-      <c r="GN2" s="11"/>
-      <c r="GO2" s="11"/>
-      <c r="GP2" s="11"/>
-      <c r="GQ2" s="11"/>
-      <c r="GR2" s="11"/>
-      <c r="GS2" s="11"/>
-      <c r="GT2" s="11"/>
-      <c r="GU2" s="11"/>
-      <c r="GV2" s="11"/>
-      <c r="GW2" s="11"/>
-      <c r="GX2" s="11"/>
-      <c r="GY2" s="11"/>
-      <c r="GZ2" s="11"/>
-      <c r="HA2" s="11"/>
-      <c r="HB2" s="11"/>
-      <c r="HC2" s="11"/>
-      <c r="HD2" s="11"/>
-      <c r="HE2" s="11"/>
-      <c r="HF2" s="11"/>
-      <c r="HG2" s="11"/>
-      <c r="HH2" s="11"/>
-      <c r="HI2" s="11"/>
-      <c r="HJ2" s="11"/>
-      <c r="HK2" s="11"/>
-      <c r="HL2" s="11"/>
-      <c r="HM2" s="11"/>
-      <c r="HN2" s="11"/>
-      <c r="HO2" s="11"/>
-      <c r="HP2" s="11"/>
-      <c r="HQ2" s="11"/>
-      <c r="HR2" s="11"/>
-      <c r="HS2" s="11"/>
-      <c r="HT2" s="11"/>
-      <c r="HU2" s="11"/>
-      <c r="HV2" s="11"/>
-      <c r="HW2" s="11"/>
-      <c r="HX2" s="11"/>
-      <c r="HY2" s="11"/>
-      <c r="HZ2" s="11"/>
-      <c r="IA2" s="11"/>
-      <c r="IB2" s="11"/>
-      <c r="IC2" s="11"/>
-      <c r="ID2" s="11"/>
-      <c r="IE2" s="11"/>
-      <c r="IF2" s="11"/>
-      <c r="IG2" s="11"/>
-      <c r="IH2" s="11"/>
-      <c r="II2" s="11"/>
-      <c r="IJ2" s="11"/>
-      <c r="IK2" s="11"/>
-      <c r="IL2" s="11"/>
-      <c r="IM2" s="11"/>
-      <c r="IN2" s="11"/>
-      <c r="IO2" s="11"/>
-      <c r="IP2" s="11"/>
-      <c r="IQ2" s="11"/>
-      <c r="IR2" s="11"/>
-      <c r="IS2" s="11"/>
-      <c r="IT2" s="11"/>
-      <c r="IU2" s="11"/>
-      <c r="IV2" s="11"/>
-      <c r="IW2" s="11"/>
-      <c r="IX2" s="13"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
+      <c r="AE2" s="9"/>
+      <c r="AF2" s="9"/>
+      <c r="AG2" s="9"/>
+      <c r="AH2" s="9"/>
+      <c r="AI2" s="9"/>
+      <c r="AJ2" s="9"/>
+      <c r="AK2" s="9"/>
+      <c r="AL2" s="9"/>
+      <c r="AM2" s="9"/>
+      <c r="AN2" s="9"/>
+      <c r="AO2" s="9"/>
+      <c r="AP2" s="9"/>
+      <c r="AQ2" s="9"/>
+      <c r="AR2" s="9"/>
+      <c r="AS2" s="9"/>
+      <c r="AT2" s="9"/>
+      <c r="AU2" s="9"/>
+      <c r="AV2" s="9"/>
+      <c r="AW2" s="9"/>
+      <c r="AX2" s="9"/>
+      <c r="AY2" s="9"/>
+      <c r="AZ2" s="9"/>
+      <c r="BA2" s="9"/>
+      <c r="BB2" s="9"/>
+      <c r="BC2" s="9"/>
+      <c r="BD2" s="9"/>
+      <c r="BE2" s="9"/>
+      <c r="BF2" s="9"/>
+      <c r="BG2" s="9"/>
+      <c r="BH2" s="9"/>
+      <c r="BI2" s="9"/>
+      <c r="BJ2" s="9"/>
+      <c r="BK2" s="9"/>
+      <c r="BL2" s="9"/>
+      <c r="BM2" s="9"/>
+      <c r="BN2" s="9"/>
+      <c r="BO2" s="9"/>
+      <c r="BP2" s="9"/>
+      <c r="BQ2" s="9"/>
+      <c r="BR2" s="9"/>
+      <c r="BS2" s="9"/>
+      <c r="BT2" s="9"/>
+      <c r="BU2" s="9"/>
+      <c r="BV2" s="9"/>
+      <c r="BW2" s="9"/>
+      <c r="BX2" s="9"/>
+      <c r="BY2" s="9"/>
+      <c r="BZ2" s="9"/>
+      <c r="CA2" s="9"/>
+      <c r="CB2" s="9"/>
+      <c r="CC2" s="9"/>
+      <c r="CD2" s="9"/>
+      <c r="CE2" s="9"/>
+      <c r="CF2" s="9"/>
+      <c r="CG2" s="9"/>
+      <c r="CH2" s="9"/>
+      <c r="CI2" s="9"/>
+      <c r="CJ2" s="9"/>
+      <c r="CK2" s="9"/>
+      <c r="CL2" s="9"/>
+      <c r="CM2" s="9"/>
+      <c r="CN2" s="9"/>
+      <c r="CO2" s="9"/>
+      <c r="CP2" s="9"/>
+      <c r="CQ2" s="9"/>
+      <c r="CR2" s="9"/>
+      <c r="CS2" s="9"/>
+      <c r="CT2" s="9"/>
+      <c r="CU2" s="9"/>
+      <c r="CV2" s="9"/>
+      <c r="CW2" s="9"/>
+      <c r="CX2" s="9"/>
+      <c r="CY2" s="9"/>
+      <c r="CZ2" s="9"/>
+      <c r="DA2" s="9"/>
+      <c r="DB2" s="9"/>
+      <c r="DC2" s="9"/>
+      <c r="DD2" s="9"/>
+      <c r="DE2" s="9"/>
+      <c r="DF2" s="9"/>
+      <c r="DG2" s="9"/>
+      <c r="DH2" s="9"/>
+      <c r="DI2" s="9"/>
+      <c r="DJ2" s="9"/>
+      <c r="DK2" s="9"/>
+      <c r="DL2" s="9"/>
+      <c r="DM2" s="9"/>
+      <c r="DN2" s="9"/>
+      <c r="DO2" s="9"/>
+      <c r="DP2" s="9"/>
+      <c r="DQ2" s="9"/>
+      <c r="DR2" s="9"/>
+      <c r="DS2" s="9"/>
+      <c r="DT2" s="9"/>
+      <c r="DU2" s="9"/>
+      <c r="DV2" s="9"/>
+      <c r="DW2" s="9"/>
+      <c r="DX2" s="9"/>
+      <c r="DY2" s="9"/>
+      <c r="DZ2" s="9"/>
+      <c r="EA2" s="9"/>
+      <c r="EB2" s="9"/>
+      <c r="EC2" s="9"/>
+      <c r="ED2" s="9"/>
+      <c r="EE2" s="9"/>
+      <c r="EF2" s="9"/>
+      <c r="EG2" s="9"/>
+      <c r="EH2" s="9"/>
+      <c r="EI2" s="9"/>
+      <c r="EJ2" s="9"/>
+      <c r="EK2" s="9"/>
+      <c r="EL2" s="9"/>
+      <c r="EM2" s="9"/>
+      <c r="EN2" s="9"/>
+      <c r="EO2" s="9"/>
+      <c r="EP2" s="9"/>
+      <c r="EQ2" s="9"/>
+      <c r="ER2" s="9"/>
+      <c r="ES2" s="9"/>
+      <c r="ET2" s="9"/>
+      <c r="EU2" s="9"/>
+      <c r="EV2" s="9"/>
+      <c r="EW2" s="9"/>
+      <c r="EX2" s="9"/>
+      <c r="EY2" s="9"/>
+      <c r="EZ2" s="9"/>
+      <c r="FA2" s="9"/>
+      <c r="FB2" s="9"/>
+      <c r="FC2" s="9"/>
+      <c r="FD2" s="9"/>
+      <c r="FE2" s="9"/>
+      <c r="FF2" s="9"/>
+      <c r="FG2" s="9"/>
+      <c r="FH2" s="9"/>
+      <c r="FI2" s="9"/>
+      <c r="FJ2" s="9"/>
+      <c r="FK2" s="9"/>
+      <c r="FL2" s="9"/>
+      <c r="FM2" s="9"/>
+      <c r="FN2" s="9"/>
+      <c r="FO2" s="9"/>
+      <c r="FP2" s="9"/>
+      <c r="FQ2" s="9"/>
+      <c r="FR2" s="9"/>
+      <c r="FS2" s="9"/>
+      <c r="FT2" s="9"/>
+      <c r="FU2" s="9"/>
+      <c r="FV2" s="9"/>
+      <c r="FW2" s="9"/>
+      <c r="FX2" s="9"/>
+      <c r="FY2" s="9"/>
+      <c r="FZ2" s="9"/>
+      <c r="GA2" s="9"/>
+      <c r="GB2" s="9"/>
+      <c r="GC2" s="9"/>
+      <c r="GD2" s="9"/>
+      <c r="GE2" s="9"/>
+      <c r="GF2" s="9"/>
+      <c r="GG2" s="9"/>
+      <c r="GH2" s="9"/>
+      <c r="GI2" s="9"/>
+      <c r="GJ2" s="9"/>
+      <c r="GK2" s="9"/>
+      <c r="GL2" s="9"/>
+      <c r="GM2" s="9"/>
+      <c r="GN2" s="9"/>
+      <c r="GO2" s="9"/>
+      <c r="GP2" s="9"/>
+      <c r="GQ2" s="9"/>
+      <c r="GR2" s="9"/>
+      <c r="GS2" s="9"/>
+      <c r="GT2" s="9"/>
+      <c r="GU2" s="9"/>
+      <c r="GV2" s="9"/>
+      <c r="GW2" s="9"/>
+      <c r="GX2" s="9"/>
+      <c r="GY2" s="9"/>
+      <c r="GZ2" s="9"/>
+      <c r="HA2" s="9"/>
+      <c r="HB2" s="9"/>
+      <c r="HC2" s="9"/>
+      <c r="HD2" s="9"/>
+      <c r="HE2" s="9"/>
+      <c r="HF2" s="9"/>
+      <c r="HG2" s="9"/>
+      <c r="HH2" s="9"/>
+      <c r="HI2" s="9"/>
+      <c r="HJ2" s="9"/>
+      <c r="HK2" s="9"/>
+      <c r="HL2" s="9"/>
+      <c r="HM2" s="9"/>
+      <c r="HN2" s="9"/>
+      <c r="HO2" s="9"/>
+      <c r="HP2" s="9"/>
+      <c r="HQ2" s="9"/>
+      <c r="HR2" s="9"/>
+      <c r="HS2" s="9"/>
+      <c r="HT2" s="9"/>
+      <c r="HU2" s="9"/>
+      <c r="HV2" s="9"/>
+      <c r="HW2" s="9"/>
+      <c r="HX2" s="9"/>
+      <c r="HY2" s="9"/>
+      <c r="HZ2" s="9"/>
+      <c r="IA2" s="9"/>
+      <c r="IB2" s="9"/>
+      <c r="IC2" s="9"/>
+      <c r="ID2" s="9"/>
+      <c r="IE2" s="9"/>
+      <c r="IF2" s="9"/>
+      <c r="IG2" s="9"/>
+      <c r="IH2" s="9"/>
+      <c r="II2" s="9"/>
+      <c r="IJ2" s="9"/>
+      <c r="IK2" s="9"/>
+      <c r="IL2" s="9"/>
+      <c r="IM2" s="9"/>
+      <c r="IN2" s="9"/>
+      <c r="IO2" s="9"/>
+      <c r="IP2" s="9"/>
+      <c r="IQ2" s="9"/>
+      <c r="IR2" s="9"/>
+      <c r="IS2" s="9"/>
+      <c r="IT2" s="9"/>
+      <c r="IU2" s="9"/>
+      <c r="IV2" s="9"/>
+      <c r="IW2" s="9"/>
+      <c r="IX2" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2233,12 +2297,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="13.8" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="13.8" customHeight="1">
-      <c r="A2" s="15"/>
+      <c r="A2" s="13"/>
     </row>
     <row r="3" spans="1:1" ht="16.05" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -2284,12 +2348,12 @@
       <c r="A11" s="3"/>
     </row>
     <row r="12" spans="1:1" ht="13.8" customHeight="1">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="14" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="12" customHeight="1">
-      <c r="A13" s="17"/>
+      <c r="A13" s="15"/>
     </row>
     <row r="14" spans="1:1" ht="16.05" customHeight="1">
       <c r="A14" s="4" t="s">

--- a/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/UserAccountImport_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\zp\code\web\hc-apm-web-ib\src\src\main\webapp\portal\uaa\userAccount\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212670825\Desktop\APM\Git\hc-apm-web\src\src\main\webapp\portal\uaa\userAccount\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA916DC9-9AB8-47D8-B24D-0BE529742578}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCA2815-638A-4FB5-A2DC-30710618B7B9}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
   <si>
     <t>所属集团</t>
   </si>
@@ -294,18 +294,12 @@
   <si>
     <t>标签</t>
   </si>
-  <si>
-    <t>所属代理商</t>
-  </si>
-  <si>
-    <t>XXXX</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -323,12 +317,6 @@
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="GE Inspira Sans"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -351,7 +339,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -464,52 +452,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -521,9 +468,11 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -539,15 +488,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1686,8 +1626,8 @@
     <col min="11" max="12" width="8.77734375" style="1" customWidth="1"/>
     <col min="13" max="13" width="24.6640625" style="1" customWidth="1"/>
     <col min="14" max="17" width="30" style="1" customWidth="1"/>
-    <col min="18" max="19" width="32.6640625" style="1" customWidth="1"/>
-    <col min="20" max="258" width="8.77734375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="32.6640625" style="1" customWidth="1"/>
+    <col min="19" max="258" width="8.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:258" ht="30.75" customHeight="1">
@@ -1745,248 +1685,246 @@
       <c r="R1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="8"/>
-      <c r="AA1" s="8"/>
-      <c r="AB1" s="8"/>
-      <c r="AC1" s="8"/>
-      <c r="AD1" s="8"/>
-      <c r="AE1" s="8"/>
-      <c r="AF1" s="8"/>
-      <c r="AG1" s="8"/>
-      <c r="AH1" s="8"/>
-      <c r="AI1" s="8"/>
-      <c r="AJ1" s="8"/>
-      <c r="AK1" s="8"/>
-      <c r="AL1" s="8"/>
-      <c r="AM1" s="8"/>
-      <c r="AN1" s="8"/>
-      <c r="AO1" s="8"/>
-      <c r="AP1" s="8"/>
-      <c r="AQ1" s="8"/>
-      <c r="AR1" s="8"/>
-      <c r="AS1" s="8"/>
-      <c r="AT1" s="8"/>
-      <c r="AU1" s="8"/>
-      <c r="AV1" s="8"/>
-      <c r="AW1" s="8"/>
-      <c r="AX1" s="8"/>
-      <c r="AY1" s="8"/>
-      <c r="AZ1" s="8"/>
-      <c r="BA1" s="8"/>
-      <c r="BB1" s="8"/>
-      <c r="BC1" s="8"/>
-      <c r="BD1" s="8"/>
-      <c r="BE1" s="8"/>
-      <c r="BF1" s="8"/>
-      <c r="BG1" s="8"/>
-      <c r="BH1" s="8"/>
-      <c r="BI1" s="8"/>
-      <c r="BJ1" s="8"/>
-      <c r="BK1" s="8"/>
-      <c r="BL1" s="8"/>
-      <c r="BM1" s="8"/>
-      <c r="BN1" s="8"/>
-      <c r="BO1" s="8"/>
-      <c r="BP1" s="8"/>
-      <c r="BQ1" s="8"/>
-      <c r="BR1" s="8"/>
-      <c r="BS1" s="8"/>
-      <c r="BT1" s="8"/>
-      <c r="BU1" s="8"/>
-      <c r="BV1" s="8"/>
-      <c r="BW1" s="8"/>
-      <c r="BX1" s="8"/>
-      <c r="BY1" s="8"/>
-      <c r="BZ1" s="8"/>
-      <c r="CA1" s="8"/>
-      <c r="CB1" s="8"/>
-      <c r="CC1" s="8"/>
-      <c r="CD1" s="8"/>
-      <c r="CE1" s="8"/>
-      <c r="CF1" s="8"/>
-      <c r="CG1" s="8"/>
-      <c r="CH1" s="8"/>
-      <c r="CI1" s="8"/>
-      <c r="CJ1" s="8"/>
-      <c r="CK1" s="8"/>
-      <c r="CL1" s="8"/>
-      <c r="CM1" s="8"/>
-      <c r="CN1" s="8"/>
-      <c r="CO1" s="8"/>
-      <c r="CP1" s="8"/>
-      <c r="CQ1" s="8"/>
-      <c r="CR1" s="8"/>
-      <c r="CS1" s="8"/>
-      <c r="CT1" s="8"/>
-      <c r="CU1" s="8"/>
-      <c r="CV1" s="8"/>
-      <c r="CW1" s="8"/>
-      <c r="CX1" s="8"/>
-      <c r="CY1" s="8"/>
-      <c r="CZ1" s="8"/>
-      <c r="DA1" s="8"/>
-      <c r="DB1" s="8"/>
-      <c r="DC1" s="8"/>
-      <c r="DD1" s="8"/>
-      <c r="DE1" s="8"/>
-      <c r="DF1" s="8"/>
-      <c r="DG1" s="8"/>
-      <c r="DH1" s="8"/>
-      <c r="DI1" s="8"/>
-      <c r="DJ1" s="8"/>
-      <c r="DK1" s="8"/>
-      <c r="DL1" s="8"/>
-      <c r="DM1" s="8"/>
-      <c r="DN1" s="8"/>
-      <c r="DO1" s="8"/>
-      <c r="DP1" s="8"/>
-      <c r="DQ1" s="8"/>
-      <c r="DR1" s="8"/>
-      <c r="DS1" s="8"/>
-      <c r="DT1" s="8"/>
-      <c r="DU1" s="8"/>
-      <c r="DV1" s="8"/>
-      <c r="DW1" s="8"/>
-      <c r="DX1" s="8"/>
-      <c r="DY1" s="8"/>
-      <c r="DZ1" s="8"/>
-      <c r="EA1" s="8"/>
-      <c r="EB1" s="8"/>
-      <c r="EC1" s="8"/>
-      <c r="ED1" s="8"/>
-      <c r="EE1" s="8"/>
-      <c r="EF1" s="8"/>
-      <c r="EG1" s="8"/>
-      <c r="EH1" s="8"/>
-      <c r="EI1" s="8"/>
-      <c r="EJ1" s="8"/>
-      <c r="EK1" s="8"/>
-      <c r="EL1" s="8"/>
-      <c r="EM1" s="8"/>
-      <c r="EN1" s="8"/>
-      <c r="EO1" s="8"/>
-      <c r="EP1" s="8"/>
-      <c r="EQ1" s="8"/>
-      <c r="ER1" s="8"/>
-      <c r="ES1" s="8"/>
-      <c r="ET1" s="8"/>
-      <c r="EU1" s="8"/>
-      <c r="EV1" s="8"/>
-      <c r="EW1" s="8"/>
-      <c r="EX1" s="8"/>
-      <c r="EY1" s="8"/>
-      <c r="EZ1" s="8"/>
-      <c r="FA1" s="8"/>
-      <c r="FB1" s="8"/>
-      <c r="FC1" s="8"/>
-      <c r="FD1" s="8"/>
-      <c r="FE1" s="8"/>
-      <c r="FF1" s="8"/>
-      <c r="FG1" s="8"/>
-      <c r="FH1" s="8"/>
-      <c r="FI1" s="8"/>
-      <c r="FJ1" s="8"/>
-      <c r="FK1" s="8"/>
-      <c r="FL1" s="8"/>
-      <c r="FM1" s="8"/>
-      <c r="FN1" s="8"/>
-      <c r="FO1" s="8"/>
-      <c r="FP1" s="8"/>
-      <c r="FQ1" s="8"/>
-      <c r="FR1" s="8"/>
-      <c r="FS1" s="8"/>
-      <c r="FT1" s="8"/>
-      <c r="FU1" s="8"/>
-      <c r="FV1" s="8"/>
-      <c r="FW1" s="8"/>
-      <c r="FX1" s="8"/>
-      <c r="FY1" s="8"/>
-      <c r="FZ1" s="8"/>
-      <c r="GA1" s="8"/>
-      <c r="GB1" s="8"/>
-      <c r="GC1" s="8"/>
-      <c r="GD1" s="8"/>
-      <c r="GE1" s="8"/>
-      <c r="GF1" s="8"/>
-      <c r="GG1" s="8"/>
-      <c r="GH1" s="8"/>
-      <c r="GI1" s="8"/>
-      <c r="GJ1" s="8"/>
-      <c r="GK1" s="8"/>
-      <c r="GL1" s="8"/>
-      <c r="GM1" s="8"/>
-      <c r="GN1" s="8"/>
-      <c r="GO1" s="8"/>
-      <c r="GP1" s="8"/>
-      <c r="GQ1" s="8"/>
-      <c r="GR1" s="8"/>
-      <c r="GS1" s="8"/>
-      <c r="GT1" s="8"/>
-      <c r="GU1" s="8"/>
-      <c r="GV1" s="8"/>
-      <c r="GW1" s="8"/>
-      <c r="GX1" s="8"/>
-      <c r="GY1" s="8"/>
-      <c r="GZ1" s="8"/>
-      <c r="HA1" s="8"/>
-      <c r="HB1" s="8"/>
-      <c r="HC1" s="8"/>
-      <c r="HD1" s="8"/>
-      <c r="HE1" s="8"/>
-      <c r="HF1" s="8"/>
-      <c r="HG1" s="8"/>
-      <c r="HH1" s="8"/>
-      <c r="HI1" s="8"/>
-      <c r="HJ1" s="8"/>
-      <c r="HK1" s="8"/>
-      <c r="HL1" s="8"/>
-      <c r="HM1" s="8"/>
-      <c r="HN1" s="8"/>
-      <c r="HO1" s="8"/>
-      <c r="HP1" s="8"/>
-      <c r="HQ1" s="8"/>
-      <c r="HR1" s="8"/>
-      <c r="HS1" s="8"/>
-      <c r="HT1" s="8"/>
-      <c r="HU1" s="8"/>
-      <c r="HV1" s="8"/>
-      <c r="HW1" s="8"/>
-      <c r="HX1" s="8"/>
-      <c r="HY1" s="8"/>
-      <c r="HZ1" s="8"/>
-      <c r="IA1" s="8"/>
-      <c r="IB1" s="8"/>
-      <c r="IC1" s="8"/>
-      <c r="ID1" s="8"/>
-      <c r="IE1" s="8"/>
-      <c r="IF1" s="8"/>
-      <c r="IG1" s="8"/>
-      <c r="IH1" s="8"/>
-      <c r="II1" s="8"/>
-      <c r="IJ1" s="8"/>
-      <c r="IK1" s="8"/>
-      <c r="IL1" s="8"/>
-      <c r="IM1" s="8"/>
-      <c r="IN1" s="8"/>
-      <c r="IO1" s="8"/>
-      <c r="IP1" s="8"/>
-      <c r="IQ1" s="8"/>
-      <c r="IR1" s="8"/>
-      <c r="IS1" s="8"/>
-      <c r="IT1" s="8"/>
-      <c r="IU1" s="8"/>
-      <c r="IV1" s="8"/>
-      <c r="IW1" s="8"/>
-      <c r="IX1" s="10"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="10"/>
+      <c r="AD1" s="10"/>
+      <c r="AE1" s="10"/>
+      <c r="AF1" s="10"/>
+      <c r="AG1" s="10"/>
+      <c r="AH1" s="10"/>
+      <c r="AI1" s="10"/>
+      <c r="AJ1" s="10"/>
+      <c r="AK1" s="10"/>
+      <c r="AL1" s="10"/>
+      <c r="AM1" s="10"/>
+      <c r="AN1" s="10"/>
+      <c r="AO1" s="10"/>
+      <c r="AP1" s="10"/>
+      <c r="AQ1" s="10"/>
+      <c r="AR1" s="10"/>
+      <c r="AS1" s="10"/>
+      <c r="AT1" s="10"/>
+      <c r="AU1" s="10"/>
+      <c r="AV1" s="10"/>
+      <c r="AW1" s="10"/>
+      <c r="AX1" s="10"/>
+      <c r="AY1" s="10"/>
+      <c r="AZ1" s="10"/>
+      <c r="BA1" s="10"/>
+      <c r="BB1" s="10"/>
+      <c r="BC1" s="10"/>
+      <c r="BD1" s="10"/>
+      <c r="BE1" s="10"/>
+      <c r="BF1" s="10"/>
+      <c r="BG1" s="10"/>
+      <c r="BH1" s="10"/>
+      <c r="BI1" s="10"/>
+      <c r="BJ1" s="10"/>
+      <c r="BK1" s="10"/>
+      <c r="BL1" s="10"/>
+      <c r="BM1" s="10"/>
+      <c r="BN1" s="10"/>
+      <c r="BO1" s="10"/>
+      <c r="BP1" s="10"/>
+      <c r="BQ1" s="10"/>
+      <c r="BR1" s="10"/>
+      <c r="BS1" s="10"/>
+      <c r="BT1" s="10"/>
+      <c r="BU1" s="10"/>
+      <c r="BV1" s="10"/>
+      <c r="BW1" s="10"/>
+      <c r="BX1" s="10"/>
+      <c r="BY1" s="10"/>
+      <c r="BZ1" s="10"/>
+      <c r="CA1" s="10"/>
+      <c r="CB1" s="10"/>
+      <c r="CC1" s="10"/>
+      <c r="CD1" s="10"/>
+      <c r="CE1" s="10"/>
+      <c r="CF1" s="10"/>
+      <c r="CG1" s="10"/>
+      <c r="CH1" s="10"/>
+      <c r="CI1" s="10"/>
+      <c r="CJ1" s="10"/>
+      <c r="CK1" s="10"/>
+      <c r="CL1" s="10"/>
+      <c r="CM1" s="10"/>
+      <c r="CN1" s="10"/>
+      <c r="CO1" s="10"/>
+      <c r="CP1" s="10"/>
+      <c r="CQ1" s="10"/>
+      <c r="CR1" s="10"/>
+      <c r="CS1" s="10"/>
+      <c r="CT1" s="10"/>
+      <c r="CU1" s="10"/>
+      <c r="CV1" s="10"/>
+      <c r="CW1" s="10"/>
+      <c r="CX1" s="10"/>
+      <c r="CY1" s="10"/>
+      <c r="CZ1" s="10"/>
+      <c r="DA1" s="10"/>
+      <c r="DB1" s="10"/>
+      <c r="DC1" s="10"/>
+      <c r="DD1" s="10"/>
+      <c r="DE1" s="10"/>
+      <c r="DF1" s="10"/>
+      <c r="DG1" s="10"/>
+      <c r="DH1" s="10"/>
+      <c r="DI1" s="10"/>
+      <c r="DJ1" s="10"/>
+      <c r="DK1" s="10"/>
+      <c r="DL1" s="10"/>
+      <c r="DM1" s="10"/>
+      <c r="DN1" s="10"/>
+      <c r="DO1" s="10"/>
+      <c r="DP1" s="10"/>
+      <c r="DQ1" s="10"/>
+      <c r="DR1" s="10"/>
+      <c r="DS1" s="10"/>
+      <c r="DT1" s="10"/>
+      <c r="DU1" s="10"/>
+      <c r="DV1" s="10"/>
+      <c r="DW1" s="10"/>
+      <c r="DX1" s="10"/>
+      <c r="DY1" s="10"/>
+      <c r="DZ1" s="10"/>
+      <c r="EA1" s="10"/>
+      <c r="EB1" s="10"/>
+      <c r="EC1" s="10"/>
+      <c r="ED1" s="10"/>
+      <c r="EE1" s="10"/>
+      <c r="EF1" s="10"/>
+      <c r="EG1" s="10"/>
+      <c r="EH1" s="10"/>
+      <c r="EI1" s="10"/>
+      <c r="EJ1" s="10"/>
+      <c r="EK1" s="10"/>
+      <c r="EL1" s="10"/>
+      <c r="EM1" s="10"/>
+      <c r="EN1" s="10"/>
+      <c r="EO1" s="10"/>
+      <c r="EP1" s="10"/>
+      <c r="EQ1" s="10"/>
+      <c r="ER1" s="10"/>
+      <c r="ES1" s="10"/>
+      <c r="ET1" s="10"/>
+      <c r="EU1" s="10"/>
+      <c r="EV1" s="10"/>
+      <c r="EW1" s="10"/>
+      <c r="EX1" s="10"/>
+      <c r="EY1" s="10"/>
+      <c r="EZ1" s="10"/>
+      <c r="FA1" s="10"/>
+      <c r="FB1" s="10"/>
+      <c r="FC1" s="10"/>
+      <c r="FD1" s="10"/>
+      <c r="FE1" s="10"/>
+      <c r="FF1" s="10"/>
+      <c r="FG1" s="10"/>
+      <c r="FH1" s="10"/>
+      <c r="FI1" s="10"/>
+      <c r="FJ1" s="10"/>
+      <c r="FK1" s="10"/>
+      <c r="FL1" s="10"/>
+      <c r="FM1" s="10"/>
+      <c r="FN1" s="10"/>
+      <c r="FO1" s="10"/>
+      <c r="FP1" s="10"/>
+      <c r="FQ1" s="10"/>
+      <c r="FR1" s="10"/>
+      <c r="FS1" s="10"/>
+      <c r="FT1" s="10"/>
+      <c r="FU1" s="10"/>
+      <c r="FV1" s="10"/>
+      <c r="FW1" s="10"/>
+      <c r="FX1" s="10"/>
+      <c r="FY1" s="10"/>
+      <c r="FZ1" s="10"/>
+      <c r="GA1" s="10"/>
+      <c r="GB1" s="10"/>
+      <c r="GC1" s="10"/>
+      <c r="GD1" s="10"/>
+      <c r="GE1" s="10"/>
+      <c r="GF1" s="10"/>
+      <c r="GG1" s="10"/>
+      <c r="GH1" s="10"/>
+      <c r="GI1" s="10"/>
+      <c r="GJ1" s="10"/>
+      <c r="GK1" s="10"/>
+      <c r="GL1" s="10"/>
+      <c r="GM1" s="10"/>
+      <c r="GN1" s="10"/>
+      <c r="GO1" s="10"/>
+      <c r="GP1" s="10"/>
+      <c r="GQ1" s="10"/>
+      <c r="GR1" s="10"/>
+      <c r="GS1" s="10"/>
+      <c r="GT1" s="10"/>
+      <c r="GU1" s="10"/>
+      <c r="GV1" s="10"/>
+      <c r="GW1" s="10"/>
+      <c r="GX1" s="10"/>
+      <c r="GY1" s="10"/>
+      <c r="GZ1" s="10"/>
+      <c r="HA1" s="10"/>
+      <c r="HB1" s="10"/>
+      <c r="HC1" s="10"/>
+      <c r="HD1" s="10"/>
+      <c r="HE1" s="10"/>
+      <c r="HF1" s="10"/>
+      <c r="HG1" s="10"/>
+      <c r="HH1" s="10"/>
+      <c r="HI1" s="10"/>
+      <c r="HJ1" s="10"/>
+      <c r="HK1" s="10"/>
+      <c r="HL1" s="10"/>
+      <c r="HM1" s="10"/>
+      <c r="HN1" s="10"/>
+      <c r="HO1" s="10"/>
+      <c r="HP1" s="10"/>
+      <c r="HQ1" s="10"/>
+      <c r="HR1" s="10"/>
+      <c r="HS1" s="10"/>
+      <c r="HT1" s="10"/>
+      <c r="HU1" s="10"/>
+      <c r="HV1" s="10"/>
+      <c r="HW1" s="10"/>
+      <c r="HX1" s="10"/>
+      <c r="HY1" s="10"/>
+      <c r="HZ1" s="10"/>
+      <c r="IA1" s="10"/>
+      <c r="IB1" s="10"/>
+      <c r="IC1" s="10"/>
+      <c r="ID1" s="10"/>
+      <c r="IE1" s="10"/>
+      <c r="IF1" s="10"/>
+      <c r="IG1" s="10"/>
+      <c r="IH1" s="10"/>
+      <c r="II1" s="10"/>
+      <c r="IJ1" s="10"/>
+      <c r="IK1" s="10"/>
+      <c r="IL1" s="10"/>
+      <c r="IM1" s="10"/>
+      <c r="IN1" s="10"/>
+      <c r="IO1" s="10"/>
+      <c r="IP1" s="10"/>
+      <c r="IQ1" s="10"/>
+      <c r="IR1" s="10"/>
+      <c r="IS1" s="10"/>
+      <c r="IT1" s="10"/>
+      <c r="IU1" s="10"/>
+      <c r="IV1" s="10"/>
+      <c r="IW1" s="10"/>
+      <c r="IX1" s="12"/>
     </row>
     <row r="2" spans="1:258" ht="34.5" customHeight="1">
       <c r="A2" s="6" t="s">
@@ -2023,260 +1961,258 @@
       <c r="L2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
-      <c r="AE2" s="9"/>
-      <c r="AF2" s="9"/>
-      <c r="AG2" s="9"/>
-      <c r="AH2" s="9"/>
-      <c r="AI2" s="9"/>
-      <c r="AJ2" s="9"/>
-      <c r="AK2" s="9"/>
-      <c r="AL2" s="9"/>
-      <c r="AM2" s="9"/>
-      <c r="AN2" s="9"/>
-      <c r="AO2" s="9"/>
-      <c r="AP2" s="9"/>
-      <c r="AQ2" s="9"/>
-      <c r="AR2" s="9"/>
-      <c r="AS2" s="9"/>
-      <c r="AT2" s="9"/>
-      <c r="AU2" s="9"/>
-      <c r="AV2" s="9"/>
-      <c r="AW2" s="9"/>
-      <c r="AX2" s="9"/>
-      <c r="AY2" s="9"/>
-      <c r="AZ2" s="9"/>
-      <c r="BA2" s="9"/>
-      <c r="BB2" s="9"/>
-      <c r="BC2" s="9"/>
-      <c r="BD2" s="9"/>
-      <c r="BE2" s="9"/>
-      <c r="BF2" s="9"/>
-      <c r="BG2" s="9"/>
-      <c r="BH2" s="9"/>
-      <c r="BI2" s="9"/>
-      <c r="BJ2" s="9"/>
-      <c r="BK2" s="9"/>
-      <c r="BL2" s="9"/>
-      <c r="BM2" s="9"/>
-      <c r="BN2" s="9"/>
-      <c r="BO2" s="9"/>
-      <c r="BP2" s="9"/>
-      <c r="BQ2" s="9"/>
-      <c r="BR2" s="9"/>
-      <c r="BS2" s="9"/>
-      <c r="BT2" s="9"/>
-      <c r="BU2" s="9"/>
-      <c r="BV2" s="9"/>
-      <c r="BW2" s="9"/>
-      <c r="BX2" s="9"/>
-      <c r="BY2" s="9"/>
-      <c r="BZ2" s="9"/>
-      <c r="CA2" s="9"/>
-      <c r="CB2" s="9"/>
-      <c r="CC2" s="9"/>
-      <c r="CD2" s="9"/>
-      <c r="CE2" s="9"/>
-      <c r="CF2" s="9"/>
-      <c r="CG2" s="9"/>
-      <c r="CH2" s="9"/>
-      <c r="CI2" s="9"/>
-      <c r="CJ2" s="9"/>
-      <c r="CK2" s="9"/>
-      <c r="CL2" s="9"/>
-      <c r="CM2" s="9"/>
-      <c r="CN2" s="9"/>
-      <c r="CO2" s="9"/>
-      <c r="CP2" s="9"/>
-      <c r="CQ2" s="9"/>
-      <c r="CR2" s="9"/>
-      <c r="CS2" s="9"/>
-      <c r="CT2" s="9"/>
-      <c r="CU2" s="9"/>
-      <c r="CV2" s="9"/>
-      <c r="CW2" s="9"/>
-      <c r="CX2" s="9"/>
-      <c r="CY2" s="9"/>
-      <c r="CZ2" s="9"/>
-      <c r="DA2" s="9"/>
-      <c r="DB2" s="9"/>
-      <c r="DC2" s="9"/>
-      <c r="DD2" s="9"/>
-      <c r="DE2" s="9"/>
-      <c r="DF2" s="9"/>
-      <c r="DG2" s="9"/>
-      <c r="DH2" s="9"/>
-      <c r="DI2" s="9"/>
-      <c r="DJ2" s="9"/>
-      <c r="DK2" s="9"/>
-      <c r="DL2" s="9"/>
-      <c r="DM2" s="9"/>
-      <c r="DN2" s="9"/>
-      <c r="DO2" s="9"/>
-      <c r="DP2" s="9"/>
-      <c r="DQ2" s="9"/>
-      <c r="DR2" s="9"/>
-      <c r="DS2" s="9"/>
-      <c r="DT2" s="9"/>
-      <c r="DU2" s="9"/>
-      <c r="DV2" s="9"/>
-      <c r="DW2" s="9"/>
-      <c r="DX2" s="9"/>
-      <c r="DY2" s="9"/>
-      <c r="DZ2" s="9"/>
-      <c r="EA2" s="9"/>
-      <c r="EB2" s="9"/>
-      <c r="EC2" s="9"/>
-      <c r="ED2" s="9"/>
-      <c r="EE2" s="9"/>
-      <c r="EF2" s="9"/>
-      <c r="EG2" s="9"/>
-      <c r="EH2" s="9"/>
-      <c r="EI2" s="9"/>
-      <c r="EJ2" s="9"/>
-      <c r="EK2" s="9"/>
-      <c r="EL2" s="9"/>
-      <c r="EM2" s="9"/>
-      <c r="EN2" s="9"/>
-      <c r="EO2" s="9"/>
-      <c r="EP2" s="9"/>
-      <c r="EQ2" s="9"/>
-      <c r="ER2" s="9"/>
-      <c r="ES2" s="9"/>
-      <c r="ET2" s="9"/>
-      <c r="EU2" s="9"/>
-      <c r="EV2" s="9"/>
-      <c r="EW2" s="9"/>
-      <c r="EX2" s="9"/>
-      <c r="EY2" s="9"/>
-      <c r="EZ2" s="9"/>
-      <c r="FA2" s="9"/>
-      <c r="FB2" s="9"/>
-      <c r="FC2" s="9"/>
-      <c r="FD2" s="9"/>
-      <c r="FE2" s="9"/>
-      <c r="FF2" s="9"/>
-      <c r="FG2" s="9"/>
-      <c r="FH2" s="9"/>
-      <c r="FI2" s="9"/>
-      <c r="FJ2" s="9"/>
-      <c r="FK2" s="9"/>
-      <c r="FL2" s="9"/>
-      <c r="FM2" s="9"/>
-      <c r="FN2" s="9"/>
-      <c r="FO2" s="9"/>
-      <c r="FP2" s="9"/>
-      <c r="FQ2" s="9"/>
-      <c r="FR2" s="9"/>
-      <c r="FS2" s="9"/>
-      <c r="FT2" s="9"/>
-      <c r="FU2" s="9"/>
-      <c r="FV2" s="9"/>
-      <c r="FW2" s="9"/>
-      <c r="FX2" s="9"/>
-      <c r="FY2" s="9"/>
-      <c r="FZ2" s="9"/>
-      <c r="GA2" s="9"/>
-      <c r="GB2" s="9"/>
-      <c r="GC2" s="9"/>
-      <c r="GD2" s="9"/>
-      <c r="GE2" s="9"/>
-      <c r="GF2" s="9"/>
-      <c r="GG2" s="9"/>
-      <c r="GH2" s="9"/>
-      <c r="GI2" s="9"/>
-      <c r="GJ2" s="9"/>
-      <c r="GK2" s="9"/>
-      <c r="GL2" s="9"/>
-      <c r="GM2" s="9"/>
-      <c r="GN2" s="9"/>
-      <c r="GO2" s="9"/>
-      <c r="GP2" s="9"/>
-      <c r="GQ2" s="9"/>
-      <c r="GR2" s="9"/>
-      <c r="GS2" s="9"/>
-      <c r="GT2" s="9"/>
-      <c r="GU2" s="9"/>
-      <c r="GV2" s="9"/>
-      <c r="GW2" s="9"/>
-      <c r="GX2" s="9"/>
-      <c r="GY2" s="9"/>
-      <c r="GZ2" s="9"/>
-      <c r="HA2" s="9"/>
-      <c r="HB2" s="9"/>
-      <c r="HC2" s="9"/>
-      <c r="HD2" s="9"/>
-      <c r="HE2" s="9"/>
-      <c r="HF2" s="9"/>
-      <c r="HG2" s="9"/>
-      <c r="HH2" s="9"/>
-      <c r="HI2" s="9"/>
-      <c r="HJ2" s="9"/>
-      <c r="HK2" s="9"/>
-      <c r="HL2" s="9"/>
-      <c r="HM2" s="9"/>
-      <c r="HN2" s="9"/>
-      <c r="HO2" s="9"/>
-      <c r="HP2" s="9"/>
-      <c r="HQ2" s="9"/>
-      <c r="HR2" s="9"/>
-      <c r="HS2" s="9"/>
-      <c r="HT2" s="9"/>
-      <c r="HU2" s="9"/>
-      <c r="HV2" s="9"/>
-      <c r="HW2" s="9"/>
-      <c r="HX2" s="9"/>
-      <c r="HY2" s="9"/>
-      <c r="HZ2" s="9"/>
-      <c r="IA2" s="9"/>
-      <c r="IB2" s="9"/>
-      <c r="IC2" s="9"/>
-      <c r="ID2" s="9"/>
-      <c r="IE2" s="9"/>
-      <c r="IF2" s="9"/>
-      <c r="IG2" s="9"/>
-      <c r="IH2" s="9"/>
-      <c r="II2" s="9"/>
-      <c r="IJ2" s="9"/>
-      <c r="IK2" s="9"/>
-      <c r="IL2" s="9"/>
-      <c r="IM2" s="9"/>
-      <c r="IN2" s="9"/>
-      <c r="IO2" s="9"/>
-      <c r="IP2" s="9"/>
-      <c r="IQ2" s="9"/>
-      <c r="IR2" s="9"/>
-      <c r="IS2" s="9"/>
-      <c r="IT2" s="9"/>
-      <c r="IU2" s="9"/>
-      <c r="IV2" s="9"/>
-      <c r="IW2" s="9"/>
-      <c r="IX2" s="11"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
+      <c r="AE2" s="11"/>
+      <c r="AF2" s="11"/>
+      <c r="AG2" s="11"/>
+      <c r="AH2" s="11"/>
+      <c r="AI2" s="11"/>
+      <c r="AJ2" s="11"/>
+      <c r="AK2" s="11"/>
+      <c r="AL2" s="11"/>
+      <c r="AM2" s="11"/>
+      <c r="AN2" s="11"/>
+      <c r="AO2" s="11"/>
+      <c r="AP2" s="11"/>
+      <c r="AQ2" s="11"/>
+      <c r="AR2" s="11"/>
+      <c r="AS2" s="11"/>
+      <c r="AT2" s="11"/>
+      <c r="AU2" s="11"/>
+      <c r="AV2" s="11"/>
+      <c r="AW2" s="11"/>
+      <c r="AX2" s="11"/>
+      <c r="AY2" s="11"/>
+      <c r="AZ2" s="11"/>
+      <c r="BA2" s="11"/>
+      <c r="BB2" s="11"/>
+      <c r="BC2" s="11"/>
+      <c r="BD2" s="11"/>
+      <c r="BE2" s="11"/>
+      <c r="BF2" s="11"/>
+      <c r="BG2" s="11"/>
+      <c r="BH2" s="11"/>
+      <c r="BI2" s="11"/>
+      <c r="BJ2" s="11"/>
+      <c r="BK2" s="11"/>
+      <c r="BL2" s="11"/>
+      <c r="BM2" s="11"/>
+      <c r="BN2" s="11"/>
+      <c r="BO2" s="11"/>
+      <c r="BP2" s="11"/>
+      <c r="BQ2" s="11"/>
+      <c r="BR2" s="11"/>
+      <c r="BS2" s="11"/>
+      <c r="BT2" s="11"/>
+      <c r="BU2" s="11"/>
+      <c r="BV2" s="11"/>
+      <c r="BW2" s="11"/>
+      <c r="BX2" s="11"/>
+      <c r="BY2" s="11"/>
+      <c r="BZ2" s="11"/>
+      <c r="CA2" s="11"/>
+      <c r="CB2" s="11"/>
+      <c r="CC2" s="11"/>
+      <c r="CD2" s="11"/>
+      <c r="CE2" s="11"/>
+      <c r="CF2" s="11"/>
+      <c r="CG2" s="11"/>
+      <c r="CH2" s="11"/>
+      <c r="CI2" s="11"/>
+      <c r="CJ2" s="11"/>
+      <c r="CK2" s="11"/>
+      <c r="CL2" s="11"/>
+      <c r="CM2" s="11"/>
+      <c r="CN2" s="11"/>
+      <c r="CO2" s="11"/>
+      <c r="CP2" s="11"/>
+      <c r="CQ2" s="11"/>
+      <c r="CR2" s="11"/>
+      <c r="CS2" s="11"/>
+      <c r="CT2" s="11"/>
+      <c r="CU2" s="11"/>
+      <c r="CV2" s="11"/>
+      <c r="CW2" s="11"/>
+      <c r="CX2" s="11"/>
+      <c r="CY2" s="11"/>
+      <c r="CZ2" s="11"/>
+      <c r="DA2" s="11"/>
+      <c r="DB2" s="11"/>
+      <c r="DC2" s="11"/>
+      <c r="DD2" s="11"/>
+      <c r="DE2" s="11"/>
+      <c r="DF2" s="11"/>
+      <c r="DG2" s="11"/>
+      <c r="DH2" s="11"/>
+      <c r="DI2" s="11"/>
+      <c r="DJ2" s="11"/>
+      <c r="DK2" s="11"/>
+      <c r="DL2" s="11"/>
+      <c r="DM2" s="11"/>
+      <c r="DN2" s="11"/>
+      <c r="DO2" s="11"/>
+      <c r="DP2" s="11"/>
+      <c r="DQ2" s="11"/>
+      <c r="DR2" s="11"/>
+      <c r="DS2" s="11"/>
+      <c r="DT2" s="11"/>
+      <c r="DU2" s="11"/>
+      <c r="DV2" s="11"/>
+      <c r="DW2" s="11"/>
+      <c r="DX2" s="11"/>
+      <c r="DY2" s="11"/>
+      <c r="DZ2" s="11"/>
+      <c r="EA2" s="11"/>
+      <c r="EB2" s="11"/>
+      <c r="EC2" s="11"/>
+      <c r="ED2" s="11"/>
+      <c r="EE2" s="11"/>
+      <c r="EF2" s="11"/>
+      <c r="EG2" s="11"/>
+      <c r="EH2" s="11"/>
+      <c r="EI2" s="11"/>
+      <c r="EJ2" s="11"/>
+      <c r="EK2" s="11"/>
+      <c r="EL2" s="11"/>
+      <c r="EM2" s="11"/>
+      <c r="EN2" s="11"/>
+      <c r="EO2" s="11"/>
+      <c r="EP2" s="11"/>
+      <c r="EQ2" s="11"/>
+      <c r="ER2" s="11"/>
+      <c r="ES2" s="11"/>
+      <c r="ET2" s="11"/>
+      <c r="EU2" s="11"/>
+      <c r="EV2" s="11"/>
+      <c r="EW2" s="11"/>
+      <c r="EX2" s="11"/>
+      <c r="EY2" s="11"/>
+      <c r="EZ2" s="11"/>
+      <c r="FA2" s="11"/>
+      <c r="FB2" s="11"/>
+      <c r="FC2" s="11"/>
+      <c r="FD2" s="11"/>
+      <c r="FE2" s="11"/>
+      <c r="FF2" s="11"/>
+      <c r="FG2" s="11"/>
+      <c r="FH2" s="11"/>
+      <c r="FI2" s="11"/>
+      <c r="FJ2" s="11"/>
+      <c r="FK2" s="11"/>
+      <c r="FL2" s="11"/>
+      <c r="FM2" s="11"/>
+      <c r="FN2" s="11"/>
+      <c r="FO2" s="11"/>
+      <c r="FP2" s="11"/>
+      <c r="FQ2" s="11"/>
+      <c r="FR2" s="11"/>
+      <c r="FS2" s="11"/>
+      <c r="FT2" s="11"/>
+      <c r="FU2" s="11"/>
+      <c r="FV2" s="11"/>
+      <c r="FW2" s="11"/>
+      <c r="FX2" s="11"/>
+      <c r="FY2" s="11"/>
+      <c r="FZ2" s="11"/>
+      <c r="GA2" s="11"/>
+      <c r="GB2" s="11"/>
+      <c r="GC2" s="11"/>
+      <c r="GD2" s="11"/>
+      <c r="GE2" s="11"/>
+      <c r="GF2" s="11"/>
+      <c r="GG2" s="11"/>
+      <c r="GH2" s="11"/>
+      <c r="GI2" s="11"/>
+      <c r="GJ2" s="11"/>
+      <c r="GK2" s="11"/>
+      <c r="GL2" s="11"/>
+      <c r="GM2" s="11"/>
+      <c r="GN2" s="11"/>
+      <c r="GO2" s="11"/>
+      <c r="GP2" s="11"/>
+      <c r="GQ2" s="11"/>
+      <c r="GR2" s="11"/>
+      <c r="GS2" s="11"/>
+      <c r="GT2" s="11"/>
+      <c r="GU2" s="11"/>
+      <c r="GV2" s="11"/>
+      <c r="GW2" s="11"/>
+      <c r="GX2" s="11"/>
+      <c r="GY2" s="11"/>
+      <c r="GZ2" s="11"/>
+      <c r="HA2" s="11"/>
+      <c r="HB2" s="11"/>
+      <c r="HC2" s="11"/>
+      <c r="HD2" s="11"/>
+      <c r="HE2" s="11"/>
+      <c r="HF2" s="11"/>
+      <c r="HG2" s="11"/>
+      <c r="HH2" s="11"/>
+      <c r="HI2" s="11"/>
+      <c r="HJ2" s="11"/>
+      <c r="HK2" s="11"/>
+      <c r="HL2" s="11"/>
+      <c r="HM2" s="11"/>
+      <c r="HN2" s="11"/>
+      <c r="HO2" s="11"/>
+      <c r="HP2" s="11"/>
+      <c r="HQ2" s="11"/>
+      <c r="HR2" s="11"/>
+      <c r="HS2" s="11"/>
+      <c r="HT2" s="11"/>
+      <c r="HU2" s="11"/>
+      <c r="HV2" s="11"/>
+      <c r="HW2" s="11"/>
+      <c r="HX2" s="11"/>
+      <c r="HY2" s="11"/>
+      <c r="HZ2" s="11"/>
+      <c r="IA2" s="11"/>
+      <c r="IB2" s="11"/>
+      <c r="IC2" s="11"/>
+      <c r="ID2" s="11"/>
+      <c r="IE2" s="11"/>
+      <c r="IF2" s="11"/>
+      <c r="IG2" s="11"/>
+      <c r="IH2" s="11"/>
+      <c r="II2" s="11"/>
+      <c r="IJ2" s="11"/>
+      <c r="IK2" s="11"/>
+      <c r="IL2" s="11"/>
+      <c r="IM2" s="11"/>
+      <c r="IN2" s="11"/>
+      <c r="IO2" s="11"/>
+      <c r="IP2" s="11"/>
+      <c r="IQ2" s="11"/>
+      <c r="IR2" s="11"/>
+      <c r="IS2" s="11"/>
+      <c r="IT2" s="11"/>
+      <c r="IU2" s="11"/>
+      <c r="IV2" s="11"/>
+      <c r="IW2" s="11"/>
+      <c r="IX2" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2297,12 +2233,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="13.8" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="13.8" customHeight="1">
-      <c r="A2" s="13"/>
+      <c r="A2" s="15"/>
     </row>
     <row r="3" spans="1:1" ht="16.05" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -2348,12 +2284,12 @@
       <c r="A11" s="3"/>
     </row>
     <row r="12" spans="1:1" ht="13.8" customHeight="1">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="16" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="12" customHeight="1">
-      <c r="A13" s="15"/>
+      <c r="A13" s="17"/>
     </row>
     <row r="14" spans="1:1" ht="16.05" customHeight="1">
       <c r="A14" s="4" t="s">
